--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -30,10 +30,13 @@
     <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
   </si>
   <si>
+    <t xml:space="preserve">MART </t>
+  </si>
+  <si>
     <t xml:space="preserve">NİSAN </t>
   </si>
   <si>
-    <t xml:space="preserve">MART </t>
+    <t>OCAK</t>
   </si>
   <si>
     <r>
@@ -55,44 +58,47 @@
     </r>
   </si>
   <si>
-    <t>OCAK</t>
+    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
   </si>
   <si>
     <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
   </si>
   <si>
     <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
     <t>İstiklal Marşı Kabulü Provası</t>
   </si>
   <si>
     <t>5 Ocak 2026 Pazartesi</t>
   </si>
   <si>
+    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
     <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
   </si>
   <si>
     <t>*18 Mart Şehitleri Anma Günü Provası 
 *16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
   </si>
   <si>
-    <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
   </si>
   <si>
     <t>Çeşme Belediyesi Türk Halk Müziği Korosu “ Çeşme’den Türkü Akıyor” 2026 Kış Konseri
@@ -101,161 +107,85 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
+    <t>CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
+  </si>
+  <si>
+    <t>13 Nisan 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Ot Festivali ile ilgili toplantı 14.00</t>
+  </si>
+  <si>
+    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
+  </si>
+  <si>
+    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
+    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+  </si>
+  <si>
+    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
   </si>
   <si>
     <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
   </si>
   <si>
-    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+    <t>Belediye TSM Konseri Tüm gün</t>
   </si>
   <si>
     <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
   </si>
   <si>
-    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>Ot Festivali ile ilgili toplantı 14.00</t>
-  </si>
-  <si>
-    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
-  </si>
-  <si>
-    <t>RAMAZAN BAYRAMI</t>
-  </si>
-  <si>
-    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
-  </si>
-  <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
     <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
-  </si>
-  <si>
-    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>YARI YIL ETKİNLİKLERİ</t>
-  </si>
-  <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>19 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim tüm gün</t>
-  </si>
-  <si>
-    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
-  </si>
-  <si>
-    <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
--Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
-  </si>
-  <si>
-    <t>CHP Eğitim 17.00-20.00</t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
-  </si>
-  <si>
-    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
-  </si>
-  <si>
-    <t>13 Nisan 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>31 Ocak 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
   </si>
   <si>
     <r>
@@ -275,48 +205,278 @@
     </r>
   </si>
   <si>
+    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
+  </si>
+  <si>
+    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+  </si>
+  <si>
+    <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>YARI YIL ETKİNLİKLERİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
+  </si>
+  <si>
     <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
   </si>
   <si>
-    <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
+    <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
+  </si>
+  <si>
+    <t>RAMAZAN BAYRAMI</t>
   </si>
   <si>
     <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
+    <t>19 Ocak 2026 Pazartesi</t>
   </si>
   <si>
     <t>28 Şubat 2026 Cumartesi</t>
   </si>
   <si>
-    <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
   </si>
   <si>
     <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
   </si>
   <si>
-    <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
+    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim tüm gün</t>
+  </si>
+  <si>
+    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
+  </si>
+  <si>
+    <t>31 Ocak 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
+  </si>
+  <si>
+    <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
+-Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
+  </si>
+  <si>
+    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+  </si>
+  <si>
+    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>MAYIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>3 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
+  </si>
+  <si>
+    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>10 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
+  </si>
+  <si>
+    <t>21.30 konser provası Başkan ile</t>
+  </si>
+  <si>
+    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
+  </si>
+  <si>
+    <t>11 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>16 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t>Bilgiç Anaokulu Prova 
+10.30-15.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilgiç Anaokulu Prova 
+10.30-15.30                                               </t>
+  </si>
+  <si>
+    <t>-Bilgiç ortaokulu 09.00-12.00
+-Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
+  </si>
+  <si>
+    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
+"No Mans Land" Yetişkin Oyunu 20.00
+onaylandı.</t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
+  </si>
+  <si>
+    <t>18 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>23 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t>24 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro</t>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
+    </r>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
+  </si>
+  <si>
+    <t>BAYRAM</t>
+  </si>
+  <si>
+    <t>25 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
   </si>
   <si>
     <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
   <si>
+    <t xml:space="preserve">TEMMUZ </t>
+  </si>
+  <si>
     <t xml:space="preserve">HAZİRAN </t>
   </si>
   <si>
-    <t>MAYIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEMMUZ </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -338,16 +498,10 @@
     <t>7 HAZİRAN 2026 PAZAR</t>
   </si>
   <si>
-    <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
+    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>3 MAYIS 2026 PAZAR</t>
   </si>
   <si>
     <r>
@@ -367,6 +521,10 @@
     </r>
   </si>
   <si>
+    <t>Latin Katolik Kilisesi Ayin 
+18.30</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -384,23 +542,19 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t>Bilgiç İlkokulu 13.00 1. Sınıf Okuma Bayramı 18.00
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
   </si>
   <si>
-    <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
+    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
   </si>
   <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
   </si>
   <si>
-    <t>Latin Katolik Kilisesi Ayin 
-18.30</t>
-  </si>
-  <si>
     <t xml:space="preserve">8 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -410,9 +564,6 @@
     <t xml:space="preserve">10 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
-    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
-  </si>
-  <si>
     <t xml:space="preserve">11 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
@@ -425,43 +576,7 @@
     <t xml:space="preserve">14 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
-    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t>10 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00</t>
-  </si>
-  <si>
-    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>21.30 konser provası Başkan ile</t>
   </si>
   <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00                                                        "SEVGİLİ DOKTOR"  20.00</t>
@@ -485,67 +600,46 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>-SERTUR KOOPERATİF TOPLANTISI HALUK BEY 05336460236 
+15.00'a kadar
+- Kent Enstitüsü Prova</t>
+  </si>
+  <si>
     <t>-Çoklu İklim Krizinin Gölgesinde Orman Yangınları
 Afet İşleri Toplantı (Başkan Davet edilecekmiş)
 -Belediye Meclisi 17.00'dan sonra</t>
   </si>
   <si>
-    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
-  </si>
-  <si>
-    <t>-SERTUR KOOPERATİF TOPLANTISI HALUK BEY 05336460236 
-15.00'a kadar
-- Kent Enstitüsü Prova</t>
-  </si>
-  <si>
     <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
   </si>
   <si>
+    <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
+  </si>
+  <si>
     <t>Belediye meclisi 16.00'dan sonra</t>
   </si>
   <si>
-    <t>11 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
+    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
   </si>
   <si>
     <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
   </si>
   <si>
-    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
     <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
-    <t>16 MAYIS 2026 CUMARTESİ</t>
+    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
     <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
   </si>
   <si>
-    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
@@ -564,13 +658,13 @@
     <t>Atatürk Lisesi tiyatro prova</t>
   </si>
   <si>
-    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
-  </si>
-  <si>
     <t>Atatürk Lisesi Oyun Günü</t>
   </si>
   <si>
     <t>Osman Uysal Prova opsiyon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
@@ -583,144 +677,50 @@
     <t>Namık Kemal Okuma Bayramı</t>
   </si>
   <si>
-    <t>Bilgiç Anaokulu Prova 
-10.30-15.30</t>
-  </si>
-  <si>
     <t>Doğu Der Toplantı</t>
   </si>
   <si>
-    <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">Bilgiç Anaokulu Prova 
-10.30-15.30                                               </t>
-  </si>
-  <si>
     <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
-    <t>-Bilgiç ortaokulu 09.00-12.00
--Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
-  </si>
-  <si>
     <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
     <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
-    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
-"No Mans Land" Yetişkin Oyunu 20.00
-onaylandı.</t>
-  </si>
-  <si>
     <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
-    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
-  </si>
-  <si>
-    <t>18 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
+    <t xml:space="preserve">21 TEMMUZ 2026 SALI </t>
   </si>
   <si>
     <t>Reyhan Cici Piyano Dinletisi
 Ödendi. Dilekçe geldi. Tel no:5320631925 12.00-20.00</t>
   </si>
   <si>
-    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t>MHP 15. Olağan Kongre Toplantısı</t>
   </si>
   <si>
-    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t>23 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
     <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t>24 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
-    </r>
-  </si>
-  <si>
-    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
-  </si>
-  <si>
-    <t>BAYRAM</t>
-  </si>
-  <si>
     <t xml:space="preserve">25 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>25 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
   </si>
   <si>
     <t>-Serakent Koop. Toplantısı Ödendi. İlhan Demli 5056804306 
@@ -818,28 +818,28 @@
     <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
   </si>
   <si>
+    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t>3 EKİM 2026 CUMARTESİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t>3 EKİM 2026 CUMARTESİ</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Yeni Parti Toplantı</t>
+  </si>
+  <si>
+    <t>5 EKİM 2026 PAZARTESİ</t>
   </si>
   <si>
     <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
 Haydar Ali tel no: 5527151935</t>
   </si>
   <si>
-    <t>Yeni Parti Toplantı</t>
-  </si>
-  <si>
-    <t>5 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
     <t xml:space="preserve">6 EKİM 2026 SALI </t>
   </si>
   <si>
@@ -849,49 +849,70 @@
     <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
   </si>
   <si>
+    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
     <t>Hafifletici Sebepler opsiyon</t>
   </si>
   <si>
+    <t>12 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t>12 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
+    <t>19 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 EKİM 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t>Belediye Meclis 15.00 Tüm alan</t>
   </si>
   <si>
-    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
+    <t xml:space="preserve">22 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
   </si>
   <si>
     <t xml:space="preserve">14 EYLÜL 2026 PAZARTESİ </t>
@@ -900,19 +921,19 @@
     <t xml:space="preserve">15 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t>19 EKİM 2026 PAZARTESİ</t>
+    <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">19 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">20 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 EKİM 2026 PERŞEMBE </t>
+    <t xml:space="preserve">27 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 EKİM 2026 PERŞEMBE </t>
   </si>
   <si>
     <t xml:space="preserve">09:00-16:00 
@@ -920,10 +941,10 @@
 Müdürlüğü   ( İzmir Yurttaş Meclisi) </t>
   </si>
   <si>
-    <t xml:space="preserve">23 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 EKİM 2026 CUMARTESİ </t>
+    <t xml:space="preserve">30 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">12:30-17:00
@@ -931,9 +952,6 @@
 Müdürlüğü   ( İzmir Yurttaş Meclisi) </t>
   </si>
   <si>
-    <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
     <t>Çeşme Belediyespor Tekwando velileri toplantı 16.00-17.00</t>
   </si>
   <si>
@@ -943,28 +961,10 @@
     <t xml:space="preserve">22 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
     <t xml:space="preserve">26 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">29 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 EKİM 2026 CUMA </t>
-  </si>
-  <si>
     <t>Osman Uysal Konser Prova 18.00-22.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>Osman Uysal Konser 20.30 (tüm gün)</t>
@@ -1219,19 +1219,19 @@
     </font>
     <font>
       <b/>
+      <sz val="14.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font/>
-    <font>
-      <b/>
-      <sz val="14.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1264,18 +1264,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF38761D"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FFEFEFEF"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF38761D"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1319,14 +1319,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6B26B"/>
-        <bgColor rgb="FFF6B26B"/>
+        <fgColor rgb="FFE69138"/>
+        <bgColor rgb="FFE69138"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE69138"/>
-        <bgColor rgb="FFE69138"/>
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF6B26B"/>
       </patternFill>
     </fill>
     <fill>
@@ -1337,8 +1337,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FF93C47D"/>
+        <bgColor rgb="FF93C47D"/>
       </patternFill>
     </fill>
     <fill>
@@ -1349,14 +1349,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF93C47D"/>
-        <bgColor rgb="FF93C47D"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -1433,49 +1433,46 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1483,21 +1480,29 @@
     <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -1505,11 +1510,21 @@
     <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1517,71 +1532,59 @@
     <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="8" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
@@ -1590,31 +1593,28 @@
     <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="15" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="12" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="12" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1887,7 +1887,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
@@ -1895,204 +1895,204 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="13" t="s">
-        <v>5</v>
+      <c r="A2" s="12" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="14">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="13">
         <v>46023.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="14">
         <v>46024.0</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>46026.0</v>
       </c>
     </row>
     <row r="4" ht="95.25" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="14">
         <v>46028.0</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="14">
         <v>46029.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="14">
         <v>46030.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="14">
         <v>46031.0</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="14">
+      <c r="F5" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="13">
         <v>46033.0</v>
       </c>
     </row>
     <row r="6" ht="97.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="24" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="25" t="s">
         <v>20</v>
       </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="25" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="14">
         <v>46035.0</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <v>46036.0</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <v>46037.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="14">
         <v>46038.0</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="28">
+      <c r="F7" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="31">
         <v>46040.0</v>
       </c>
     </row>
     <row r="8" ht="69.0" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="16" t="s">
+      <c r="A8" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="30" t="s">
+      <c r="B8" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="30" t="s">
-        <v>42</v>
+      <c r="C8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="14">
         <v>46042.0</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <v>46043.0</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <v>46044.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="14">
         <v>46045.0</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="14">
+      <c r="F9" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="13">
         <v>46047.0</v>
       </c>
     </row>
     <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>42</v>
+      <c r="A10" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>55</v>
       </c>
       <c r="G10" s="21"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="14">
         <v>46049.0</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="28">
         <v>46050.0</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="28">
         <v>46051.0</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <v>46052.0</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="10"/>
+      <c r="F11" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16" t="s">
-        <v>65</v>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="21"/>
-      <c r="F12" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="37"/>
+      <c r="F12" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2128,7 +2128,7 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -2139,95 +2139,95 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="18" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="F3" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4" ht="84.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
       <c r="D4" s="21"/>
       <c r="E4" s="21"/>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="G4" s="49" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="G4" s="48" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>239</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1">
       <c r="A6" s="21"/>
       <c r="B6" s="21"/>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="62" t="s">
         <v>242</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
-      <c r="F6" s="63" t="s">
+      <c r="F6" s="62" t="s">
         <v>242</v>
       </c>
       <c r="G6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="F7" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>251</v>
+      <c r="G7" s="18" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
@@ -2240,26 +2240,26 @@
       <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="F9" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="G9" s="18" t="s">
         <v>258</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="10" ht="100.5" customHeight="1">
@@ -2272,25 +2272,25 @@
       <c r="G10" s="21"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="F11" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="G11" s="10"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
       <c r="A12" s="21"/>
@@ -2299,7 +2299,7 @@
       <c r="D12" s="21"/>
       <c r="E12" s="21"/>
       <c r="F12" s="21"/>
-      <c r="G12" s="10"/>
+      <c r="G12" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2333,10 +2333,10 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="42" t="s">
         <v>280</v>
       </c>
       <c r="B2" s="3"/>
@@ -2344,48 +2344,48 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="18" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="17" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="21"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>282</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>288</v>
       </c>
     </row>
@@ -2399,25 +2399,25 @@
       <c r="G6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>295</v>
       </c>
     </row>
@@ -2431,25 +2431,25 @@
       <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>297</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>300</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>301</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>302</v>
       </c>
     </row>
@@ -2463,25 +2463,25 @@
       <c r="G10" s="21"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>309</v>
       </c>
     </row>
@@ -2497,24 +2497,24 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2550,10 +2550,10 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="51" t="s">
         <v>312</v>
       </c>
       <c r="B2" s="3"/>
@@ -2561,31 +2561,31 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>317</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="10"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
@@ -2594,25 +2594,25 @@
       <c r="G4" s="21"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>325</v>
       </c>
     </row>
@@ -2626,25 +2626,25 @@
       <c r="G6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>332</v>
       </c>
     </row>
@@ -2658,25 +2658,25 @@
       <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>339</v>
       </c>
     </row>
@@ -2690,30 +2690,30 @@
       <c r="G10" s="21"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>340</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="17" t="s">
         <v>343</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2741,7 +2741,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="63.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
@@ -2749,7 +2749,7 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
@@ -2765,15 +2765,15 @@
       <c r="T1" s="7"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>4</v>
+      <c r="A2" s="10" t="s">
+        <v>5</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -2789,13 +2789,13 @@
       <c r="T2" s="7"/>
     </row>
     <row r="3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="17">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="19">
         <v>46054.0</v>
       </c>
       <c r="H3" s="7"/>
@@ -2813,13 +2813,13 @@
       <c r="T3" s="7"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
       <c r="F4" s="20"/>
-      <c r="G4" s="16"/>
+      <c r="G4" s="15"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -2835,25 +2835,25 @@
       <c r="T4" s="7"/>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="25">
+      <c r="A5" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="24">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="24">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="24">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="24">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="17">
+      <c r="F5" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="19">
         <v>46061.0</v>
       </c>
       <c r="H5" s="7"/>
@@ -2871,18 +2871,18 @@
       <c r="T5" s="7"/>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>34</v>
+      <c r="A6" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>30</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -2899,25 +2899,25 @@
       <c r="T6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="25">
+      <c r="A7" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="24">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="24">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="24">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="24">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="17">
+      <c r="F7" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="19">
         <v>46068.0</v>
       </c>
       <c r="H7" s="7"/>
@@ -2935,22 +2935,22 @@
       <c r="T7" s="7"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="15"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="16"/>
       <c r="G8" s="34" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -2967,25 +2967,25 @@
       <c r="T8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="25">
+      <c r="A9" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="24">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="24">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="24">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="17">
+      <c r="F9" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="19">
         <v>46075.0</v>
       </c>
       <c r="H9" s="7"/>
@@ -3003,18 +3003,18 @@
       <c r="T9" s="7"/>
     </row>
     <row r="10" ht="89.25" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>72</v>
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -3031,25 +3031,25 @@
       <c r="T10" s="7"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="25">
+      <c r="A11" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="24">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="24">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="24">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="24">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="15"/>
+      <c r="F11" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="16"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
@@ -3065,15 +3065,15 @@
       <c r="T11" s="7"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
@@ -24394,214 +24394,214 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="9" t="s">
-        <v>3</v>
+      <c r="A2" s="8" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="14">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="13">
         <v>46082.0</v>
       </c>
     </row>
     <row r="4" ht="69.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="16" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="B5" s="14">
         <v>46084.0</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="14">
         <v>46085.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="14">
         <v>46086.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="14">
         <v>46087.0</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>46089.0</v>
       </c>
     </row>
     <row r="6" ht="113.25" customHeight="1">
-      <c r="A6" s="10"/>
+      <c r="A6" s="11"/>
       <c r="B6" s="21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="21"/>
-      <c r="D6" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="22"/>
+      <c r="D6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="14">
         <v>46091.0</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="14">
         <v>46092.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="14">
         <v>46093.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="14">
         <v>46094.0</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="14">
+      <c r="F7" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="13">
         <v>46096.0</v>
       </c>
     </row>
     <row r="8" ht="87.0" customHeight="1">
-      <c r="A8" s="10"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="10"/>
+        <v>12</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="11"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="14">
         <v>46098.0</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <v>46099.0</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <v>46100.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="14">
         <v>46101.0</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="14">
+      <c r="F9" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="13">
         <v>46103.0</v>
       </c>
     </row>
     <row r="10" ht="96.0" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="29" t="s">
-        <v>33</v>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="38" t="s">
+        <v>65</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="6"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="14">
         <v>46105.0</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="14">
         <v>46106.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <v>46107.0</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <v>46108.0</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="14">
+      <c r="F11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="13">
         <v>46110.0</v>
       </c>
     </row>
     <row r="12" ht="91.5" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="A13" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="14">
         <v>46112.0</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" ht="95.25" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -24630,7 +24630,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
@@ -24638,187 +24638,187 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="8" t="s">
-        <v>2</v>
+      <c r="A2" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="12">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="14">
         <v>46113.0</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="14">
         <v>46114.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="14">
         <v>46115.0</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="14">
+      <c r="F3" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="13">
         <v>46117.0</v>
       </c>
     </row>
     <row r="4" ht="99.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="14">
         <v>46119.0</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="14">
         <v>46120.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="14">
         <v>46121.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="14">
         <v>46122.0</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="14">
+      <c r="F5" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="13">
         <v>46124.0</v>
       </c>
     </row>
     <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="31" t="s">
-        <v>57</v>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="23" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="14">
+        <v>46126.0</v>
+      </c>
+      <c r="C7" s="28">
+        <v>46127.0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>46128.0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>46129.0</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="13">
+        <v>46131.0</v>
+      </c>
+    </row>
+    <row r="8" ht="80.25" customHeight="1">
+      <c r="A8" s="30"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="14">
+        <v>46133.0</v>
+      </c>
+      <c r="C9" s="14">
+        <v>46134.0</v>
+      </c>
+      <c r="D9" s="13">
+        <v>46135.0</v>
+      </c>
+      <c r="E9" s="14">
+        <v>46136.0</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="13">
+        <v>46138.0</v>
+      </c>
+    </row>
+    <row r="10" ht="92.25" customHeight="1">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="12">
-        <v>46126.0</v>
-      </c>
-      <c r="C7" s="27">
-        <v>46127.0</v>
-      </c>
-      <c r="D7" s="12">
-        <v>46128.0</v>
-      </c>
-      <c r="E7" s="12">
-        <v>46129.0</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="14">
-        <v>46131.0</v>
-      </c>
-    </row>
-    <row r="8" ht="80.25" customHeight="1">
-      <c r="A8" s="35"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="31" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="12">
-        <v>46133.0</v>
-      </c>
-      <c r="C9" s="12">
-        <v>46134.0</v>
-      </c>
-      <c r="D9" s="14">
-        <v>46135.0</v>
-      </c>
-      <c r="E9" s="12">
-        <v>46136.0</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="14">
-        <v>46138.0</v>
-      </c>
-    </row>
-    <row r="10" ht="92.25" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="14">
         <v>46140.0</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="14">
         <v>46141.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <v>46142.0</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13">
-      <c r="D13" s="40"/>
+      <c r="D13" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24854,219 +24854,219 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>84</v>
+      <c r="A2" s="42" t="s">
+        <v>82</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="19" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" customHeight="1">
+      <c r="A4" s="11"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="45"/>
+      <c r="G4" s="23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" ht="20.25" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="G5" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" ht="91.5" customHeight="1">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="D6" s="11"/>
+      <c r="E6" s="46" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="46" t="s">
+      <c r="F6" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="45"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="31" t="s">
+      <c r="E7" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" ht="97.5" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="18" t="s">
+      <c r="E8" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="F9" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="G5" s="19" t="s">
+    </row>
+    <row r="10" ht="93.75" customHeight="1">
+      <c r="A10" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="23" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="31" t="s">
+      <c r="D10" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="50" t="s">
+      <c r="G10" s="50" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="C11" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="G6" s="47"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8" s="52" t="s">
-        <v>168</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="F10" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="G10" s="57" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>197</v>
+      <c r="G11" s="18" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="F12" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="G12" s="57" t="s">
-        <v>189</v>
+      <c r="A12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -25096,183 +25096,183 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>83</v>
+      <c r="A2" s="51" t="s">
+        <v>132</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>92</v>
+      <c r="A3" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="16"/>
+      <c r="A4" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="G4" s="15"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>111</v>
+      <c r="A5" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="183.75" customHeight="1">
-      <c r="A6" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>134</v>
+      <c r="A6" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>149</v>
+      <c r="A7" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="8" ht="101.25" customHeight="1">
-      <c r="A8" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>153</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>154</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>159</v>
+      <c r="A8" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>170</v>
+      <c r="A9" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="10" ht="99.75" customHeight="1">
@@ -25281,25 +25281,25 @@
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
       <c r="E10" s="21"/>
-      <c r="F10" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>177</v>
+      <c r="F10" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="A11" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
       <c r="A12" s="21"/>
@@ -25344,111 +25344,111 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>85</v>
+      <c r="A2" s="51" t="s">
+        <v>131</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="12">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="14">
         <v>46204.0</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="14">
         <v>46205.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="14">
         <v>46206.0</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="G3" s="14">
+      <c r="F3" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="13">
         <v>46208.0</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
       <c r="E4" s="21"/>
-      <c r="F4" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="G4" s="16"/>
+      <c r="F4" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" s="15"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="12">
+      <c r="A5" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="14">
         <v>46211.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="14">
         <v>46212.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="14">
         <v>46213.0</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="G5" s="14">
+      <c r="F5" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="G5" s="13">
         <v>46215.0</v>
       </c>
     </row>
     <row r="6" ht="92.25" customHeight="1">
-      <c r="A6" s="51" t="s">
-        <v>127</v>
+      <c r="A6" s="54" t="s">
+        <v>161</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
-      <c r="D6" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" s="31" t="s">
+      <c r="D6" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6" s="49" t="s">
         <v>143</v>
       </c>
+      <c r="G6" s="23" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" s="27">
+      <c r="A7" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="28">
         <v>46218.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="14">
         <v>46219.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="14">
         <v>46220.0</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G7" s="55">
+      <c r="F7" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="56">
         <v>46222.0</v>
       </c>
     </row>
@@ -25458,31 +25458,31 @@
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
-      <c r="F8" s="48" t="s">
-        <v>103</v>
+      <c r="F8" s="49" t="s">
+        <v>143</v>
       </c>
       <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="C9" s="12">
+      <c r="A9" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" s="14">
         <v>46225.0</v>
       </c>
-      <c r="D9" s="56">
+      <c r="D9" s="57">
         <v>46226.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="14">
         <v>46227.0</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="G9" s="14">
+      <c r="F9" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="G9" s="13">
         <v>46229.0</v>
       </c>
     </row>
@@ -25492,31 +25492,31 @@
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
       <c r="E10" s="21"/>
-      <c r="F10" s="52" t="s">
+      <c r="F10" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="47" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="14">
         <v>46232.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <v>46233.0</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
       <c r="A12" s="21"/>
@@ -25524,8 +25524,8 @@
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="34"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25561,10 +25561,10 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="51" t="s">
         <v>203</v>
       </c>
       <c r="B2" s="3"/>
@@ -25572,52 +25572,52 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="19" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>46236.0</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="48" t="s">
-        <v>103</v>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="49" t="s">
+        <v>143</v>
       </c>
       <c r="G4" s="21"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="14">
         <v>46239.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="14">
         <v>46240.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="14">
         <v>46241.0</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>46243.0</v>
       </c>
     </row>
@@ -25627,31 +25627,31 @@
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="23" t="s">
         <v>208</v>
       </c>
       <c r="G6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="14">
         <v>46246.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="14">
         <v>46247.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="14">
         <v>46248.0</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <v>46250.0</v>
       </c>
     </row>
@@ -25661,110 +25661,110 @@
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
-      <c r="F8" s="48" t="s">
-        <v>103</v>
+      <c r="F8" s="49" t="s">
+        <v>143</v>
       </c>
       <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="14">
         <v>46253.0</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="14">
         <v>46254.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="14">
         <v>46255.0</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="13">
         <v>46257.0</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="48" t="s">
+      <c r="C10" s="40"/>
+      <c r="D10" s="49" t="s">
         <v>215</v>
       </c>
       <c r="E10" s="21"/>
-      <c r="F10" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="G10" s="31" t="s">
+      <c r="F10" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="23" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="14">
         <v>46260.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <v>46261.0</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <v>46262.0</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <v>46264.0</v>
       </c>
     </row>
     <row r="12" ht="94.5" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="49" t="s">
         <v>215</v>
       </c>
       <c r="C12" s="21"/>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="23" t="s">
         <v>221</v>
       </c>
       <c r="G12" s="21"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25800,10 +25800,10 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="51" t="s">
         <v>223</v>
       </c>
       <c r="B2" s="3"/>
@@ -25811,66 +25811,66 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="14">
         <v>46267.0</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="14">
         <v>46268.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="14">
         <v>46269.0</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="G3" s="14">
+      <c r="F3" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="G3" s="13">
         <v>46271.0</v>
       </c>
     </row>
     <row r="4" ht="85.5" customHeight="1">
-      <c r="A4" s="10"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
       <c r="E4" s="60" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>237</v>
+      <c r="A5" s="17" t="s">
+        <v>240</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>240</v>
-      </c>
-      <c r="C5" s="62">
+        <v>241</v>
+      </c>
+      <c r="C5" s="63">
         <v>46274.0</v>
       </c>
       <c r="D5" s="64">
         <v>46275.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="14">
         <v>46276.0</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="G5" s="14">
+      <c r="F5" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="G5" s="13">
         <v>46278.0</v>
       </c>
     </row>
     <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="31" t="s">
-        <v>249</v>
+      <c r="A6" s="23" t="s">
+        <v>254</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -25880,37 +25880,37 @@
       <c r="G6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>252</v>
+      <c r="A7" s="17" t="s">
+        <v>259</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>253</v>
-      </c>
-      <c r="C7" s="62">
+        <v>260</v>
+      </c>
+      <c r="C7" s="63">
         <v>46281.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="14">
         <v>46282.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="14">
         <v>46283.0</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="G7" s="14">
+      <c r="F7" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="G7" s="13">
         <v>46285.0</v>
       </c>
     </row>
     <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>264</v>
+      <c r="A8" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>270</v>
       </c>
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
@@ -25918,31 +25918,31 @@
       <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="C9" s="12">
+      <c r="A9" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="C9" s="14">
         <v>46288.0</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="14">
         <v>46289.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="14">
         <v>46290.0</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="G9" s="14">
+      <c r="F9" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="G9" s="13">
         <v>46292.0</v>
       </c>
     </row>
     <row r="10" ht="98.25" customHeight="1">
       <c r="A10" s="60" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
@@ -25950,36 +25950,36 @@
       <c r="E10" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="23" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="14">
         <v>46295.0</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -30,10 +30,10 @@
     <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
   </si>
   <si>
+    <t xml:space="preserve">MART </t>
+  </si>
+  <si>
     <t>OCAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NİSAN </t>
   </si>
   <si>
     <r>
@@ -55,16 +55,28 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">MART </t>
+    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
   </si>
   <si>
     <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NİSAN </t>
+  </si>
+  <si>
     <t>5 Ocak 2026 Pazartesi</t>
   </si>
   <si>
     <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Provası</t>
   </si>
   <si>
     <t>Çeşme Belediyesi Türk Halk Müziği Korosu “ Çeşme’den Türkü Akıyor” 2026 Kış Konseri
@@ -73,143 +85,189 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
-    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
+    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
   </si>
   <si>
     <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
-  </si>
-  <si>
-    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
-  </si>
-  <si>
-    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
-  </si>
-  <si>
-    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
-  </si>
-  <si>
-    <t>YARI YIL ETKİNLİKLERİ</t>
   </si>
   <si>
     <t>*18 Mart Şehitleri Anma Günü Provası 
 *16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
   </si>
   <si>
+    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
+  </si>
+  <si>
+    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
+  </si>
+  <si>
+    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+  </si>
+  <si>
+    <t>YARI YIL ETKİNLİKLERİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>RAMAZAN BAYRAMI</t>
+  </si>
+  <si>
+    <t>19 Ocak 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Ot Festivali ile ilgili toplantı 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
+  </si>
+  <si>
+    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim tüm gün</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
+  </si>
+  <si>
+    <t>31 Ocak 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
+-Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
+  </si>
+  <si>
+    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
+  </si>
+  <si>
+    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Belediye TSM Konseri Tüm gün</t>
+  </si>
+  <si>
+    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
+  </si>
+  <si>
     <t>CHP Eğitim 17.00-20.00</t>
   </si>
   <si>
-    <t>19 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
+    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
+  </si>
+  <si>
+    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
   </si>
   <si>
     <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
   </si>
   <si>
-    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
+    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
   </si>
   <si>
     <t>13 Nisan 2026 Pazartesi</t>
   </si>
   <si>
-    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
+    <t>28 Şubat 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
   </si>
   <si>
     <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>Ot Festivali ile ilgili toplantı 14.00</t>
-  </si>
-  <si>
-    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
-  </si>
-  <si>
-    <t>31 Ocak 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
-  </si>
-  <si>
-    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
-  </si>
-  <si>
-    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
-  </si>
-  <si>
-    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
     <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>RAMAZAN BAYRAMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
   </si>
   <si>
     <r>
@@ -229,152 +287,64 @@
     </r>
   </si>
   <si>
-    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
-  </si>
-  <si>
     <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
   </si>
   <si>
-    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
-  </si>
-  <si>
     <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
-  </si>
-  <si>
     <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
     <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
   </si>
   <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim tüm gün</t>
-  </si>
-  <si>
-    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
-  </si>
-  <si>
     <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
-  </si>
-  <si>
-    <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
--Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
     <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
   </si>
   <si>
-    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
-  </si>
-  <si>
-    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>28 Şubat 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
+    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAZİRAN </t>
   </si>
   <si>
     <t>MAYIS</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
+    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>7 HAZİRAN 2026 PAZAR</t>
   </si>
   <si>
     <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
   </si>
   <si>
-    <t xml:space="preserve">HAZİRAN </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>3 MAYIS 2026 PAZAR</t>
   </si>
   <si>
-    <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>7 HAZİRAN 2026 PAZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
-  </si>
-  <si>
-    <t>10 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
   </si>
   <si>
     <r>
@@ -394,7 +364,7 @@
     </r>
   </si>
   <si>
-    <t>21.30 konser provası Başkan ile</t>
+    <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
   </si>
   <si>
     <r>
@@ -418,64 +388,67 @@
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
   </si>
   <si>
-    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
-  </si>
-  <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
   </si>
   <si>
-    <t>11 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
+    <t xml:space="preserve">8 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
     <t xml:space="preserve">TEMMUZ </t>
   </si>
   <si>
-    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t>16 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t xml:space="preserve">12 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
     <t>13 HAZİRAN 2026 CUMARTESİ</t>
   </si>
   <si>
+    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">14 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
+    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00</t>
   </si>
   <si>
-    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
+    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>10 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
   </si>
   <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00                                                        "SEVGİLİ DOKTOR"  20.00</t>
+  </si>
+  <si>
+    <t>21.30 konser provası Başkan ile</t>
   </si>
   <si>
     <r>
@@ -496,24 +469,98 @@
     </r>
   </si>
   <si>
-    <t>Bilgiç Anaokulu Prova 
-10.30-15.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t>-SERTUR KOOPERATİF TOPLANTISI HALUK BEY 05336460236 
 15.00'a kadar
 - Kent Enstitüsü Prova</t>
   </si>
   <si>
+    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
+  </si>
+  <si>
+    <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
+  </si>
+  <si>
+    <t>11 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t>16 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t>Atatürk Lisesi tiyatro prova</t>
+  </si>
+  <si>
+    <t>Atatürk Lisesi Oyun Günü</t>
+  </si>
+  <si>
+    <t>Bilgiç Anaokulu Prova 
+10.30-15.30</t>
+  </si>
+  <si>
+    <t>Osman Uysal Prova opsiyon</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bilgiç Anaokulu Prova 
 10.30-15.30                                               </t>
   </si>
   <si>
+    <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
+sabahtan 21.00'a kadar</t>
+  </si>
+  <si>
     <t>-Bilgiç ortaokulu 09.00-12.00
 -Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
+  </si>
+  <si>
+    <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
+  </si>
+  <si>
+    <t>Latin Katolik Kilisesi Ayin 
+18.30</t>
   </si>
   <si>
     <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
@@ -521,65 +568,70 @@
 onaylandı.</t>
   </si>
   <si>
+    <t>Namık Kemal Okuma Bayramı</t>
+  </si>
+  <si>
     <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
   </si>
   <si>
-    <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
+    <t>Doğu Der Toplantı</t>
   </si>
   <si>
     <t>18 MAYIS 2026 PAZARTESİ</t>
   </si>
   <si>
+    <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">19 MAYIS 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
   </si>
   <si>
+    <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
     <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
   </si>
   <si>
-    <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
+    <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
     <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
     <t>23 MAYIS 2026 CUMARTESİ</t>
   </si>
   <si>
-    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
+    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>24 MAYIS 2026 PAZAR</t>
   </si>
   <si>
-    <t>Latin Katolik Kilisesi Ayin 
-18.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
+    <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
     <t>Özhan Bakadur tiyatro</t>
   </si>
   <si>
-    <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
   </si>
   <si>
-    <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
+    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
   </si>
   <si>
     <r>
@@ -599,41 +651,11 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
     <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
   </si>
   <si>
-    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t>Atatürk Lisesi tiyatro prova</t>
-  </si>
-  <si>
-    <t>Atatürk Lisesi Oyun Günü</t>
-  </si>
-  <si>
-    <t>Osman Uysal Prova opsiyon</t>
-  </si>
-  <si>
-    <t>BAYRAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
-sabahtan 21.00'a kadar</t>
-  </si>
-  <si>
-    <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
-  </si>
-  <si>
-    <t>Namık Kemal Okuma Bayramı</t>
-  </si>
-  <si>
-    <t>Doğu Der Toplantı</t>
+    <t>Reyhan Cici Piyano Dinletisi
+Ödendi. Dilekçe geldi. Tel no:5320631925 12.00-20.00</t>
   </si>
   <si>
     <t>-Çoklu İklim Krizinin Gölgesinde Orman Yangınları
@@ -641,77 +663,55 @@
 -Belediye Meclisi 17.00'dan sonra</t>
   </si>
   <si>
-    <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
+    <t>MHP 15. Olağan Kongre Toplantısı</t>
+  </si>
+  <si>
+    <t>BAYRAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t>Belediye meclisi 16.00'dan sonra</t>
   </si>
   <si>
     <t>25 MAYIS 2026 PAZARTESİ</t>
   </si>
   <si>
-    <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
+    <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
   </si>
   <si>
     <t xml:space="preserve">26 MAYIS 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
     <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
   </si>
   <si>
-    <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
   </si>
   <si>
-    <t>Belediye meclisi 16.00'dan sonra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
+    <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
   </si>
   <si>
     <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
   </si>
   <si>
-    <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
+    <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
   </si>
   <si>
-    <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
   </si>
   <si>
-    <t>Reyhan Cici Piyano Dinletisi
-Ödendi. Dilekçe geldi. Tel no:5320631925 12.00-20.00</t>
-  </si>
-  <si>
-    <t>MHP 15. Olağan Kongre Toplantısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
@@ -742,22 +742,38 @@
     <t xml:space="preserve">31 TEMMZ 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">EYLÜL </t>
+  </si>
+  <si>
     <t>AĞUSTOS</t>
   </si>
   <si>
+    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
+Haydar Ali tel no: 5527151935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">4 AĞUSTOS 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">8 AĞUSTOS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EYLÜL </t>
   </si>
   <si>
     <t>-Orkent Sitesi 11.00-13.00 ödendi.
@@ -765,97 +781,34 @@
 18.30</t>
   </si>
   <si>
+    <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">10 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">11 AĞUSTOS 2026 SALI </t>
   </si>
   <si>
+    <t>Belediye Meclis 15.00 Tüm alan</t>
+  </si>
+  <si>
     <t xml:space="preserve">15 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
+    <t xml:space="preserve">14 EYLÜL 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">17 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">18 AĞUSTOS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 AĞUSTOS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ritim 10.00-12.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Deniz Tatil Sitesi Toplantı 11.00-18.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 AĞUSTOS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 AĞUSTOS 2026 SALI </t>
-  </si>
-  <si>
-    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
-Haydar Ali tel no: 5527151935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 AĞUSTOS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DORUK BELDESİ, ARSA VE YAPI KOOPERATİFİ                                 13.00-15.00  </t>
-  </si>
-  <si>
-    <t>-Saygun Sanat Şirinler Müzikali 2 seans 
--Latin Katolik Kilisesi Ayin 
-18.30(farklı odalar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EKİM </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t>3 EKİM 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t>Belediye Meclis 15.00 Tüm alan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 EYLÜL 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Yeni Parti Toplantı</t>
   </si>
   <si>
     <t xml:space="preserve">09:00-16:00 
@@ -863,51 +816,42 @@
 Müdürlüğü   ( İzmir Yurttaş Meclisi) </t>
   </si>
   <si>
-    <t>5 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
     <t xml:space="preserve">12:30-17:00
 İzmir Büyükşehir Belediyesi Sosyal Hizmetler Dairesi Başkanlığı Kentsel Adalet ve Eşitlik Şube
 Müdürlüğü   ( İzmir Yurttaş Meclisi) </t>
   </si>
   <si>
-    <t xml:space="preserve">6 EKİM 2026 SALI </t>
+    <t xml:space="preserve">22 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>Çeşme Belediyespor Tekwando velileri toplantı 16.00-17.00</t>
   </si>
   <si>
-    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
+    <t xml:space="preserve">Ritim 10.00-12.00 </t>
   </si>
   <si>
     <t xml:space="preserve">21 EYLÜL 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">22 EYLÜL 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">26 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t>Hafifletici Sebepler opsiyon</t>
-  </si>
-  <si>
     <t>Osman Uysal Konser Prova 18.00-22.00</t>
   </si>
   <si>
+    <t>Deniz Tatil Sitesi Toplantı 11.00-18.00</t>
+  </si>
+  <si>
     <t>Osman Uysal Konser 20.30 (tüm gün)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 AĞUSTOS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 AĞUSTOS 2026 SALI </t>
   </si>
   <si>
     <r>
@@ -927,6 +871,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">29 AĞUSTOS 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -944,18 +891,71 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">28 EYLÜL 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORUK BELDESİ, ARSA VE YAPI KOOPERATİFİ                                 13.00-15.00  </t>
+  </si>
+  <si>
+    <t>-Saygun Sanat Şirinler Müzikali 2 seans 
+-Latin Katolik Kilisesi Ayin 
+18.30(farklı odalar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EKİM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t>3 EKİM 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Yeni Parti Toplantı</t>
+  </si>
+  <si>
+    <t>5 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Hafifletici Sebepler opsiyon</t>
+  </si>
+  <si>
     <t>12 EKİM 2026 PAZARTESİ</t>
   </si>
   <si>
-    <t xml:space="preserve">28 EYLÜL 2026 PAZARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">13 EKİM 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">29 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
   </si>
   <si>
@@ -1016,6 +1016,9 @@
     <t xml:space="preserve">1 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t xml:space="preserve">ARALIK </t>
+  </si>
+  <si>
     <t>2 KASIM 2026 PAZARTESİ</t>
   </si>
   <si>
@@ -1037,12 +1040,30 @@
     <t xml:space="preserve">8 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t xml:space="preserve">1 ARALIK 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 ARALIK 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 ARALIK 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 ARALIK 2026 CUMA </t>
+  </si>
+  <si>
     <t>9 KASIM 2026 PAZARTESİ</t>
   </si>
   <si>
+    <t xml:space="preserve">5 ARALIK 2026 CUMA RTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">10 KASIM 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">6 ARALIK 2026 PAZAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">11 KASIM 2026 ÇARŞAMBA </t>
   </si>
   <si>
@@ -1058,12 +1079,33 @@
     <t xml:space="preserve">15 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t xml:space="preserve">7 ARALIK 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 ARALIK 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 ARALIK 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 ARALIK 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 ARALIK 2026 CUMA </t>
+  </si>
+  <si>
     <t xml:space="preserve">16 KASIM 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">12 ARALIK 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">17 KASIM 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">13 ARALIK 2026 PAZAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">18 KASIM 2026 ÇARŞAMBA </t>
   </si>
   <si>
@@ -1079,15 +1121,33 @@
     <t xml:space="preserve">22 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t xml:space="preserve">14 ARALIK 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 ARALIK 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 ARALIK 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 ARALIK 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 ARALIK 2026 CUMA </t>
+  </si>
+  <si>
     <t xml:space="preserve">23 KASIM 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">ARALIK </t>
+    <t xml:space="preserve">19 ARALIK 2026 CUARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">24 KASIM 2025 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">20 ARALIK 2026 PAZAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">25 KASIM 2026 ÇARŞAMBA </t>
   </si>
   <si>
@@ -1103,91 +1163,31 @@
     <t xml:space="preserve">29 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t xml:space="preserve">21 ARALIK 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 ARALIK 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 ARALIK 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 ARALIK 2026 PERŞEMBE </t>
+  </si>
+  <si>
     <t>Tuncay Hoca Çsm</t>
   </si>
   <si>
-    <t xml:space="preserve">1 ARALIK 2026 SALI </t>
+    <t xml:space="preserve">25 ARALIK 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 ARALIK 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>27 ARALIK 2026 PAZAR</t>
   </si>
   <si>
     <t>30 KASIM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 ARALIK 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 ARALIK 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 ARALIK 2026 CUMA RTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 ARALIK 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 ARALIK 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 ARALIK 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 ARALIK 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 ARALIK 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 ARALIK 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 ARALIK 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 ARALIK 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 ARALIK 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 ARALIK 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 ARALIK 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 ARALIK 2026 CUARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 ARALIK 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 ARALIK 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 ARALIK 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 ARALIK 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 ARALIK 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 ARALIK 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>27 ARALIK 2026 PAZAR</t>
   </si>
   <si>
     <t xml:space="preserve">28 ARALIK 2026 PAZARTESİ </t>
@@ -1219,6 +1219,13 @@
     </font>
     <font>
       <b/>
+      <sz val="14.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1227,7 +1234,12 @@
     <font/>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="15.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1235,11 +1247,6 @@
     <font>
       <b/>
       <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1258,19 +1265,12 @@
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
-      <color theme="1"/>
+      <color rgb="FF38761D"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF38761D"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1319,6 +1319,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE69138"/>
+        <bgColor rgb="FFE69138"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF9CB9C"/>
         <bgColor rgb="FFF9CB9C"/>
       </patternFill>
@@ -1331,18 +1337,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE69138"/>
-        <bgColor rgb="FFE69138"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93C47D"/>
-        <bgColor rgb="FF93C47D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
@@ -1351,6 +1345,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
         <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93C47D"/>
+        <bgColor rgb="FF93C47D"/>
       </patternFill>
     </fill>
     <fill>
@@ -1432,111 +1432,111 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1544,66 +1544,60 @@
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="8" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="8" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="14" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
@@ -1611,10 +1605,16 @@
     <xf borderId="4" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="12" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="12" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1887,7 +1887,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
@@ -1898,8 +1898,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>2</v>
+      <c r="A2" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1935,8 +1935,8 @@
       <c r="G4" s="8"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>7</v>
+      <c r="A5" s="16" t="s">
+        <v>9</v>
       </c>
       <c r="B5" s="12">
         <v>46028.0</v>
@@ -1951,7 +1951,7 @@
         <v>46031.0</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5" s="10">
         <v>46033.0</v>
@@ -1962,137 +1962,137 @@
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="19" t="s">
-        <v>9</v>
+      <c r="E6" s="20" t="s">
+        <v>13</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="19" t="s">
-        <v>12</v>
+      <c r="G6" s="20" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>13</v>
+      <c r="A7" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="B7" s="12">
         <v>46035.0</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="23">
         <v>46036.0</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="23">
         <v>46037.0</v>
       </c>
       <c r="E7" s="12">
         <v>46038.0</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="23">
+        <v>20</v>
+      </c>
+      <c r="G7" s="25">
         <v>46040.0</v>
       </c>
     </row>
     <row r="8" ht="69.0" customHeight="1">
-      <c r="A8" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="20" t="s">
+      <c r="A8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="B8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="27" t="s">
-        <v>28</v>
+      <c r="D8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>31</v>
+      <c r="A9" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="B9" s="12">
         <v>46042.0</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="23">
         <v>46043.0</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="23">
         <v>46044.0</v>
       </c>
       <c r="E9" s="12">
         <v>46045.0</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G9" s="10">
         <v>46047.0</v>
       </c>
     </row>
     <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="25"/>
+      <c r="A10" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="19"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>39</v>
+      <c r="A11" s="16" t="s">
+        <v>45</v>
       </c>
       <c r="B11" s="12">
         <v>46049.0</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <v>46050.0</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <v>46051.0</v>
       </c>
       <c r="E11" s="12">
         <v>46052.0</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>43</v>
+      <c r="F11" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="34"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2120,7 +2120,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
@@ -2131,8 +2131,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="61" t="s">
-        <v>229</v>
+      <c r="A2" s="63" t="s">
+        <v>246</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2145,82 +2145,82 @@
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>232</v>
+      <c r="D3" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>248</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" ht="84.0" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="52" t="s">
-        <v>239</v>
-      </c>
-      <c r="G4" s="52" t="s">
-        <v>239</v>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>247</v>
+      <c r="A5" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>256</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
       <c r="C6" s="64" t="s">
-        <v>253</v>
-      </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+        <v>259</v>
+      </c>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
       <c r="F6" s="64" t="s">
-        <v>253</v>
-      </c>
-      <c r="G6" s="25"/>
+        <v>259</v>
+      </c>
+      <c r="G6" s="19"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="B7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>264</v>
       </c>
       <c r="F7" s="14" t="s">
@@ -2231,28 +2231,28 @@
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>271</v>
       </c>
       <c r="F9" s="14" t="s">
@@ -2263,28 +2263,28 @@
       </c>
     </row>
     <row r="10" ht="100.5" customHeight="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>278</v>
       </c>
       <c r="F11" s="14" t="s">
@@ -2293,12 +2293,12 @@
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="8"/>
     </row>
   </sheetData>
@@ -2336,7 +2336,7 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>280</v>
       </c>
       <c r="B2" s="3"/>
@@ -2353,7 +2353,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="16" t="s">
         <v>281</v>
       </c>
     </row>
@@ -2364,141 +2364,141 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="25"/>
+      <c r="G4" s="19"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>286</v>
       </c>
+      <c r="E5" s="16" t="s">
+        <v>287</v>
+      </c>
       <c r="F5" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>293</v>
+      <c r="A7" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>300</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>300</v>
+      <c r="A9" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>314</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>308</v>
+      <c r="A11" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>328</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="65" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>313</v>
+      <c r="A13" s="16" t="s">
+        <v>339</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2508,7 +2508,7 @@
       <c r="G13" s="8"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
-      <c r="A14" s="25"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -2553,8 +2553,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>304</v>
+      <c r="A2" s="42" t="s">
+        <v>282</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2565,141 +2565,141 @@
     </row>
     <row r="3">
       <c r="A3" s="44"/>
-      <c r="B3" s="17" t="s">
-        <v>312</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>316</v>
+      <c r="B3" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>293</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
       <c r="A4" s="8"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6" ht="99.0" customHeight="1">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="D7" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>322</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="F7" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="G5" s="14" t="s">
+      <c r="G7" s="14" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="6" ht="99.0" customHeight="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F7" s="14" t="s">
+    <row r="8" ht="96.0" customHeight="1">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="B9" s="16" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="8" ht="96.0" customHeight="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="D9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="F9" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="G9" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="G9" s="14" t="s">
-        <v>339</v>
-      </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>341</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>342</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>343</v>
       </c>
       <c r="E11" s="8"/>
@@ -2707,10 +2707,10 @@
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -2765,7 +2765,7 @@
       <c r="T1" s="7"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="15" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3"/>
@@ -2789,13 +2789,13 @@
       <c r="T2" s="7"/>
     </row>
     <row r="3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="18">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="21">
         <v>46054.0</v>
       </c>
       <c r="H3" s="7"/>
@@ -2813,13 +2813,13 @@
       <c r="T3" s="7"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="20"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="13"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -2835,25 +2835,25 @@
       <c r="T4" s="7"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="28">
+      <c r="A5" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="27">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="27">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="27">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="27">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="18">
+      <c r="F5" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="21">
         <v>46061.0</v>
       </c>
       <c r="H5" s="7"/>
@@ -2871,18 +2871,18 @@
       <c r="T5" s="7"/>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>46</v>
+      <c r="G6" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -2899,25 +2899,25 @@
       <c r="T6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="28">
+      <c r="A7" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="27">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="27">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="27">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="27">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="18">
+      <c r="F7" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="21">
         <v>46068.0</v>
       </c>
       <c r="H7" s="7"/>
@@ -2935,22 +2935,22 @@
       <c r="T7" s="7"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="20" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="20" t="s">
+      <c r="F8" s="18"/>
+      <c r="G8" s="32" t="s">
         <v>58</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="37" t="s">
-        <v>62</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -2967,25 +2967,25 @@
       <c r="T8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="28">
+      <c r="A9" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="27">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="27">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="27">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" s="18">
+      <c r="F9" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="21">
         <v>46075.0</v>
       </c>
       <c r="H9" s="7"/>
@@ -3003,18 +3003,18 @@
       <c r="T9" s="7"/>
     </row>
     <row r="10" ht="89.25" customHeight="1">
-      <c r="A10" s="20"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>78</v>
+      <c r="A10" s="13"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -3031,25 +3031,25 @@
       <c r="T10" s="7"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="28">
+      <c r="A11" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="27">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="27">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="27">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="27">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="16"/>
+      <c r="F11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="18"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
@@ -3065,15 +3065,15 @@
       <c r="T11" s="7"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
@@ -24386,7 +24386,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="3"/>
@@ -24397,8 +24397,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="13" t="s">
-        <v>5</v>
+      <c r="A2" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -24425,13 +24425,13 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="20" t="s">
-        <v>10</v>
+      <c r="G4" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>14</v>
+      <c r="A5" s="16" t="s">
+        <v>7</v>
       </c>
       <c r="B5" s="12">
         <v>46084.0</v>
@@ -24446,7 +24446,7 @@
         <v>46087.0</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G5" s="10">
         <v>46089.0</v>
@@ -24454,22 +24454,22 @@
     </row>
     <row r="6" ht="113.25" customHeight="1">
       <c r="A6" s="8"/>
-      <c r="B6" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="30"/>
+      <c r="B6" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>36</v>
+      <c r="A7" s="16" t="s">
+        <v>18</v>
       </c>
       <c r="B7" s="12">
         <v>46091.0</v>
@@ -24484,7 +24484,7 @@
         <v>46094.0</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G7" s="10">
         <v>46096.0</v>
@@ -24492,24 +24492,24 @@
     </row>
     <row r="8" ht="87.0" customHeight="1">
       <c r="A8" s="8"/>
-      <c r="B8" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>42</v>
+      <c r="B8" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="20" t="s">
-        <v>45</v>
+      <c r="F8" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="G8" s="8"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>48</v>
+      <c r="A9" s="16" t="s">
+        <v>24</v>
       </c>
       <c r="B9" s="12">
         <v>46098.0</v>
@@ -24517,33 +24517,33 @@
       <c r="C9" s="10">
         <v>46099.0</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="23">
         <v>46100.0</v>
       </c>
       <c r="E9" s="12">
         <v>46101.0</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G9" s="10">
         <v>46103.0</v>
       </c>
     </row>
     <row r="10" ht="96.0" customHeight="1">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="36" t="s">
-        <v>54</v>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="30" t="s">
+        <v>35</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>64</v>
+      <c r="A11" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B11" s="12">
         <v>46105.0</v>
@@ -24558,7 +24558,7 @@
         <v>46108.0</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G11" s="10">
         <v>46110.0</v>
@@ -24566,24 +24566,24 @@
     </row>
     <row r="12" ht="91.5" customHeight="1">
       <c r="A12" s="8"/>
-      <c r="B12" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="B12" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>76</v>
+      <c r="A13" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="B13" s="12">
         <v>46112.0</v>
@@ -24630,7 +24630,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
@@ -24641,8 +24641,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>3</v>
+      <c r="A2" s="17" t="s">
+        <v>8</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -24664,7 +24664,7 @@
         <v>46115.0</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G3" s="10">
         <v>46117.0</v>
@@ -24676,12 +24676,12 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
-      <c r="F4" s="20"/>
+      <c r="F4" s="13"/>
       <c r="G4" s="8"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>17</v>
+      <c r="A5" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="B5" s="12">
         <v>46119.0</v>
@@ -24696,7 +24696,7 @@
         <v>46122.0</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="G5" s="10">
         <v>46124.0</v>
@@ -24706,25 +24706,25 @@
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
-      <c r="D6" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="26" t="s">
-        <v>33</v>
+      <c r="D6" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="34" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>35</v>
+      <c r="A7" s="16" t="s">
+        <v>70</v>
       </c>
       <c r="B7" s="12">
         <v>46126.0</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="23">
         <v>46127.0</v>
       </c>
       <c r="D7" s="12">
@@ -24734,30 +24734,30 @@
         <v>46129.0</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="G7" s="10">
         <v>46131.0</v>
       </c>
     </row>
     <row r="8" ht="80.25" customHeight="1">
-      <c r="A8" s="32"/>
-      <c r="B8" s="33"/>
+      <c r="A8" s="36"/>
+      <c r="B8" s="37"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="26" t="s">
-        <v>59</v>
+      <c r="D8" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="34" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>61</v>
+      <c r="A9" s="16" t="s">
+        <v>77</v>
       </c>
       <c r="B9" s="12">
         <v>46133.0</v>
@@ -24772,7 +24772,7 @@
         <v>46136.0</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G9" s="10">
         <v>46138.0</v>
@@ -24782,16 +24782,16 @@
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="26" t="s">
-        <v>66</v>
+      <c r="D10" s="34" t="s">
+        <v>79</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>70</v>
+      <c r="A11" s="16" t="s">
+        <v>80</v>
       </c>
       <c r="B11" s="12">
         <v>46140.0</v>
@@ -24811,7 +24811,7 @@
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="39" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
@@ -24857,8 +24857,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>82</v>
+      <c r="A2" s="43" t="s">
+        <v>84</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -24873,13 +24873,13 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="14" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
@@ -24888,185 +24888,185 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="26" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="F4" s="47"/>
+      <c r="G4" s="34" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>101</v>
+      <c r="A5" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>115</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="26" t="s">
-        <v>105</v>
+      <c r="C6" s="34" t="s">
+        <v>118</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="47" t="s">
-        <v>107</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="46"/>
+      <c r="E6" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" s="47"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>119</v>
+      <c r="A7" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>130</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="20"/>
-      <c r="B8" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>137</v>
+      <c r="A8" s="13"/>
+      <c r="B8" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>139</v>
+      <c r="A9" s="16" t="s">
+        <v>155</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>144</v>
+        <v>157</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>163</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="26" t="s">
-        <v>150</v>
+      <c r="A10" s="34" t="s">
+        <v>171</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>164</v>
+        <v>97</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="55" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>181</v>
+      <c r="A11" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>189</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="G12" s="54" t="s">
-        <v>164</v>
+      <c r="A12" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="55" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -25096,7 +25096,7 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -25106,8 +25106,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>85</v>
+      <c r="A2" s="42" t="s">
+        <v>83</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -25117,183 +25117,183 @@
       <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="F3" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="G3" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="14" t="s">
+    </row>
+    <row r="4" ht="91.5" customHeight="1">
+      <c r="A4" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="26" t="s">
+      <c r="C4" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="20" t="s">
+      <c r="D5" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="G5" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" ht="183.75" customHeight="1">
+      <c r="A6" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" ht="183.75" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="G6" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="50" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="29" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="C7" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G7" s="14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" ht="101.25" customHeight="1">
+      <c r="A8" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="53" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B7" s="17" t="s">
+      <c r="C8" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" s="17" t="s">
+      <c r="F8" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="G8" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="G7" s="14" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="8" ht="101.25" customHeight="1">
-      <c r="A8" s="52" t="s">
-        <v>161</v>
-      </c>
-      <c r="B8" s="52" t="s">
+      <c r="B9" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C8" s="52" t="s">
-        <v>163</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="F8" s="52" t="s">
+      <c r="E9" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="G9" s="14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" ht="99.75" customHeight="1">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" ht="99.75" customHeight="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>194</v>
+      <c r="B11" s="16" t="s">
+        <v>181</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -25302,13 +25302,13 @@
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25347,8 +25347,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>114</v>
+      <c r="A2" s="42" t="s">
+        <v>106</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -25370,7 +25370,7 @@
         <v>46206.0</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G3" s="10">
         <v>46208.0</v>
@@ -25379,20 +25379,20 @@
     <row r="4" ht="91.5" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="20"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" s="13"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>160</v>
+      <c r="A5" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>167</v>
       </c>
       <c r="C5" s="12">
         <v>46211.0</v>
@@ -25404,39 +25404,39 @@
         <v>46213.0</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G5" s="10">
         <v>46215.0</v>
       </c>
     </row>
     <row r="6" ht="92.25" customHeight="1">
-      <c r="A6" s="55" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="52" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="F6" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>187</v>
+      <c r="A6" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="A7" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="23">
         <v>46218.0</v>
       </c>
       <c r="D7" s="12">
@@ -25446,28 +25446,28 @@
         <v>46220.0</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G7" s="56">
         <v>46222.0</v>
       </c>
     </row>
     <row r="8" ht="88.5" customHeight="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="G8" s="25"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="19"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>196</v>
       </c>
       <c r="C9" s="12">
@@ -25487,23 +25487,23 @@
       </c>
     </row>
     <row r="10" ht="77.25" customHeight="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="49" t="s">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="50" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>201</v>
       </c>
       <c r="C11" s="12">
@@ -25512,18 +25512,18 @@
       <c r="D11" s="12">
         <v>46233.0</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>202</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="37"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="32"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
     </row>
@@ -25564,8 +25564,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>203</v>
+      <c r="A2" s="42" t="s">
+        <v>204</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -25581,7 +25581,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G3" s="10">
         <v>46236.0</v>
@@ -25593,17 +25593,17 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
-      <c r="F4" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="25"/>
+      <c r="F4" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" s="19"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>206</v>
+      <c r="A5" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>211</v>
       </c>
       <c r="C5" s="12">
         <v>46239.0</v>
@@ -25615,29 +25615,29 @@
         <v>46241.0</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="G5" s="10">
         <v>46243.0</v>
       </c>
     </row>
     <row r="6" ht="84.0" customHeight="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="G6" s="25"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" s="19"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>211</v>
+      <c r="A7" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>217</v>
       </c>
       <c r="C7" s="12">
         <v>46246.0</v>
@@ -25649,29 +25649,29 @@
         <v>46248.0</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G7" s="10">
         <v>46250.0</v>
       </c>
     </row>
     <row r="8" ht="93.75" customHeight="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="G8" s="25"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="19"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>215</v>
+      <c r="A9" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>224</v>
       </c>
       <c r="C9" s="12">
         <v>46253.0</v>
@@ -25683,35 +25683,35 @@
         <v>46255.0</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="G9" s="10">
         <v>46257.0</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>219</v>
+      <c r="A10" s="19"/>
+      <c r="B10" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>221</v>
+      <c r="A11" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>237</v>
       </c>
       <c r="C11" s="12">
         <v>46260.0</v>
@@ -25723,32 +25723,32 @@
         <v>46262.0</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="G11" s="10">
         <v>46264.0</v>
       </c>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="E12" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="G12" s="25"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="G12" s="19"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>227</v>
+      <c r="A13" s="16" t="s">
+        <v>245</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -25758,7 +25758,7 @@
       <c r="G13" s="8"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
-      <c r="A14" s="25"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -25803,8 +25803,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>208</v>
+      <c r="A2" s="42" t="s">
+        <v>203</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -25815,8 +25815,8 @@
     </row>
     <row r="3">
       <c r="A3" s="8"/>
-      <c r="B3" s="17" t="s">
-        <v>213</v>
+      <c r="B3" s="16" t="s">
+        <v>205</v>
       </c>
       <c r="C3" s="12">
         <v>46267.0</v>
@@ -25828,7 +25828,7 @@
         <v>46269.0</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="G3" s="10">
         <v>46271.0</v>
@@ -25836,57 +25836,57 @@
     </row>
     <row r="4" ht="85.5" customHeight="1">
       <c r="A4" s="8"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="59" t="s">
-        <v>222</v>
-      </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" s="60" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" s="62">
+      <c r="A5" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="60">
         <v>46274.0</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="61">
         <v>46275.0</v>
       </c>
       <c r="E5" s="12">
         <v>46276.0</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="G5" s="10">
         <v>46278.0</v>
       </c>
     </row>
     <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
+      <c r="A6" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="B7" s="60" t="s">
-        <v>237</v>
-      </c>
-      <c r="C7" s="62">
+      <c r="A7" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="60">
         <v>46281.0</v>
       </c>
       <c r="D7" s="12">
@@ -25896,33 +25896,33 @@
         <v>46283.0</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="G7" s="10">
         <v>46285.0</v>
       </c>
     </row>
     <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="A8" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>251</v>
+      <c r="A9" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="C9" s="12">
         <v>46288.0</v>
@@ -25934,35 +25934,35 @@
         <v>46290.0</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="G9" s="10">
         <v>46292.0</v>
       </c>
     </row>
     <row r="10" ht="98.25" customHeight="1">
-      <c r="A10" s="59" t="s">
-        <v>254</v>
-      </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="59" t="s">
-        <v>255</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>257</v>
+      <c r="A10" s="58" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="58" t="s">
+        <v>235</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>261</v>
+      <c r="A11" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>242</v>
       </c>
       <c r="C11" s="12">
         <v>46295.0</v>
@@ -25973,9 +25973,9 @@
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -30,7 +30,7 @@
     <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
   </si>
   <si>
-    <t xml:space="preserve">MART </t>
+    <t>OCAK</t>
   </si>
   <si>
     <r>
@@ -52,16 +52,10 @@
     </r>
   </si>
   <si>
-    <t>OCAK</t>
-  </si>
-  <si>
     <t xml:space="preserve">NİSAN </t>
   </si>
   <si>
-    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
+    <t xml:space="preserve">MART </t>
   </si>
   <si>
     <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
@@ -70,53 +64,13 @@
     <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
-  </si>
-  <si>
     <t>5 Ocak 2026 Pazartesi</t>
   </si>
   <si>
-    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>*18 Mart Şehitleri Anma Günü Provası 
-*16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
-  </si>
-  <si>
     <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
-  </si>
-  <si>
-    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
   </si>
   <si>
     <t>Çeşme Belediyesi Türk Halk Müziği Korosu “ Çeşme’den Türkü Akıyor” 2026 Kış Konseri
@@ -125,76 +79,164 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
+    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Ot Festivali ile ilgili toplantı 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
+  </si>
+  <si>
+    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
     <t>CHP Eğitim 17.00-20.00</t>
   </si>
   <si>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+  </si>
+  <si>
+    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+  </si>
+  <si>
     <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
   </si>
   <si>
-    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
+    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+  </si>
+  <si>
+    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
+  </si>
+  <si>
+    <t>*18 Mart Şehitleri Anma Günü Provası 
+*16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
   </si>
   <si>
     <t>13 Nisan 2026 Pazartesi</t>
   </si>
   <si>
-    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
-  </si>
-  <si>
-    <t>RAMAZAN BAYRAMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+    <t>YARI YIL ETKİNLİKLERİ</t>
+  </si>
+  <si>
+    <t>Belediye TSM Konseri Tüm gün</t>
+  </si>
+  <si>
+    <t>19 Ocak 2026 Pazartesi</t>
   </si>
   <si>
     <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t>Ot Festivali ile ilgili toplantı 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
-  </si>
-  <si>
-    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>31 Ocak 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
+  </si>
+  <si>
+    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
   </si>
   <si>
     <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
-    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim tüm gün</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
+  </si>
+  <si>
+    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
+  </si>
+  <si>
+    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>28 Şubat 2026 Cumartesi</t>
   </si>
   <si>
     <r>
@@ -214,133 +256,236 @@
     </r>
   </si>
   <si>
-    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+    <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>RAMAZAN BAYRAMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim tüm gün</t>
   </si>
   <si>
     <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
   </si>
   <si>
-    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
-  </si>
-  <si>
-    <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>YARI YIL ETKİNLİKLERİ</t>
   </si>
   <si>
     <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
 -Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
   </si>
   <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>19 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
     <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
-  </si>
-  <si>
-    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
-  </si>
-  <si>
-    <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>28 Şubat 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
-  </si>
-  <si>
-    <t>31 Ocak 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
-  </si>
-  <si>
-    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
+    <t>MAYIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>3 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
+  </si>
+  <si>
+    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>10 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
+  </si>
+  <si>
+    <t>21.30 konser provası Başkan ile</t>
+  </si>
+  <si>
+    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
+  </si>
+  <si>
+    <t>11 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>16 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t>Bilgiç Anaokulu Prova 
+10.30-15.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilgiç Anaokulu Prova 
+10.30-15.30                                               </t>
+  </si>
+  <si>
+    <t>-Bilgiç ortaokulu 09.00-12.00
+-Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
+  </si>
+  <si>
+    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
+"No Mans Land" Yetişkin Oyunu 20.00
+onaylandı.</t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
+  </si>
+  <si>
+    <t>18 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>23 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t>24 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro</t>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
+    </r>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
+  </si>
+  <si>
+    <t>BAYRAM</t>
   </si>
   <si>
     <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
   <si>
-    <t>MAYIS</t>
+    <t>25 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
   </si>
   <si>
     <t xml:space="preserve">HAZİRAN </t>
   </si>
   <si>
-    <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>3 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">TEMMUZ </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
   </si>
   <si>
-    <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
-  </si>
-  <si>
     <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
@@ -350,28 +495,7 @@
     <t>7 HAZİRAN 2026 PAZAR</t>
   </si>
   <si>
-    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
   </si>
   <si>
     <r>
@@ -391,9 +515,6 @@
     </r>
   </si>
   <si>
-    <t>10 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -411,35 +532,19 @@
     </r>
   </si>
   <si>
-    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
-  </si>
-  <si>
     <t>Bilgiç İlkokulu 13.00 1. Sınıf Okuma Bayramı 18.00
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
   </si>
   <si>
-    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>21.30 konser provası Başkan ile</t>
-  </si>
-  <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
   </si>
   <si>
     <t xml:space="preserve">8 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
-  </si>
-  <si>
     <t xml:space="preserve">9 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t>Latin Katolik Kilisesi Ayin 
-18.30</t>
-  </si>
-  <si>
     <t xml:space="preserve">10 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
@@ -449,46 +554,19 @@
     <t xml:space="preserve">12 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
-    <t>11 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
     <t>13 HAZİRAN 2026 CUMARTESİ</t>
   </si>
   <si>
-    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">14 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
-    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t>16 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00</t>
   </si>
   <si>
-    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00                                                        "SEVGİLİ DOKTOR"  20.00</t>
   </si>
   <si>
-    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
+    <t xml:space="preserve">TEMMUZ </t>
   </si>
   <si>
     <r>
@@ -509,35 +587,83 @@
     </r>
   </si>
   <si>
-    <t>Bilgiç Anaokulu Prova 
-10.30-15.30</t>
-  </si>
-  <si>
     <t>-SERTUR KOOPERATİF TOPLANTISI HALUK BEY 05336460236 
 15.00'a kadar
 - Kent Enstitüsü Prova</t>
   </si>
   <si>
-    <t xml:space="preserve">Bilgiç Anaokulu Prova 
-10.30-15.30                                               </t>
+    <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
+  </si>
+  <si>
+    <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Atatürk Lisesi tiyatro prova</t>
+  </si>
+  <si>
+    <t>Atatürk Lisesi Oyun Günü</t>
+  </si>
+  <si>
+    <t>Osman Uysal Prova opsiyon</t>
+  </si>
+  <si>
+    <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
+sabahtan 21.00'a kadar</t>
+  </si>
+  <si>
+    <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
+  </si>
+  <si>
+    <t>Namık Kemal Okuma Bayramı</t>
+  </si>
+  <si>
+    <t>Doğu Der Toplantı</t>
+  </si>
+  <si>
+    <t>Latin Katolik Kilisesi Ayin 
+18.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t>-Bilgiç ortaokulu 09.00-12.00
--Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
-  </si>
-  <si>
-    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
-"No Mans Land" Yetişkin Oyunu 20.00
-onaylandı.</t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
-  </si>
-  <si>
-    <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
+    <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t>-Çoklu İklim Krizinin Gölgesinde Orman Yangınları
@@ -545,179 +671,53 @@
 -Belediye Meclisi 17.00'dan sonra</t>
   </si>
   <si>
-    <t>18 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t>23 MAYIS 2026 CUMARTESİ</t>
+    <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
     <t>Belediye meclisi 16.00'dan sonra</t>
   </si>
   <si>
-    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t>24 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
   </si>
   <si>
-    <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
-  </si>
-  <si>
     <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
-    </r>
-  </si>
-  <si>
-    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
-  </si>
-  <si>
-    <t>Atatürk Lisesi tiyatro prova</t>
-  </si>
-  <si>
     <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t>BAYRAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t>Atatürk Lisesi Oyun Günü</t>
-  </si>
-  <si>
-    <t>Osman Uysal Prova opsiyon</t>
-  </si>
-  <si>
-    <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
-sabahtan 21.00'a kadar</t>
-  </si>
-  <si>
-    <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
-  </si>
-  <si>
-    <t>25 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t>Namık Kemal Okuma Bayramı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t>Doğu Der Toplantı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
     <t>Reyhan Cici Piyano Dinletisi
 Ödendi. Dilekçe geldi. Tel no:5320631925 12.00-20.00</t>
   </si>
   <si>
+    <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
     <t>MHP 15. Olağan Kongre Toplantısı</t>
   </si>
   <si>
+    <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">21 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">25 TEMMUZ 2026 CUMARTESİ </t>
@@ -771,9 +771,6 @@
     <t xml:space="preserve">15 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">EYLÜL </t>
-  </si>
-  <si>
     <t xml:space="preserve">17 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -786,9 +783,6 @@
     <t xml:space="preserve">Ritim 10.00-12.00 </t>
   </si>
   <si>
-    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
     <t>Deniz Tatil Sitesi Toplantı 11.00-18.00</t>
   </si>
   <si>
@@ -799,9 +793,6 @@
   </si>
   <si>
     <t xml:space="preserve">29 AĞUSTOS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">DORUK BELDESİ, ARSA VE YAPI KOOPERATİFİ                                 13.00-15.00  </t>
@@ -813,6 +804,15 @@
   </si>
   <si>
     <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EYLÜL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
@@ -1224,6 +1224,7 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font/>
     <font>
       <b/>
       <sz val="14.0"/>
@@ -1231,21 +1232,7 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font/>
     <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1259,7 +1246,20 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1269,13 +1269,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF38761D"/>
+      <color rgb="FFEFEFEF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFEFEFEF"/>
+      <b/>
+      <color rgb="FF38761D"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1319,8 +1319,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE69138"/>
-        <bgColor rgb="FFE69138"/>
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor rgb="FFF9CB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -1331,8 +1331,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9CB9C"/>
-        <bgColor rgb="FFF9CB9C"/>
+        <fgColor rgb="FFE69138"/>
+        <bgColor rgb="FFE69138"/>
       </patternFill>
     </fill>
     <fill>
@@ -1343,14 +1343,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -1432,93 +1432,96 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1526,31 +1529,25 @@
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1560,9 +1557,6 @@
     <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1570,13 +1564,22 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1584,10 +1587,7 @@
     <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1608,7 +1608,7 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1887,212 +1887,212 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="13">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="12">
         <v>46023.0</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="14">
         <v>46024.0</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="12">
+        <v>46026.0</v>
+      </c>
+    </row>
+    <row r="4" ht="95.25" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="13">
-        <v>46026.0</v>
-      </c>
-    </row>
-    <row r="4" ht="95.25" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="17">
+      <c r="B5" s="14">
         <v>46028.0</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="14">
         <v>46029.0</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="14">
         <v>46030.0</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <v>46031.0</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
         <v>46033.0</v>
       </c>
     </row>
     <row r="6" ht="97.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="28" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="18.0" customHeight="1">
+      <c r="A7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="14">
+        <v>46035.0</v>
+      </c>
+      <c r="C7" s="25">
+        <v>46036.0</v>
+      </c>
+      <c r="D7" s="25">
+        <v>46037.0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>46038.0</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="27">
+        <v>46040.0</v>
+      </c>
+    </row>
+    <row r="8" ht="69.0" customHeight="1">
+      <c r="A8" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="17">
-        <v>46035.0</v>
-      </c>
-      <c r="C7" s="27">
-        <v>46036.0</v>
-      </c>
-      <c r="D7" s="27">
-        <v>46037.0</v>
-      </c>
-      <c r="E7" s="17">
-        <v>46038.0</v>
-      </c>
-      <c r="F7" s="19" t="s">
+      <c r="E8" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="32">
-        <v>46040.0</v>
-      </c>
-    </row>
-    <row r="8" ht="69.0" customHeight="1">
-      <c r="A8" s="16" t="s">
+      <c r="F8" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="G8" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="16" t="s">
+      <c r="B9" s="14">
+        <v>46042.0</v>
+      </c>
+      <c r="C9" s="25">
+        <v>46043.0</v>
+      </c>
+      <c r="D9" s="25">
+        <v>46044.0</v>
+      </c>
+      <c r="E9" s="14">
+        <v>46045.0</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="12">
+        <v>46047.0</v>
+      </c>
+    </row>
+    <row r="10" ht="78.75" customHeight="1">
+      <c r="A10" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="28"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="14">
+        <v>46049.0</v>
+      </c>
+      <c r="C11" s="25">
+        <v>46050.0</v>
+      </c>
+      <c r="D11" s="25">
+        <v>46051.0</v>
+      </c>
+      <c r="E11" s="14">
+        <v>46052.0</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="17">
-        <v>46042.0</v>
-      </c>
-      <c r="C9" s="27">
-        <v>46043.0</v>
-      </c>
-      <c r="D9" s="27">
-        <v>46044.0</v>
-      </c>
-      <c r="E9" s="17">
-        <v>46045.0</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="13">
-        <v>46047.0</v>
-      </c>
-    </row>
-    <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="21"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="17">
-        <v>46049.0</v>
-      </c>
-      <c r="C11" s="27">
-        <v>46050.0</v>
-      </c>
-      <c r="D11" s="27">
-        <v>46051.0</v>
-      </c>
-      <c r="E11" s="17">
-        <v>46052.0</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="10"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="40"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2123,183 +2123,183 @@
       <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="63" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="18" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="17" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="4" ht="84.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="50" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="49" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="17" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
       <c r="C6" s="64" t="s">
         <v>259</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="64" t="s">
         <v>259</v>
       </c>
-      <c r="G6" s="21"/>
+      <c r="G6" s="28"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="17" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="10" ht="100.5" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="G11" s="10"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2328,193 +2328,193 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="18" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="20" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="21"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="28"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="17" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="17" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="17" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="65" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
-      <c r="A14" s="21"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2545,175 +2545,175 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="17" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="17" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>329</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="17" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2741,15 +2741,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="63.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -2765,15 +2765,15 @@
       <c r="T1" s="6"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -2789,13 +2789,13 @@
       <c r="T2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="15">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="16">
         <v>46054.0</v>
       </c>
       <c r="H3" s="6"/>
@@ -2813,13 +2813,13 @@
       <c r="T3" s="6"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="16"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
@@ -2835,25 +2835,25 @@
       <c r="T4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="25">
+      <c r="A5" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="22">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="22">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="22">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="22">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="15">
+      <c r="F5" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="16">
         <v>46061.0</v>
       </c>
       <c r="H5" s="6"/>
@@ -2871,18 +2871,18 @@
       <c r="T5" s="6"/>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>39</v>
+      <c r="A6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>24</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -2899,25 +2899,25 @@
       <c r="T6" s="6"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="25">
+      <c r="A7" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="22">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="22">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="22">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="22">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="15">
+      <c r="F7" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="16">
         <v>46068.0</v>
       </c>
       <c r="H7" s="6"/>
@@ -2935,22 +2935,22 @@
       <c r="T7" s="6"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="12"/>
-      <c r="B8" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="36" t="s">
-        <v>62</v>
+      <c r="A8" s="13"/>
+      <c r="B8" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="31" t="s">
+        <v>43</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -2967,25 +2967,25 @@
       <c r="T8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="25">
+      <c r="A9" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="22">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="22">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="22">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="22">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="15">
+      <c r="F9" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="16">
         <v>46075.0</v>
       </c>
       <c r="H9" s="6"/>
@@ -3003,18 +3003,18 @@
       <c r="T9" s="6"/>
     </row>
     <row r="10" ht="89.25" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>73</v>
+      <c r="A10" s="19"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -3031,25 +3031,25 @@
       <c r="T10" s="6"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="25">
+      <c r="A11" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="22">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="22">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="22">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="22">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="12"/>
+      <c r="F11" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="13"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
@@ -3065,15 +3065,15 @@
       <c r="T11" s="6"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
@@ -24386,222 +24386,222 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="13">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="12">
         <v>46082.0</v>
       </c>
     </row>
     <row r="4" ht="69.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="16" t="s">
-        <v>6</v>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="19" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="17">
+      <c r="A5" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="14">
         <v>46084.0</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="14">
         <v>46085.0</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="14">
         <v>46086.0</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <v>46087.0</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="12">
         <v>46089.0</v>
       </c>
     </row>
     <row r="6" ht="113.25" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="22"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="17">
+      <c r="A7" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="14">
         <v>46091.0</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="14">
         <v>46092.0</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="14">
         <v>46093.0</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="14">
         <v>46094.0</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="12">
         <v>46096.0</v>
       </c>
     </row>
     <row r="8" ht="87.0" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="10"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="17">
+      <c r="A9" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="14">
         <v>46098.0</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="12">
         <v>46099.0</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="25">
         <v>46100.0</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="14">
         <v>46101.0</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="12">
         <v>46103.0</v>
       </c>
     </row>
     <row r="10" ht="96.0" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="5"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="17">
+      <c r="A11" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="14">
         <v>46105.0</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="14">
         <v>46106.0</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="14">
         <v>46107.0</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="14">
         <v>46108.0</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="13">
+      <c r="F11" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="12">
         <v>46110.0</v>
       </c>
     </row>
     <row r="12" ht="91.5" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="17">
+      <c r="A13" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="14">
         <v>46112.0</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" ht="95.25" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -24630,192 +24630,192 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="17">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="14">
         <v>46113.0</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="14">
         <v>46114.0</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="14">
         <v>46115.0</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="12">
         <v>46117.0</v>
       </c>
     </row>
     <row r="4" ht="99.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="10"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="17">
+      <c r="A5" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="14">
         <v>46119.0</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="14">
         <v>46120.0</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="14">
         <v>46121.0</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <v>46122.0</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>46124.0</v>
       </c>
     </row>
     <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="24" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="29" t="s">
         <v>28</v>
       </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="26" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="17">
+      <c r="A7" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="14">
         <v>46126.0</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="25">
         <v>46127.0</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="14">
         <v>46128.0</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="14">
         <v>46129.0</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="12">
         <v>46131.0</v>
       </c>
     </row>
     <row r="8" ht="80.25" customHeight="1">
-      <c r="A8" s="31"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="24" t="s">
-        <v>56</v>
+      <c r="A8" s="33"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="26" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="17">
+      <c r="A9" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="14">
         <v>46133.0</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="14">
         <v>46134.0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>46135.0</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="14">
         <v>46136.0</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="12">
         <v>46138.0</v>
       </c>
     </row>
     <row r="10" ht="92.25" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="17">
+      <c r="A11" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="14">
         <v>46140.0</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="14">
         <v>46141.0</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="14">
         <v>46142.0</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13">
       <c r="D13" s="39"/>
@@ -24849,224 +24849,224 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="19" t="s">
+    </row>
+    <row r="4" ht="94.5" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="F4" s="45"/>
+      <c r="G4" s="26" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="45" t="s">
+    <row r="5" ht="20.25" customHeight="1">
+      <c r="A5" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="24" t="s">
+      <c r="G5" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" ht="91.5" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="47" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="18" t="s">
+      <c r="G6" s="45"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B7" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="G5" s="19" t="s">
+    </row>
+    <row r="8" ht="97.5" customHeight="1">
+      <c r="A8" s="19"/>
+      <c r="B8" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="49" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="24" t="s">
+      <c r="D8" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="48" t="s">
+      <c r="F8" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="F6" s="49" t="s">
+      <c r="B9" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="46"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="E9" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" ht="93.75" customHeight="1">
+      <c r="A10" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="E10" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="G10" s="50" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="C11" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="D11" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="E11" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="17" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="52" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="F10" s="55" t="s">
-        <v>168</v>
-      </c>
-      <c r="G10" s="55" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>186</v>
+      <c r="G11" s="17" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="55" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>168</v>
-      </c>
-      <c r="C12" s="55" t="s">
-        <v>168</v>
-      </c>
-      <c r="D12" s="55" t="s">
-        <v>168</v>
-      </c>
-      <c r="E12" s="55" t="s">
-        <v>168</v>
-      </c>
-      <c r="F12" s="55" t="s">
-        <v>168</v>
-      </c>
-      <c r="G12" s="55" t="s">
-        <v>168</v>
+      <c r="A12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -25096,219 +25096,219 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+        <v>123</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>96</v>
+      <c r="A3" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>27</v>
+      <c r="A4" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>28</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="16"/>
+        <v>143</v>
+      </c>
+      <c r="G4" s="19"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>123</v>
+      <c r="A5" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="6" ht="183.75" customHeight="1">
-      <c r="A6" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>146</v>
+      <c r="A6" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="18" t="s">
+      <c r="A7" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="C7" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="E7" s="20" t="s">
         <v>162</v>
       </c>
+      <c r="F7" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="8" ht="101.25" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="F8" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="G8" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="F8" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="G8" s="24" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="B9" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="E9" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="F9" s="19" t="s">
+      <c r="G9" s="17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" ht="99.75" customHeight="1">
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="G9" s="19" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" ht="99.75" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="24" t="s">
+      <c r="G10" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="G10" s="24" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="B11" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25339,193 +25339,193 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="17">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="14">
         <v>46204.0</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="14">
         <v>46205.0</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="14">
         <v>46206.0</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="G3" s="12">
         <v>46208.0</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="16"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" s="19"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="17">
+      <c r="A5" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="14">
         <v>46211.0</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="14">
         <v>46212.0</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <v>46213.0</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" s="12">
         <v>46215.0</v>
       </c>
     </row>
     <row r="6" ht="92.25" customHeight="1">
-      <c r="A6" s="54" t="s">
-        <v>143</v>
-      </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="F6" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>163</v>
+      <c r="A6" s="55" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="27">
+      <c r="A7" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="25">
         <v>46218.0</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="14">
         <v>46219.0</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="14">
         <v>46220.0</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>179</v>
+      <c r="F7" s="17" t="s">
+        <v>193</v>
       </c>
       <c r="G7" s="56">
         <v>46222.0</v>
       </c>
     </row>
     <row r="8" ht="88.5" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="21"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" s="28"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="C9" s="17">
+      <c r="A9" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="14">
         <v>46225.0</v>
       </c>
       <c r="D9" s="57">
         <v>46226.0</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="14">
         <v>46227.0</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>46229.0</v>
       </c>
     </row>
     <row r="10" ht="77.25" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="49" t="s">
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="47" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="14">
         <v>46232.0</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="14">
         <v>46233.0</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25556,215 +25556,215 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="19" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>46236.0</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="21"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" s="28"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="14">
         <v>46239.0</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="14">
         <v>46240.0</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <v>46241.0</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>46243.0</v>
       </c>
     </row>
     <row r="6" ht="84.0" customHeight="1">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="24" t="s">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="G6" s="21"/>
+      <c r="G6" s="28"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="14">
         <v>46246.0</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="14">
         <v>46247.0</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="14">
         <v>46248.0</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>46250.0</v>
       </c>
     </row>
     <row r="8" ht="93.75" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="21"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" s="28"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="C9" s="14">
+        <v>46253.0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>46254.0</v>
+      </c>
+      <c r="E9" s="14">
+        <v>46255.0</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="C9" s="17">
-        <v>46253.0</v>
-      </c>
-      <c r="D9" s="17">
-        <v>46254.0</v>
-      </c>
-      <c r="E9" s="17">
-        <v>46255.0</v>
-      </c>
-      <c r="F9" s="19" t="s">
+      <c r="G9" s="12">
+        <v>46257.0</v>
+      </c>
+    </row>
+    <row r="10" ht="93.75" customHeight="1">
+      <c r="A10" s="28"/>
+      <c r="B10" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="G9" s="13">
-        <v>46257.0</v>
-      </c>
-    </row>
-    <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="50" t="s">
+      <c r="C10" s="36"/>
+      <c r="D10" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10" s="28"/>
+      <c r="F10" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="50" t="s">
-        <v>216</v>
-      </c>
-      <c r="E10" s="21"/>
-      <c r="F10" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="G10" s="24" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="C11" s="14">
+        <v>46260.0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>46261.0</v>
+      </c>
+      <c r="E11" s="14">
+        <v>46262.0</v>
+      </c>
+      <c r="F11" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="G11" s="12">
+        <v>46264.0</v>
+      </c>
+    </row>
+    <row r="12" ht="94.5" customHeight="1">
+      <c r="A12" s="28"/>
+      <c r="B12" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="C11" s="17">
-        <v>46260.0</v>
-      </c>
-      <c r="D11" s="17">
-        <v>46261.0</v>
-      </c>
-      <c r="E11" s="17">
-        <v>46262.0</v>
-      </c>
-      <c r="F11" s="19" t="s">
+      <c r="E12" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="G11" s="13">
-        <v>46264.0</v>
-      </c>
-    </row>
-    <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="50" t="s">
-        <v>216</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>216</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>224</v>
-      </c>
-      <c r="G12" s="21"/>
+      <c r="G12" s="28"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="A13" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
-      <c r="A14" s="21"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25795,58 +25795,58 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="C3" s="17">
+      <c r="A3" s="9"/>
+      <c r="B3" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="14">
         <v>46267.0</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="14">
         <v>46268.0</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="14">
         <v>46269.0</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="G3" s="12">
         <v>46271.0</v>
       </c>
     </row>
     <row r="4" ht="85.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
       <c r="E4" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>227</v>
       </c>
       <c r="B5" s="59" t="s">
@@ -25858,29 +25858,29 @@
       <c r="D5" s="61">
         <v>46275.0</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <v>46276.0</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>46278.0</v>
       </c>
     </row>
     <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>231</v>
       </c>
       <c r="B7" s="59" t="s">
@@ -25889,54 +25889,54 @@
       <c r="C7" s="60">
         <v>46281.0</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="14">
         <v>46282.0</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="14">
         <v>46283.0</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>46285.0</v>
       </c>
     </row>
     <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="14">
         <v>46288.0</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="14">
         <v>46289.0</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="14">
         <v>46290.0</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>46292.0</v>
       </c>
     </row>
@@ -25944,42 +25944,42 @@
       <c r="A10" s="58" t="s">
         <v>240</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="58" t="s">
         <v>241</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="26" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="14">
         <v>46295.0</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -30,13 +30,13 @@
     <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
   </si>
   <si>
+    <t xml:space="preserve">NİSAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MART </t>
+  </si>
+  <si>
     <t>OCAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NİSAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MART </t>
   </si>
   <si>
     <r>
@@ -58,13 +58,16 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
   </si>
   <si>
     <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
   </si>
   <si>
-    <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
+    <t>5 Ocak 2026 Pazartesi</t>
   </si>
   <si>
     <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
@@ -73,44 +76,19 @@
     <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t>5 Ocak 2026 Pazartesi</t>
+    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
   </si>
   <si>
     <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
+    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
   </si>
   <si>
     <t>İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
-  </si>
-  <si>
-    <t>*18 Mart Şehitleri Anma Günü Provası 
-*16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
-  </si>
-  <si>
-    <t>Ot Festivali ile ilgili toplantı 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
-  </si>
-  <si>
-    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
   </si>
   <si>
     <t>Çeşme Belediyesi Türk Halk Müziği Korosu “ Çeşme’den Türkü Akıyor” 2026 Kış Konseri
@@ -119,115 +97,113 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
+    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
+  </si>
+  <si>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
+  </si>
+  <si>
+    <t>*18 Mart Şehitleri Anma Günü Provası 
+*16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
+  </si>
+  <si>
+    <t>13 Nisan 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
+  </si>
+  <si>
+    <t>Ot Festivali ile ilgili toplantı 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
+  </si>
+  <si>
+    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>RAMAZAN BAYRAMI</t>
+  </si>
+  <si>
     <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
   </si>
   <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
     <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
   </si>
   <si>
     <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
   </si>
   <si>
-    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
-  </si>
-  <si>
-    <t>CHP Eğitim 17.00-20.00</t>
+    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
   </si>
   <si>
     <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
   </si>
   <si>
-    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
-  </si>
-  <si>
     <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
   </si>
   <si>
+    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
-  </si>
-  <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
-  </si>
-  <si>
-    <t>13 Nisan 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>RAMAZAN BAYRAMI</t>
-  </si>
-  <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
-    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
-  </si>
-  <si>
-    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
-  </si>
-  <si>
-    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
-  </si>
-  <si>
-    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
-  </si>
-  <si>
-    <t>YARI YIL ETKİNLİKLERİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>28 Şubat 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
   </si>
   <si>
     <r>
@@ -247,31 +223,22 @@
     </r>
   </si>
   <si>
-    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
-  </si>
-  <si>
-    <t>19 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
     <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
   </si>
   <si>
+    <t>YARI YIL ETKİNLİKLERİ</t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim tüm gün</t>
+  </si>
+  <si>
+    <t>Belediye TSM Konseri Tüm gün</t>
+  </si>
+  <si>
     <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim tüm gün</t>
-  </si>
-  <si>
     <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
   </si>
   <si>
     <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
@@ -281,30 +248,63 @@
 -Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
   </si>
   <si>
+    <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
     <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
   </si>
   <si>
+    <t>19 Ocak 2026 Pazartesi</t>
+  </si>
+  <si>
     <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
+    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
   </si>
   <si>
     <t>31 Ocak 2026 Cumartesi</t>
   </si>
   <si>
-    <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
+    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
   </si>
   <si>
     <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
   </si>
   <si>
+    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
     <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
   </si>
   <si>
+    <t>28 Şubat 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
+  </si>
+  <si>
     <t>MAYIS</t>
   </si>
   <si>
@@ -323,6 +323,9 @@
     <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
   </si>
   <si>
+    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -350,6 +353,9 @@
     <t>21.30 konser provası Başkan ile</t>
   </si>
   <si>
+    <t xml:space="preserve">HAZİRAN </t>
+  </si>
+  <si>
     <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
   </si>
   <si>
@@ -375,18 +381,27 @@
   </si>
   <si>
     <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
     <t>Bilgiç Anaokulu Prova 
 10.30-15.30</t>
   </si>
   <si>
+    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">Bilgiç Anaokulu Prova 
 10.30-15.30                                               </t>
   </si>
   <si>
     <t>-Bilgiç ortaokulu 09.00-12.00
 -Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
@@ -394,9 +409,15 @@
 onaylandı.</t>
   </si>
   <si>
+    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
+  </si>
+  <si>
     <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
   </si>
   <si>
+    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
     <t>18 MAYIS 2026 PAZARTESİ</t>
   </si>
   <si>
@@ -412,16 +433,25 @@
     <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t>23 MAYIS 2026 CUMARTESİ</t>
   </si>
   <si>
     <t>24 MAYIS 2026 PAZAR</t>
   </si>
   <si>
+    <t>7 HAZİRAN 2026 PAZAR</t>
+  </si>
+  <si>
     <t>Özhan Bakadur tiyatro</t>
   </si>
   <si>
     <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
   </si>
   <si>
     <r>
@@ -441,133 +471,6 @@
     </r>
   </si>
   <si>
-    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
-  </si>
-  <si>
-    <t>BAYRAM</t>
-  </si>
-  <si>
-    <t>25 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEMMUZ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
-  </si>
-  <si>
-    <t>Latin Katolik Kilisesi Ayin 
-18.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>-Çoklu İklim Krizinin Gölgesinde Orman Yangınları
-Afet İşleri Toplantı (Başkan Davet edilecekmiş)
--Belediye Meclisi 17.00'dan sonra</t>
-  </si>
-  <si>
-    <t>Belediye meclisi 16.00'dan sonra</t>
-  </si>
-  <si>
-    <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
-  </si>
-  <si>
-    <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAZİRAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>-Serakent Koop. Toplantısı Ödendi. İlhan Demli 5056804306 
--Latin Katolik Kilisesi Ayin 
-18.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-Deniz 1 Tatil Sitesi Kurul Toplantısı ödendi.11.00-15.30
--Yaşayan Hayat Engelliler Tiyatro Oyunu 19.00-21.00
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 TEMMZ 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>7 HAZİRAN 2026 PAZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -585,6 +488,12 @@
     </r>
   </si>
   <si>
+    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
+  </si>
+  <si>
+    <t>BAYRAM</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -606,7 +515,28 @@
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
   </si>
   <si>
+    <t>25 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
   </si>
   <si>
     <t xml:space="preserve">8 HAZİRAN 2026 PAZARTESİ </t>
@@ -742,6 +672,76 @@
     <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">TEMMUZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>Latin Katolik Kilisesi Ayin 
+18.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>-Çoklu İklim Krizinin Gölgesinde Orman Yangınları
+Afet İşleri Toplantı (Başkan Davet edilecekmiş)
+-Belediye Meclisi 17.00'dan sonra</t>
+  </si>
+  <si>
+    <t>Belediye meclisi 16.00'dan sonra</t>
+  </si>
+  <si>
+    <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
+  </si>
+  <si>
+    <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>-Serakent Koop. Toplantısı Ödendi. İlhan Demli 5056804306 
+-Latin Katolik Kilisesi Ayin 
+18.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Deniz 1 Tatil Sitesi Kurul Toplantısı ödendi.11.00-15.30
+-Yaşayan Hayat Engelliler Tiyatro Oyunu 19.00-21.00
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 TEMMZ 2026 CUMA </t>
+  </si>
+  <si>
     <t>AĞUSTOS</t>
   </si>
   <si>
@@ -752,6 +752,9 @@
   </si>
   <si>
     <t xml:space="preserve">4 AĞUSTOS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EYLÜL </t>
   </si>
   <si>
     <t xml:space="preserve">8 AĞUSTOS 2026 CUMARTESİ </t>
@@ -762,6 +765,9 @@
 18.30</t>
   </si>
   <si>
+    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">10 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -771,6 +777,9 @@
     <t xml:space="preserve">15 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">17 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -780,10 +789,20 @@
     <t xml:space="preserve">22 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
+Haydar Ali tel no: 5527151935</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ritim 10.00-12.00 </t>
   </si>
   <si>
+    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t>Deniz Tatil Sitesi Toplantı 11.00-18.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">24 AĞUSTOS 2026 PAZARTESİ </t>
@@ -803,29 +822,10 @@
 18.30(farklı odalar)</t>
   </si>
   <si>
+    <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EYLÜL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
-Haydar Ali tel no: 5527151935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>Belediye Meclis 15.00 Tüm alan</t>
@@ -920,42 +920,102 @@
     <t>3 EKİM 2026 CUMARTESİ</t>
   </si>
   <si>
+    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Yeni Parti Toplantı</t>
+  </si>
+  <si>
+    <t>5 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Hafifletici Sebepler opsiyon</t>
+  </si>
+  <si>
+    <t>12 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>19 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">KASIM </t>
   </si>
   <si>
-    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Yeni Parti Toplantı</t>
-  </si>
-  <si>
-    <t>5 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 KASIM 2026 PAZAR </t>
   </si>
   <si>
-    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Hafifletici Sebepler opsiyon</t>
-  </si>
-  <si>
     <t>2 KASIM 2026 PAZARTESİ</t>
   </si>
   <si>
@@ -977,30 +1037,9 @@
     <t xml:space="preserve">8 KASIM 2026 PAZAR </t>
   </si>
   <si>
-    <t>12 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t>9 KASIM 2026 PAZARTESİ</t>
   </si>
   <si>
-    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">10 KASIM 2026 SALI </t>
   </si>
   <si>
@@ -1019,30 +1058,9 @@
     <t xml:space="preserve">15 KASIM 2026 PAZAR </t>
   </si>
   <si>
-    <t>19 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">16 KASIM 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">17 KASIM 2026 SALI </t>
   </si>
   <si>
@@ -1061,33 +1079,18 @@
     <t xml:space="preserve">22 KASIM 2026 PAZAR </t>
   </si>
   <si>
-    <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 EKİM 2026 CUMA </t>
-  </si>
-  <si>
     <t xml:space="preserve">23 KASIM 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">24 KASIM 2025 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">25 KASIM 2026 ÇARŞAMBA </t>
   </si>
   <si>
+    <t xml:space="preserve">ARALIK </t>
+  </si>
+  <si>
     <t xml:space="preserve">26 KASIM 2026 PERŞEMBE </t>
   </si>
   <si>
@@ -1103,22 +1106,19 @@
     <t>Tuncay Hoca Çsm</t>
   </si>
   <si>
+    <t xml:space="preserve">1 ARALIK 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 ARALIK 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 ARALIK 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 ARALIK 2026 CUMA </t>
+  </si>
+  <si>
     <t>30 KASIM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARALIK </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 ARALIK 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 ARALIK 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 ARALIK 2026 CUMA </t>
   </si>
   <si>
     <t xml:space="preserve">5 ARALIK 2026 CUMA RTESİ </t>
@@ -1239,14 +1239,14 @@
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="15.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1325,14 +1325,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9CB9C"/>
-        <bgColor rgb="FFF9CB9C"/>
+        <fgColor rgb="FFE69138"/>
+        <bgColor rgb="FFE69138"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE69138"/>
-        <bgColor rgb="FFE69138"/>
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor rgb="FFF9CB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -1432,17 +1432,17 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1453,57 +1453,57 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1511,14 +1511,11 @@
     <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1531,6 +1528,9 @@
     </xf>
     <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1547,7 +1547,7 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1563,6 +1563,9 @@
     <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1572,8 +1575,14 @@
     <xf borderId="4" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1583,15 +1592,6 @@
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
@@ -1608,7 +1608,7 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1887,7 +1887,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
@@ -1895,86 +1895,86 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="9" t="s">
-        <v>2</v>
+      <c r="A2" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="13">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="14">
         <v>46023.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="15">
         <v>46024.0</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="14">
         <v>46026.0</v>
       </c>
     </row>
     <row r="4" ht="95.25" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="15">
         <v>46028.0</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="15">
         <v>46029.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="15">
         <v>46030.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="15">
         <v>46031.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="14">
         <v>46033.0</v>
       </c>
     </row>
     <row r="6" ht="97.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="10"/>
+        <v>17</v>
+      </c>
+      <c r="F6" s="12"/>
       <c r="G6" s="26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="15">
         <v>46035.0</v>
       </c>
       <c r="C7" s="29">
@@ -1983,44 +1983,44 @@
       <c r="D7" s="29">
         <v>46037.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>46038.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>43</v>
+      <c r="F7" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="G7" s="31">
         <v>46040.0</v>
       </c>
     </row>
     <row r="8" ht="69.0" customHeight="1">
-      <c r="A8" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="15" t="s">
+      <c r="A8" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>58</v>
+      <c r="G8" s="35" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="15">
         <v>46042.0</v>
       </c>
       <c r="C9" s="29">
@@ -2029,42 +2029,42 @@
       <c r="D9" s="29">
         <v>46044.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="15">
         <v>46045.0</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <v>46047.0</v>
       </c>
     </row>
     <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="23"/>
+      <c r="A10" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="22"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="15">
         <v>46049.0</v>
       </c>
       <c r="C11" s="29">
@@ -2073,24 +2073,24 @@
       <c r="D11" s="29">
         <v>46051.0</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="15">
         <v>46052.0</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="10"/>
+      <c r="F11" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="15" t="s">
-        <v>81</v>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="G12" s="40"/>
     </row>
@@ -2128,7 +2128,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="63" t="s">
@@ -2139,167 +2139,167 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="17" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="17" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" ht="84.0" customHeight="1">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="50" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="4" ht="84.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="49" t="s">
+      <c r="G4" s="50" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="G4" s="49" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="B5" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="C5" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="14" t="s">
+    </row>
+    <row r="6" ht="93.75" customHeight="1">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="64" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="64" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="22"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="64" t="s">
+      <c r="B7" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="64" t="s">
-        <v>261</v>
-      </c>
-      <c r="G6" s="23"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="C7" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" ht="97.5" customHeight="1">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="D9" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="E9" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="F9" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="G9" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="F7" s="14" t="s">
+    </row>
+    <row r="10" ht="100.5" customHeight="1">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="B11" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="10" ht="100.5" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="G11" s="10"/>
+      <c r="D11" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2333,188 +2333,188 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="42" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="17" t="s">
-        <v>259</v>
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="20" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="23"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>268</v>
+      <c r="A5" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>282</v>
+      <c r="A7" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="G9" s="14" t="s">
+      <c r="A9" s="20" t="s">
         <v>296</v>
       </c>
+      <c r="B9" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="E11" s="17" t="s">
+      <c r="D11" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="E11" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="F11" s="17" t="s">
         <v>309</v>
       </c>
+      <c r="G11" s="17" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
       <c r="G12" s="65" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="A13" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
-      <c r="A14" s="23"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2550,170 +2550,170 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>312</v>
+      <c r="A2" s="48" t="s">
+        <v>306</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="43"/>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="D3" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="E3" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="17" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="17" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="20" t="s">
         <v>329</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="17" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="17" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2741,7 +2741,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="63.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
@@ -2749,7 +2749,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
@@ -2765,7 +2765,7 @@
       <c r="T1" s="7"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2"/>
@@ -2773,7 +2773,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -2789,13 +2789,13 @@
       <c r="T2" s="7"/>
     </row>
     <row r="3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="16">
         <v>46054.0</v>
       </c>
       <c r="H3" s="7"/>
@@ -2813,13 +2813,13 @@
       <c r="T3" s="7"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="15"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -2836,24 +2836,24 @@
     </row>
     <row r="5">
       <c r="A5" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="22">
+        <v>12</v>
+      </c>
+      <c r="B5" s="23">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="23">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="23">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="23">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="19">
+      <c r="F5" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="16">
         <v>46061.0</v>
       </c>
       <c r="H5" s="7"/>
@@ -2871,18 +2871,18 @@
       <c r="T5" s="7"/>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>23</v>
+      <c r="A6" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -2900,24 +2900,24 @@
     </row>
     <row r="7">
       <c r="A7" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="22">
+        <v>40</v>
+      </c>
+      <c r="B7" s="23">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="23">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="23">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="23">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="19">
+      <c r="F7" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="16">
         <v>46068.0</v>
       </c>
       <c r="H7" s="7"/>
@@ -2935,22 +2935,22 @@
       <c r="T7" s="7"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="30" t="s">
-        <v>41</v>
+      <c r="A8" s="13"/>
+      <c r="B8" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="36" t="s">
+        <v>58</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -2968,24 +2968,24 @@
     </row>
     <row r="9">
       <c r="A9" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="22">
+        <v>69</v>
+      </c>
+      <c r="B9" s="23">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="23">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="23">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="23">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="F9" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="16">
         <v>46075.0</v>
       </c>
       <c r="H9" s="7"/>
@@ -3003,18 +3003,18 @@
       <c r="T9" s="7"/>
     </row>
     <row r="10" ht="89.25" customHeight="1">
-      <c r="A10" s="15"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>55</v>
+      <c r="A10" s="19"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>76</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -3032,24 +3032,24 @@
     </row>
     <row r="11">
       <c r="A11" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="22">
+        <v>78</v>
+      </c>
+      <c r="B11" s="23">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="23">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="18"/>
+      <c r="F11" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="13"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
@@ -3065,15 +3065,15 @@
       <c r="T11" s="7"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
@@ -24394,214 +24394,214 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>4</v>
+      <c r="A2" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="13">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="14">
         <v>46082.0</v>
       </c>
     </row>
     <row r="4" ht="69.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="15" t="s">
-        <v>7</v>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="19" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="15">
         <v>46084.0</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="15">
         <v>46085.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="15">
         <v>46086.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="15">
         <v>46087.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="14">
         <v>46089.0</v>
       </c>
     </row>
     <row r="6" ht="113.25" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="15" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="15"/>
+      <c r="E6" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="19"/>
       <c r="G6" s="25"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="15">
         <v>46091.0</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="15">
         <v>46092.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>46093.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>46094.0</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="14">
+        <v>46096.0</v>
+      </c>
+    </row>
+    <row r="8" ht="87.0" customHeight="1">
+      <c r="A8" s="12"/>
+      <c r="B8" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="13">
-        <v>46096.0</v>
-      </c>
-    </row>
-    <row r="8" ht="87.0" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="D8" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="10"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="B9" s="15">
         <v>46098.0</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="14">
         <v>46099.0</v>
       </c>
       <c r="D9" s="29">
         <v>46100.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="15">
         <v>46101.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="14">
         <v>46103.0</v>
       </c>
     </row>
     <row r="10" ht="96.0" customHeight="1">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="34" t="s">
-        <v>48</v>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="33" t="s">
+        <v>39</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="4"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="15">
+        <v>46105.0</v>
+      </c>
+      <c r="C11" s="15">
+        <v>46106.0</v>
+      </c>
+      <c r="D11" s="15">
+        <v>46107.0</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46108.0</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="14">
+        <v>46110.0</v>
+      </c>
+    </row>
+    <row r="12" ht="91.5" customHeight="1">
+      <c r="A12" s="12"/>
+      <c r="B12" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="12">
-        <v>46105.0</v>
-      </c>
-      <c r="C11" s="12">
-        <v>46106.0</v>
-      </c>
-      <c r="D11" s="12">
-        <v>46107.0</v>
-      </c>
-      <c r="E11" s="12">
-        <v>46108.0</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="13">
-        <v>46110.0</v>
-      </c>
-    </row>
-    <row r="12" ht="91.5" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>73</v>
+      <c r="E12" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="F12" s="37"/>
       <c r="G12" s="37"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="A13" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="15">
         <v>46112.0</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
     </row>
     <row r="14" ht="95.25" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -24630,7 +24630,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
@@ -24638,184 +24638,184 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="12">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="15">
         <v>46113.0</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="15">
         <v>46114.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="15">
         <v>46115.0</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="14">
         <v>46117.0</v>
       </c>
     </row>
     <row r="4" ht="99.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="10"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="15">
         <v>46119.0</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="15">
         <v>46120.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="15">
         <v>46121.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="15">
         <v>46122.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="14">
         <v>46124.0</v>
       </c>
     </row>
     <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="27" t="s">
-        <v>26</v>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="24" t="s">
+        <v>19</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="27" t="s">
-        <v>40</v>
+        <v>22</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="24" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="15">
         <v>46126.0</v>
       </c>
       <c r="C7" s="29">
         <v>46127.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>46128.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>46129.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="14">
         <v>46131.0</v>
       </c>
     </row>
     <row r="8" ht="80.25" customHeight="1">
-      <c r="A8" s="32"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="27" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="15">
+        <v>46133.0</v>
+      </c>
+      <c r="C9" s="15">
+        <v>46134.0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>46135.0</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46136.0</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="14">
+        <v>46138.0</v>
+      </c>
+    </row>
+    <row r="10" ht="92.25" customHeight="1">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="12">
-        <v>46133.0</v>
-      </c>
-      <c r="C9" s="12">
-        <v>46134.0</v>
-      </c>
-      <c r="D9" s="13">
-        <v>46135.0</v>
-      </c>
-      <c r="E9" s="12">
-        <v>46136.0</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="13">
-        <v>46138.0</v>
-      </c>
-    </row>
-    <row r="10" ht="92.25" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="B11" s="15">
         <v>46140.0</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="15">
         <v>46141.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="15">
         <v>46142.0</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
       <c r="D12" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
     </row>
     <row r="13">
       <c r="D13" s="39"/>
@@ -24854,7 +24854,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="42" t="s">
@@ -24865,208 +24865,208 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="14" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="17" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="10"/>
+      <c r="A4" s="12"/>
       <c r="B4" s="43"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
       <c r="E4" s="44" t="s">
         <v>86</v>
       </c>
       <c r="F4" s="45"/>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="24" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="A5" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="B5" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="C5" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="E5" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="F5" s="17" t="s">
         <v>94</v>
       </c>
+      <c r="G5" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="10"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="12"/>
       <c r="E6" s="46" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G6" s="45"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="17" t="s">
+      <c r="A7" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="B7" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="C7" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="D7" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="E7" s="20" t="s">
         <v>104</v>
       </c>
+      <c r="F7" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="27" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="27" t="s">
-        <v>108</v>
+      <c r="C8" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>112</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>117</v>
+      <c r="A9" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="27" t="s">
-        <v>118</v>
+      <c r="A10" s="24" t="s">
+        <v>127</v>
       </c>
       <c r="B10" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="G10" s="50" t="s">
-        <v>122</v>
+      <c r="C10" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>129</v>
+      <c r="A11" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="F12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="G12" s="50" t="s">
-        <v>122</v>
+      <c r="A12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -25096,219 +25096,219 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>146</v>
+      <c r="A2" s="48" t="s">
+        <v>98</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" ht="91.5" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="G4" s="19"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" ht="183.75" customHeight="1">
+      <c r="A6" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="E6" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="F6" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="G6" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="E3" s="17" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="B7" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="C7" s="20" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="27" t="s">
+      <c r="D7" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="E7" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="F7" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="G7" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="38" t="s">
+    </row>
+    <row r="8" ht="101.25" customHeight="1">
+      <c r="A8" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="G4" s="15"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="B8" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="C8" s="50" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D8" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E8" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F8" s="50" t="s">
         <v>169</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G8" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="G5" s="14" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="6" ht="183.75" customHeight="1">
-      <c r="A6" s="56" t="s">
+      <c r="B9" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="B6" s="56" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="56" t="s">
+      <c r="C9" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D9" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E9" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="F9" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G9" s="17" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
+    <row r="10" ht="99.75" customHeight="1">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="G10" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="17" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="B11" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="8" ht="101.25" customHeight="1">
-      <c r="A8" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" ht="99.75" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25344,188 +25344,188 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>130</v>
+      <c r="A2" s="48" t="s">
+        <v>182</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="12">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="15">
         <v>46204.0</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="15">
         <v>46205.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="15">
         <v>46206.0</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="14">
         <v>46208.0</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="G4" s="15"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="19"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="12">
+      <c r="A5" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="15">
         <v>46211.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="15">
         <v>46212.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="15">
         <v>46213.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="14">
         <v>46215.0</v>
       </c>
     </row>
     <row r="6" ht="92.25" customHeight="1">
-      <c r="A6" s="52" t="s">
-        <v>137</v>
-      </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>140</v>
+      <c r="A6" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>142</v>
+      <c r="A7" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>193</v>
       </c>
       <c r="C7" s="29">
         <v>46218.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>46219.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>46220.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="G7" s="53">
+      <c r="F7" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="G7" s="56">
         <v>46222.0</v>
       </c>
     </row>
     <row r="8" ht="88.5" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="G8" s="23"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="22"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="12">
+      <c r="A9" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="15">
         <v>46225.0</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="57">
         <v>46226.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="15">
         <v>46227.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="G9" s="14">
         <v>46229.0</v>
       </c>
     </row>
     <row r="10" ht="77.25" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
       <c r="F10" s="47" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="G10" s="47" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" s="12">
+      <c r="A11" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" s="15">
         <v>46232.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="15">
         <v>46233.0</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25561,10 +25561,10 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="48" t="s">
         <v>203</v>
       </c>
       <c r="B2" s="2"/>
@@ -25572,199 +25572,199 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="14" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="14">
         <v>46236.0</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="G4" s="23"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="22"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="15">
         <v>46239.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="15">
         <v>46240.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="15">
         <v>46241.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="G5" s="14">
         <v>46243.0</v>
       </c>
     </row>
     <row r="6" ht="84.0" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="G6" s="23"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="G6" s="22"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="12">
+      <c r="A7" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="15">
         <v>46246.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>46247.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>46248.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" s="14">
         <v>46250.0</v>
       </c>
     </row>
     <row r="8" ht="93.75" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="G8" s="23"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="22"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="C9" s="12">
+      <c r="A9" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="15">
         <v>46253.0</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="15">
         <v>46254.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="15">
         <v>46255.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="G9" s="14">
         <v>46257.0</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="49" t="s">
-        <v>215</v>
+      <c r="A10" s="22"/>
+      <c r="B10" s="50" t="s">
+        <v>219</v>
       </c>
       <c r="C10" s="40"/>
-      <c r="D10" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>216</v>
+      <c r="D10" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="22"/>
+      <c r="F10" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="12">
+      <c r="A11" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="15">
         <v>46260.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="15">
         <v>46261.0</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="15">
         <v>46262.0</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="G11" s="14">
+        <v>46264.0</v>
+      </c>
+    </row>
+    <row r="12" ht="94.5" customHeight="1">
+      <c r="A12" s="22"/>
+      <c r="B12" s="50" t="s">
         <v>219</v>
       </c>
-      <c r="G11" s="13">
-        <v>46264.0</v>
-      </c>
-    </row>
-    <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="G12" s="23"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="G12" s="22"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="A13" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
-      <c r="A14" s="23"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25800,57 +25800,57 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>223</v>
+      <c r="A2" s="48" t="s">
+        <v>207</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="C3" s="12">
+      <c r="A3" s="12"/>
+      <c r="B3" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="15">
         <v>46267.0</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="15">
         <v>46268.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="15">
         <v>46269.0</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="G3" s="14">
         <v>46271.0</v>
       </c>
     </row>
     <row r="4" ht="85.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="58" t="s">
-        <v>226</v>
-      </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+        <v>218</v>
+      </c>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>227</v>
+      <c r="A5" s="20" t="s">
+        <v>220</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C5" s="60">
         <v>46274.0</v>
@@ -25858,29 +25858,29 @@
       <c r="D5" s="61">
         <v>46275.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="15">
         <v>46276.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="G5" s="14">
         <v>46278.0</v>
       </c>
     </row>
     <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="20" t="s">
         <v>231</v>
       </c>
       <c r="B7" s="59" t="s">
@@ -25889,54 +25889,54 @@
       <c r="C7" s="60">
         <v>46281.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>46282.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>46283.0</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="14">
         <v>46285.0</v>
       </c>
     </row>
     <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="15">
         <v>46288.0</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="15">
         <v>46289.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="15">
         <v>46290.0</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <v>46292.0</v>
       </c>
     </row>
@@ -25944,42 +25944,42 @@
       <c r="A10" s="58" t="s">
         <v>240</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
       <c r="E10" s="58" t="s">
         <v>241</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="24" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="15">
         <v>46295.0</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -30,56 +30,19 @@
     <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
   </si>
   <si>
+    <t>OCAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MART </t>
+  </si>
+  <si>
     <t xml:space="preserve">NİSAN </t>
   </si>
   <si>
-    <t xml:space="preserve">MART </t>
-  </si>
-  <si>
-    <t>OCAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
+    <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
   </si>
   <si>
     <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
-  </si>
-  <si>
-    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
-  </si>
-  <si>
-    <t>*18 Mart Şehitleri Anma Günü Provası 
-*16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
-  </si>
-  <si>
-    <t>5 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t>CHP Eğitim 17.00-20.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
   </si>
   <si>
     <r>
@@ -101,25 +64,16 @@
     </r>
   </si>
   <si>
+    <t>5 Ocak 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
-  </si>
-  <si>
-    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t>13 Nisan 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
-  </si>
-  <si>
-    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
   </si>
   <si>
     <t>Çeşme Belediyesi Türk Halk Müziği Korosu “ Çeşme’den Türkü Akıyor” 2026 Kış Konseri
@@ -128,40 +82,192 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
+    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
+  </si>
+  <si>
+    <t>*18 Mart Şehitleri Anma Günü Provası 
+*16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
+  </si>
+  <si>
+    <t>CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
+  </si>
+  <si>
+    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
+  </si>
+  <si>
+    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+  </si>
+  <si>
+    <t>YARI YIL ETKİNLİKLERİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
+  </si>
+  <si>
+    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
+  </si>
+  <si>
     <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
+  </si>
+  <si>
+    <t>13 Nisan 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t>RAMAZAN BAYRAMI</t>
+  </si>
+  <si>
     <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>RAMAZAN BAYRAMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+    <t>19 Ocak 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>31 Ocak 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+  </si>
+  <si>
+    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim tüm gün</t>
+  </si>
+  <si>
+    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
+  </si>
+  <si>
+    <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
+-Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
+  </si>
+  <si>
+    <t>Ot Festivali ile ilgili toplantı 14.00</t>
+  </si>
+  <si>
+    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
+  </si>
+  <si>
+    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
+  </si>
+  <si>
+    <t>Belediye TSM Konseri Tüm gün</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
+  </si>
+  <si>
+    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
   </si>
   <si>
     <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
   </si>
   <si>
-    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim tüm gün</t>
-  </si>
-  <si>
-    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
+    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>28 Şubat 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
   </si>
   <si>
     <r>
@@ -181,133 +287,36 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
-  </si>
-  <si>
-    <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
--Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
-  </si>
-  <si>
     <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
   </si>
   <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
-  </si>
-  <si>
     <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
-  </si>
-  <si>
-    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
-  </si>
-  <si>
     <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t>YARI YIL ETKİNLİKLERİ</t>
-  </si>
-  <si>
     <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
   </si>
   <si>
     <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
     <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
   </si>
   <si>
-    <t>19 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>31 Ocak 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
-  </si>
-  <si>
-    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
-  </si>
-  <si>
-    <t>Ot Festivali ile ilgili toplantı 14.00</t>
-  </si>
-  <si>
-    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
-  </si>
-  <si>
-    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
-  </si>
-  <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
-  </si>
-  <si>
-    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>28 Şubat 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
-  </si>
-  <si>
     <t>MAYIS</t>
   </si>
   <si>
+    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAZİRAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMMUZ </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
   </si>
   <si>
@@ -317,76 +326,31 @@
     <t>3 MAYIS 2026 PAZAR</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
+    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>7 HAZİRAN 2026 PAZAR</t>
   </si>
   <si>
     <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
   </si>
   <si>
-    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAZİRAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>10 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t>21.30 konser provası Başkan ile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
-  </si>
-  <si>
-    <t>7 HAZİRAN 2026 PAZAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
-  </si>
-  <si>
-    <t>11 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
   </si>
   <si>
     <r>
@@ -406,12 +370,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -429,35 +387,56 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
+    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>Bilgiç İlkokulu 13.00 1. Sınıf Okuma Bayramı 18.00
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
   </si>
   <si>
-    <t>16 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
+    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
+  </si>
+  <si>
+    <t>Latin Katolik Kilisesi Ayin 
+18.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>10 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
   </si>
   <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
   </si>
   <si>
+    <t>21.30 konser provası Başkan ile</t>
+  </si>
+  <si>
     <t xml:space="preserve">8 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">9 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t>Bilgiç Anaokulu Prova 
-10.30-15.30</t>
-  </si>
-  <si>
     <t xml:space="preserve">10 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
@@ -467,56 +446,33 @@
     <t xml:space="preserve">12 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
-    <t xml:space="preserve">Bilgiç Anaokulu Prova 
-10.30-15.30                                               </t>
-  </si>
-  <si>
     <t>13 HAZİRAN 2026 CUMARTESİ</t>
   </si>
   <si>
-    <t>-Bilgiç ortaokulu 09.00-12.00
--Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
-  </si>
-  <si>
     <t xml:space="preserve">14 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
-    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
-"No Mans Land" Yetişkin Oyunu 20.00
-onaylandı.</t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
-  </si>
-  <si>
-    <t>18 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00</t>
   </si>
   <si>
-    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t>23 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t>24 MAYIS 2026 PAZAR</t>
+    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
+  </si>
+  <si>
+    <t>-Çoklu İklim Krizinin Gölgesinde Orman Yangınları
+Afet İşleri Toplantı (Başkan Davet edilecekmiş)
+-Belediye Meclisi 17.00'dan sonra</t>
   </si>
   <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00                                                        "SEVGİLİ DOKTOR"  20.00</t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro</t>
   </si>
   <si>
     <r>
@@ -537,12 +493,174 @@
     </r>
   </si>
   <si>
-    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
-  </si>
-  <si>
     <t>-SERTUR KOOPERATİF TOPLANTISI HALUK BEY 05336460236 
 15.00'a kadar
 - Kent Enstitüsü Prova</t>
+  </si>
+  <si>
+    <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
+  </si>
+  <si>
+    <t>11 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>16 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Belediye meclisi 16.00'dan sonra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
+  </si>
+  <si>
+    <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
+    <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>Bilgiç Anaokulu Prova 
+10.30-15.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilgiç Anaokulu Prova 
+10.30-15.30                                               </t>
+  </si>
+  <si>
+    <t>-Bilgiç ortaokulu 09.00-12.00
+-Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
+  </si>
+  <si>
+    <t>Atatürk Lisesi tiyatro prova</t>
+  </si>
+  <si>
+    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
+"No Mans Land" Yetişkin Oyunu 20.00
+onaylandı.</t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
+  </si>
+  <si>
+    <t>Atatürk Lisesi Oyun Günü</t>
+  </si>
+  <si>
+    <t>Osman Uysal Prova opsiyon</t>
+  </si>
+  <si>
+    <t>18 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
+sabahtan 21.00'a kadar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t>Namık Kemal Okuma Bayramı</t>
+  </si>
+  <si>
+    <t>Doğu Der Toplantı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
+    <t>23 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t>24 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
   </si>
   <si>
     <r>
@@ -565,101 +683,7 @@
     <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
   </si>
   <si>
-    <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
-  </si>
-  <si>
     <t>BAYRAM</t>
-  </si>
-  <si>
-    <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t>25 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t>Atatürk Lisesi tiyatro prova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Atatürk Lisesi Oyun Günü</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEMMUZ </t>
-  </si>
-  <si>
-    <t>Osman Uysal Prova opsiyon</t>
-  </si>
-  <si>
-    <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
-sabahtan 21.00'a kadar</t>
-  </si>
-  <si>
-    <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
-  </si>
-  <si>
-    <t>Namık Kemal Okuma Bayramı</t>
-  </si>
-  <si>
-    <t>Doğu Der Toplantı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
     <t>Reyhan Cici Piyano Dinletisi
@@ -669,58 +693,13 @@
     <t>MHP 15. Olağan Kongre Toplantısı</t>
   </si>
   <si>
+    <t xml:space="preserve">25 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Latin Katolik Kilisesi Ayin 
-18.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>-Çoklu İklim Krizinin Gölgesinde Orman Yangınları
-Afet İşleri Toplantı (Başkan Davet edilecekmiş)
--Belediye Meclisi 17.00'dan sonra</t>
-  </si>
-  <si>
-    <t>Belediye meclisi 16.00'dan sonra</t>
-  </si>
-  <si>
-    <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
-  </si>
-  <si>
-    <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 TEMMUZ 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>-Serakent Koop. Toplantısı Ödendi. İlhan Demli 5056804306 
@@ -728,52 +707,54 @@
 18.30</t>
   </si>
   <si>
+    <t>25 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">-Deniz 1 Tatil Sitesi Kurul Toplantısı ödendi.11.00-15.30
 -Yaşayan Hayat Engelliler Tiyatro Oyunu 19.00-21.00
 </t>
   </si>
   <si>
+    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">27 TEMMUZ 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
     <t xml:space="preserve">28 TEMMUZ 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">31 TEMMZ 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
     <t>AĞUSTOS</t>
   </si>
   <si>
-    <t xml:space="preserve">EYLÜL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
-Haydar Ali tel no: 5527151935</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">4 AĞUSTOS 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">8 AĞUSTOS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
   </si>
   <si>
     <t>-Orkent Sitesi 11.00-13.00 ödendi.
@@ -787,19 +768,109 @@
     <t xml:space="preserve">11 AĞUSTOS 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">15 AĞUSTOS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 AĞUSTOS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 AĞUSTOS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 AĞUSTOS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ritim 10.00-12.00 </t>
+  </si>
+  <si>
+    <t>Deniz Tatil Sitesi Toplantı 11.00-18.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 AĞUSTOS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 AĞUSTOS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 AĞUSTOS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORUK BELDESİ, ARSA VE YAPI KOOPERATİFİ                                 13.00-15.00  </t>
+  </si>
+  <si>
+    <t>-Saygun Sanat Şirinler Müzikali 2 seans 
+-Latin Katolik Kilisesi Ayin 
+18.30(farklı odalar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EYLÜL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EKİM </t>
+  </si>
+  <si>
+    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
+Haydar Ali tel no: 5527151935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t>3 EKİM 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Yeni Parti Toplantı</t>
+  </si>
+  <si>
+    <t>5 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
     <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">15 AĞUSTOS 2026 CUMARTESİ </t>
+    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
   </si>
   <si>
     <t>Belediye Meclis 15.00 Tüm alan</t>
   </si>
   <si>
-    <t xml:space="preserve">17 AĞUSTOS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 AĞUSTOS 2026 SALI </t>
+    <t>Hafifletici Sebepler opsiyon</t>
   </si>
   <si>
     <t xml:space="preserve">14 EYLÜL 2026 PAZARTESİ </t>
@@ -808,13 +879,7 @@
     <t xml:space="preserve">15 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">22 AĞUSTOS 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">19 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ritim 10.00-12.00 </t>
   </si>
   <si>
     <t xml:space="preserve">09:00-16:00 
@@ -836,36 +901,34 @@
     <t xml:space="preserve">22 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t>Deniz Tatil Sitesi Toplantı 11.00-18.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 AĞUSTOS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 AĞUSTOS 2026 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">26 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">29 AĞUSTOS 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t>Osman Uysal Konser Prova 18.00-22.00</t>
   </si>
   <si>
-    <t xml:space="preserve">DORUK BELDESİ, ARSA VE YAPI KOOPERATİFİ                                 13.00-15.00  </t>
+    <t>12 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
   </si>
   <si>
     <t>Osman Uysal Konser 20.30 (tüm gün)</t>
-  </si>
-  <si>
-    <t>-Saygun Sanat Şirinler Müzikali 2 seans 
--Latin Katolik Kilisesi Ayin 
-18.30(farklı odalar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
     <r>
@@ -887,6 +950,9 @@
     </r>
   </si>
   <si>
+    <t>İZMİR KENT TİYATROSU 05547273157</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -910,72 +976,6 @@
     <t xml:space="preserve">29 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">EKİM </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t>3 EKİM 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Yeni Parti Toplantı</t>
-  </si>
-  <si>
-    <t>5 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Hafifletici Sebepler opsiyon</t>
-  </si>
-  <si>
-    <t>12 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>İZMİR KENT TİYATROSU 05547273157</t>
-  </si>
-  <si>
     <t>19 EKİM 2026 PAZARTESİ</t>
   </si>
   <si>
@@ -1042,63 +1042,90 @@
     <t xml:space="preserve">8 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t>9 KASIM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 KASIM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 KASIM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 KASIM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 KASIM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 KASIM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 KASIM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 KASIM 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 KASIM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 KASIM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 KASIM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 KASIM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 KASIM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 KASIM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 KASIM 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 KASIM 2025 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 KASIM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 KASIM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 KASIM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 KASIM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 KASIM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Tuncay Hoca Çsm</t>
+  </si>
+  <si>
+    <t>30 KASIM 2026 PAZARTESİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARALIK </t>
   </si>
   <si>
-    <t>9 KASIM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 KASIM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 KASIM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 KASIM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 KASIM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 KASIM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 KASIM 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 ARALIK 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">16 KASIM 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 KASIM 2026 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 ARALIK 2026 ÇARŞAMBA </t>
   </si>
   <si>
-    <t xml:space="preserve">18 KASIM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 ARALIK 2026 PERŞEMBE </t>
   </si>
   <si>
-    <t xml:space="preserve">19 KASIM 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t xml:space="preserve">4 ARALIK 2026 CUMA </t>
   </si>
   <si>
-    <t xml:space="preserve">20 KASIM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 KASIM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 KASIM 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 ARALIK 2026 CUMA RTESİ </t>
   </si>
   <si>
@@ -1114,39 +1141,18 @@
     <t xml:space="preserve">9 ARALIK 2026 ÇARŞAMBA </t>
   </si>
   <si>
-    <t xml:space="preserve">23 KASIM 2026 PAZARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">10 ARALIK 2026 PERŞEMBE </t>
   </si>
   <si>
-    <t xml:space="preserve">24 KASIM 2025 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">11 ARALIK 2026 CUMA </t>
   </si>
   <si>
-    <t xml:space="preserve">25 KASIM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
     <t xml:space="preserve">12 ARALIK 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">26 KASIM 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t xml:space="preserve">13 ARALIK 2026 PAZAR </t>
   </si>
   <si>
-    <t xml:space="preserve">27 KASIM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 KASIM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 KASIM 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">14 ARALIK 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -1156,9 +1162,6 @@
     <t xml:space="preserve">16 ARALIK 2026 ÇARŞAMBA </t>
   </si>
   <si>
-    <t>Tuncay Hoca Çsm</t>
-  </si>
-  <si>
     <t xml:space="preserve">17 ARALIK 2026 PERŞEMBE </t>
   </si>
   <si>
@@ -1181,9 +1184,6 @@
   </si>
   <si>
     <t xml:space="preserve">24 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t>30 KASIM 2026 PAZARTESİ</t>
   </si>
   <si>
     <t xml:space="preserve">25 ARALIK 2026 CUMA </t>
@@ -1224,6 +1224,14 @@
     </font>
     <font>
       <b/>
+      <sz val="13.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font/>
+    <font>
+      <b/>
       <sz val="14.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1231,13 +1239,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font/>
-    <font>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1250,7 +1252,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1263,19 +1264,18 @@
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <color rgb="FF38761D"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1297,13 +1297,13 @@
     </font>
     <font>
       <b/>
+      <sz val="13.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1324,14 +1324,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6B26B"/>
-        <bgColor rgb="FFF6B26B"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor rgb="FFF9CB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -1342,8 +1342,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9CB9C"/>
-        <bgColor rgb="FFF9CB9C"/>
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF6B26B"/>
       </patternFill>
     </fill>
     <fill>
@@ -1354,14 +1354,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -1443,81 +1443,65 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
@@ -1525,119 +1509,135 @@
     <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="1" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="15" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="12" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="12" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1910,41 +1910,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="13">
+      <c r="D3" s="10">
         <v>46023.0</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="12">
         <v>46024.0</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="10">
         <v>46026.0</v>
       </c>
     </row>
@@ -1959,24 +1959,24 @@
     </row>
     <row r="5">
       <c r="A5" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="10">
+        <v>8</v>
+      </c>
+      <c r="B5" s="12">
         <v>46028.0</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="12">
         <v>46029.0</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="12">
         <v>46030.0</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="12">
         <v>46031.0</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="10">
         <v>46033.0</v>
       </c>
     </row>
@@ -1985,137 +1985,137 @@
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="23" t="s">
-        <v>27</v>
+      <c r="E6" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="23" t="s">
-        <v>32</v>
+      <c r="G6" s="18" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
       <c r="A7" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="10">
+        <v>15</v>
+      </c>
+      <c r="B7" s="12">
         <v>46035.0</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="19">
         <v>46036.0</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="19">
         <v>46037.0</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="12">
         <v>46038.0</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="29">
+      <c r="F7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="23">
         <v>46040.0</v>
       </c>
     </row>
     <row r="8" ht="69.0" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>52</v>
+        <v>28</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="10">
+        <v>42</v>
+      </c>
+      <c r="B9" s="12">
         <v>46042.0</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="19">
         <v>46043.0</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="19">
         <v>46044.0</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="12">
         <v>46045.0</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="10">
         <v>46047.0</v>
       </c>
     </row>
     <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="17"/>
+      <c r="A10" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="21"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="10">
+        <v>45</v>
+      </c>
+      <c r="B11" s="12">
         <v>46049.0</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="19">
         <v>46050.0</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="19">
         <v>46051.0</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="12">
         <v>46052.0</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
       <c r="A12" s="15"/>
       <c r="B12" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+        <v>47</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
       <c r="F12" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="39"/>
+        <v>48</v>
+      </c>
+      <c r="G12" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2143,25 +2143,25 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="64" t="s">
-        <v>246</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="59" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
@@ -2169,101 +2169,101 @@
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="16" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>250</v>
+        <v>231</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="4" ht="84.0" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="G4" s="51" t="s">
-        <v>251</v>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="48" t="s">
+        <v>234</v>
+      </c>
+      <c r="G4" s="48" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>258</v>
+        <v>240</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="65" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="66" t="s">
-        <v>259</v>
-      </c>
-      <c r="G6" s="17"/>
-      <c r="L6" s="67"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="64" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="65" t="s">
+        <v>244</v>
+      </c>
+      <c r="G6" s="21"/>
+      <c r="L6" s="66"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="G7" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="E7" s="16" t="s">
+    </row>
+    <row r="8" ht="97.5" customHeight="1">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="68" t="s">
         <v>264</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="68" t="s">
-        <v>267</v>
-      </c>
-      <c r="G8" s="17"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
@@ -2281,21 +2281,21 @@
       <c r="E9" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="14" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="10" ht="100.5" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="s">
@@ -2313,18 +2313,18 @@
       <c r="E11" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="14" t="s">
         <v>280</v>
       </c>
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="8"/>
     </row>
   </sheetData>
@@ -2354,22 +2354,22 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -2390,7 +2390,7 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="17"/>
+      <c r="G4" s="21"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="s">
@@ -2408,123 +2408,123 @@
       <c r="E5" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="14" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="C7" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="D7" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="E7" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="F7" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="G7" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>297</v>
-      </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="E9" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="F9" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>307</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>308</v>
+      <c r="G9" s="14" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>324</v>
+        <v>308</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="69" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2534,7 +2534,7 @@
       <c r="G13" s="8"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
-      <c r="A14" s="17"/>
+      <c r="A14" s="21"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -2571,149 +2571,149 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="46" t="s">
-        <v>290</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="43" t="s">
+        <v>313</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="43"/>
+      <c r="A3" s="44"/>
       <c r="B3" s="16" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>310</v>
+        <v>317</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
       <c r="A4" s="8"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>321</v>
+        <v>324</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="F7" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="F7" s="14" t="s">
         <v>332</v>
       </c>
+      <c r="G7" s="14" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="14" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="s">
@@ -2733,10 +2733,10 @@
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -2767,14 +2767,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="63.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
@@ -2791,14 +2791,14 @@
       <c r="T1" s="11"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -2815,13 +2815,13 @@
       <c r="T2" s="11"/>
     </row>
     <row r="3">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="30">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="24">
         <v>46054.0</v>
       </c>
       <c r="H3" s="11"/>
@@ -2839,12 +2839,12 @@
       <c r="T3" s="11"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="32"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="15"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
@@ -2861,25 +2861,25 @@
       <c r="T4" s="11"/>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="36">
+      <c r="A5" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="30">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="30">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="30">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="30">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="30">
+      <c r="F5" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="24">
         <v>46061.0</v>
       </c>
       <c r="H5" s="11"/>
@@ -2898,17 +2898,17 @@
     </row>
     <row r="6" ht="93.75" customHeight="1">
       <c r="A6" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+        <v>55</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
       <c r="F6" s="15" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -2925,25 +2925,25 @@
       <c r="T6" s="11"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="36">
+      <c r="A7" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="30">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="30">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="30">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="30">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="30">
+      <c r="F7" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="24">
         <v>46068.0</v>
       </c>
       <c r="H7" s="11"/>
@@ -2961,22 +2961,22 @@
       <c r="T7" s="11"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="25"/>
+      <c r="A8" s="20"/>
       <c r="B8" s="15" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="40" t="s">
-        <v>73</v>
+        <v>64</v>
+      </c>
+      <c r="F8" s="20"/>
+      <c r="G8" s="36" t="s">
+        <v>65</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -2993,25 +2993,25 @@
       <c r="T8" s="11"/>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="36">
+      <c r="A9" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="30">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="30">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="30">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="30">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="30">
+      <c r="F9" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="24">
         <v>46075.0</v>
       </c>
       <c r="H9" s="11"/>
@@ -3030,17 +3030,17 @@
     </row>
     <row r="10" ht="89.25" customHeight="1">
       <c r="A10" s="15"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="15" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -3057,25 +3057,25 @@
       <c r="T10" s="11"/>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="36">
+      <c r="A11" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="30">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="30">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="30">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="30">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="25"/>
+      <c r="F11" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="20"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
@@ -3091,15 +3091,15 @@
       <c r="T11" s="11"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
+        <v>74</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
@@ -24412,25 +24412,25 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
@@ -24440,7 +24440,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="13">
+      <c r="G3" s="10">
         <v>46082.0</v>
       </c>
     </row>
@@ -24457,102 +24457,102 @@
     </row>
     <row r="5">
       <c r="A5" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="10">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12">
         <v>46084.0</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="12">
         <v>46085.0</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="12">
         <v>46086.0</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="12">
         <v>46087.0</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="10">
         <v>46089.0</v>
       </c>
     </row>
     <row r="6" ht="113.25" customHeight="1">
       <c r="A6" s="8"/>
-      <c r="B6" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="17"/>
+      <c r="B6" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="21"/>
       <c r="D6" s="15" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F6" s="15"/>
-      <c r="G6" s="19"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="10">
+        <v>30</v>
+      </c>
+      <c r="B7" s="12">
         <v>46091.0</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="12">
         <v>46092.0</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="12">
         <v>46093.0</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="12">
         <v>46094.0</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="10">
         <v>46096.0</v>
       </c>
     </row>
     <row r="8" ht="87.0" customHeight="1">
       <c r="A8" s="8"/>
-      <c r="B8" s="17" t="s">
-        <v>11</v>
+      <c r="B8" s="21" t="s">
+        <v>19</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="15" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G8" s="8"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="10">
+        <v>35</v>
+      </c>
+      <c r="B9" s="12">
         <v>46098.0</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="10">
         <v>46099.0</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="19">
         <v>46100.0</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="12">
         <v>46101.0</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="10">
         <v>46103.0</v>
       </c>
     </row>
@@ -24560,58 +24560,58 @@
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
-      <c r="D10" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="D10" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
       <c r="G10" s="4"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="10">
+        <v>49</v>
+      </c>
+      <c r="B11" s="12">
         <v>46105.0</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="12">
         <v>46106.0</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="12">
         <v>46107.0</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="12">
         <v>46108.0</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="13">
+      <c r="F11" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="10">
         <v>46110.0</v>
       </c>
     </row>
     <row r="12" ht="91.5" customHeight="1">
       <c r="A12" s="8"/>
       <c r="B12" s="15" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
+        <v>54</v>
+      </c>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="10">
+        <v>58</v>
+      </c>
+      <c r="B13" s="12">
         <v>46112.0</v>
       </c>
       <c r="C13" s="8"/>
@@ -24656,43 +24656,43 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="10">
+      <c r="C3" s="12">
         <v>46113.0</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="12">
         <v>46114.0</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="12">
         <v>46115.0</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="10">
         <v>46117.0</v>
       </c>
     </row>
@@ -24707,24 +24707,24 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="10">
+        <v>13</v>
+      </c>
+      <c r="B5" s="12">
         <v>46119.0</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="12">
         <v>46120.0</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="12">
         <v>46121.0</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="12">
         <v>46122.0</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="10">
         <v>46124.0</v>
       </c>
     </row>
@@ -24732,75 +24732,75 @@
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
-      <c r="D6" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>17</v>
+      <c r="D6" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>23</v>
       </c>
       <c r="F6" s="15"/>
-      <c r="G6" s="18" t="s">
-        <v>22</v>
+      <c r="G6" s="22" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="21.0" customHeight="1">
       <c r="A7" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="10">
+        <v>39</v>
+      </c>
+      <c r="B7" s="12">
         <v>46126.0</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="19">
         <v>46127.0</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="12">
         <v>46128.0</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="12">
         <v>46129.0</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="10">
         <v>46131.0</v>
       </c>
     </row>
     <row r="8" ht="80.25" customHeight="1">
-      <c r="A8" s="24"/>
-      <c r="B8" s="26"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="37"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>40</v>
+      <c r="D8" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>75</v>
       </c>
       <c r="F8" s="15"/>
-      <c r="G8" s="18" t="s">
-        <v>43</v>
+      <c r="G8" s="22" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="10">
+        <v>77</v>
+      </c>
+      <c r="B9" s="12">
         <v>46133.0</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="12">
         <v>46134.0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="10">
         <v>46135.0</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="12">
         <v>46136.0</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="10">
         <v>46138.0</v>
       </c>
     </row>
@@ -24808,8 +24808,8 @@
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="18" t="s">
-        <v>53</v>
+      <c r="D10" s="22" t="s">
+        <v>79</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
@@ -24817,15 +24817,15 @@
     </row>
     <row r="11">
       <c r="A11" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="10">
+        <v>80</v>
+      </c>
+      <c r="B11" s="12">
         <v>46140.0</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="12">
         <v>46141.0</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="12">
         <v>46142.0</v>
       </c>
       <c r="E11" s="8"/>
@@ -24836,15 +24836,15 @@
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
-      <c r="D12" s="35" t="s">
-        <v>56</v>
+      <c r="D12" s="39" t="s">
+        <v>81</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
     </row>
     <row r="13">
-      <c r="D13" s="37"/>
+      <c r="D13" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24875,22 +24875,22 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -24898,201 +24898,201 @@
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
-      <c r="E3" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>85</v>
+      <c r="E3" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
       <c r="A4" s="8"/>
-      <c r="B4" s="43"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" s="45"/>
-      <c r="G4" s="18" t="s">
-        <v>88</v>
+      <c r="E4" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="46"/>
+      <c r="G4" s="22" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="5" ht="20.25" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>96</v>
+        <v>108</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="18" t="s">
-        <v>97</v>
+      <c r="C6" s="22" t="s">
+        <v>111</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="G6" s="45"/>
+      <c r="E6" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="46"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>117</v>
+        <v>135</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
       <c r="A8" s="15"/>
-      <c r="B8" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>131</v>
+      <c r="B8" s="54" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>134</v>
+        <v>161</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>163</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>139</v>
+        <v>170</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>148</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>148</v>
+      <c r="A10" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="G10" s="57" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>165</v>
+        <v>199</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="54" t="s">
-        <v>148</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>148</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>148</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>148</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>148</v>
-      </c>
-      <c r="G12" s="54" t="s">
-        <v>148</v>
+      <c r="A12" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -25122,204 +25122,204 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" ht="91.5" customHeight="1">
+      <c r="A4" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="C4" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="35" t="s">
-        <v>119</v>
+      <c r="E4" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>112</v>
       </c>
       <c r="G4" s="15"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="16" t="s">
+    </row>
+    <row r="6" ht="183.75" customHeight="1">
+      <c r="A6" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="12" t="s">
+      <c r="B6" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="D6" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="27" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="6" ht="183.75" customHeight="1">
-      <c r="A6" s="52" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="52" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E6" s="20" t="s">
+      <c r="F6" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="22" t="s">
         <v>144</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="F7" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" ht="101.25" customHeight="1">
+      <c r="A8" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="48" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="8" ht="101.25" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="C8" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="E8" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="F8" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="G8" s="22" t="s">
         <v>167</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="G9" s="12" t="s">
         <v>178</v>
       </c>
+      <c r="F9" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="10" ht="99.75" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>180</v>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -25328,13 +25328,13 @@
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25365,191 +25365,191 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="10">
+      <c r="C3" s="12">
         <v>46204.0</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="12">
         <v>46205.0</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="12">
         <v>46206.0</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="10">
         <v>46208.0</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="51" t="s">
-        <v>184</v>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="48" t="s">
+        <v>103</v>
       </c>
       <c r="G4" s="15"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="s">
-        <v>185</v>
+        <v>122</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="C5" s="10">
+        <v>123</v>
+      </c>
+      <c r="C5" s="12">
         <v>46211.0</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="12">
         <v>46212.0</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="12">
         <v>46213.0</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" s="10">
         <v>46215.0</v>
       </c>
     </row>
     <row r="6" ht="92.25" customHeight="1">
-      <c r="A6" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>191</v>
+      <c r="A6" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="C7" s="22">
+        <v>143</v>
+      </c>
+      <c r="C7" s="19">
         <v>46218.0</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="12">
         <v>46219.0</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="12">
         <v>46220.0</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="G7" s="56">
+      <c r="F7" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G7" s="55">
         <v>46222.0</v>
       </c>
     </row>
     <row r="8" ht="88.5" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="G8" s="17"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="C9" s="10">
+        <v>172</v>
+      </c>
+      <c r="C9" s="12">
         <v>46225.0</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="56">
         <v>46226.0</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="12">
         <v>46227.0</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="G9" s="10">
         <v>46229.0</v>
       </c>
     </row>
     <row r="10" ht="77.25" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="48" t="s">
-        <v>198</v>
-      </c>
-      <c r="G10" s="48" t="s">
-        <v>199</v>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B11" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="12">
+        <v>46232.0</v>
+      </c>
+      <c r="D11" s="12">
+        <v>46233.0</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>201</v>
-      </c>
-      <c r="C11" s="10">
-        <v>46232.0</v>
-      </c>
-      <c r="D11" s="10">
-        <v>46233.0</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>202</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="40"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="36"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
     </row>
@@ -25582,22 +25582,22 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
@@ -25606,10 +25606,10 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="G3" s="10">
         <v>46236.0</v>
       </c>
     </row>
@@ -25619,162 +25619,162 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
-      <c r="F4" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="G4" s="17"/>
+      <c r="F4" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="21"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="C5" s="10">
+        <v>206</v>
+      </c>
+      <c r="C5" s="12">
         <v>46239.0</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="12">
         <v>46240.0</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="12">
         <v>46241.0</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="10">
         <v>46243.0</v>
       </c>
     </row>
     <row r="6" ht="84.0" customHeight="1">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="G6" s="17"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="G6" s="21"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="C7" s="10">
+        <v>210</v>
+      </c>
+      <c r="C7" s="12">
         <v>46246.0</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="12">
         <v>46247.0</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="12">
         <v>46248.0</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="G7" s="10">
         <v>46250.0</v>
       </c>
     </row>
     <row r="8" ht="93.75" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="G8" s="17"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="C9" s="10">
+        <v>213</v>
+      </c>
+      <c r="C9" s="12">
         <v>46253.0</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="12">
         <v>46254.0</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="12">
         <v>46255.0</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="G9" s="10">
         <v>46257.0</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="51" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="51" t="s">
-        <v>226</v>
-      </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>232</v>
+      <c r="A10" s="21"/>
+      <c r="B10" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="35"/>
+      <c r="D10" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10" s="21"/>
+      <c r="F10" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="C11" s="10">
+        <v>218</v>
+      </c>
+      <c r="C11" s="12">
         <v>46260.0</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="12">
         <v>46261.0</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="12">
         <v>46262.0</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="G11" s="13">
+      <c r="F11" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G11" s="10">
         <v>46264.0</v>
       </c>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="51" t="s">
-        <v>226</v>
-      </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>226</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="G12" s="17"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="G12" s="21"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -25784,7 +25784,7 @@
       <c r="G13" s="8"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
-      <c r="A14" s="17"/>
+      <c r="A14" s="21"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -25821,176 +25821,176 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="8"/>
       <c r="B3" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" s="10">
+        <v>224</v>
+      </c>
+      <c r="C3" s="12">
         <v>46267.0</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="12">
         <v>46268.0</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="12">
         <v>46269.0</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="G3" s="10">
         <v>46271.0</v>
       </c>
     </row>
     <row r="4" ht="85.5" customHeight="1">
       <c r="A4" s="8"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="58" t="s">
-        <v>208</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>213</v>
-      </c>
-      <c r="C5" s="60">
+        <v>228</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="62">
         <v>46274.0</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="63">
         <v>46275.0</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="12">
         <v>46276.0</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="G5" s="10">
         <v>46278.0</v>
       </c>
     </row>
     <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="A6" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>223</v>
-      </c>
-      <c r="C7" s="60">
+        <v>245</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="62">
         <v>46281.0</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="12">
         <v>46282.0</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="12">
         <v>46283.0</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G7" s="10">
         <v>46285.0</v>
       </c>
     </row>
     <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
+      <c r="A8" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="C9" s="10">
+        <v>252</v>
+      </c>
+      <c r="C9" s="12">
         <v>46288.0</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="12">
         <v>46289.0</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="12">
         <v>46290.0</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="G9" s="10">
         <v>46292.0</v>
       </c>
     </row>
     <row r="10" ht="98.25" customHeight="1">
-      <c r="A10" s="62" t="s">
-        <v>237</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="62" t="s">
-        <v>239</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>243</v>
+      <c r="A10" s="67" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="67" t="s">
+        <v>262</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="10">
+        <v>267</v>
+      </c>
+      <c r="C11" s="12">
         <v>46295.0</v>
       </c>
       <c r="D11" s="8"/>
@@ -25999,9 +25999,9 @@
       <c r="G11" s="8"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -33,10 +33,10 @@
     <t>OCAK</t>
   </si>
   <si>
+    <t xml:space="preserve">MART </t>
+  </si>
+  <si>
     <t xml:space="preserve">NİSAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MART </t>
   </si>
   <si>
     <r>
@@ -58,31 +58,56 @@
     </r>
   </si>
   <si>
+    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
   </si>
   <si>
+    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
+  </si>
+  <si>
+    <t>*18 Mart Şehitleri Anma Günü Provası 
+*16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
+  </si>
+  <si>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
+  </si>
+  <si>
     <t>5 Ocak 2026 Pazartesi</t>
   </si>
   <si>
-    <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
+    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>CHP Eğitim 17.00-20.00</t>
   </si>
   <si>
     <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
   </si>
   <si>
     <t>Çeşme Belediyesi Türk Halk Müziği Korosu “ Çeşme’den Türkü Akıyor” 2026 Kış Konseri
@@ -91,34 +116,52 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
+    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
+  </si>
+  <si>
+    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
+  </si>
+  <si>
+    <t>13 Nisan 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
+  </si>
+  <si>
+    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
-    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
+    <t>RAMAZAN BAYRAMI</t>
   </si>
   <si>
     <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
@@ -127,125 +170,56 @@
     <t>YARI YIL ETKİNLİKLERİ</t>
   </si>
   <si>
-    <t>CHP Eğitim 17.00-20.00</t>
-  </si>
-  <si>
-    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
-  </si>
-  <si>
-    <t>13 Nisan 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
-  </si>
-  <si>
-    <t>*18 Mart Şehitleri Anma Günü Provası 
-*16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
+    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
+  </si>
+  <si>
+    <t>19 Ocak 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
   </si>
   <si>
     <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>31 Ocak 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
     <t>Ot Festivali ile ilgili toplantı 14.00</t>
   </si>
   <si>
+    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim tüm gün</t>
+  </si>
+  <si>
+    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
+  </si>
+  <si>
     <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
   </si>
   <si>
+    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
+  </si>
+  <si>
+    <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
+-Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
+  </si>
+  <si>
     <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>19 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
-  </si>
-  <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>31 Ocak 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
-  </si>
-  <si>
-    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
-  </si>
-  <si>
-    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t>28 Şubat 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
-  </si>
-  <si>
-    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
-  </si>
-  <si>
-    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>RAMAZAN BAYRAMI</t>
   </si>
   <si>
     <r>
@@ -271,47 +245,142 @@
     <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
   </si>
   <si>
     <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
   </si>
   <si>
+    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+  </si>
+  <si>
     <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
+    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
+  </si>
+  <si>
+    <t>Belediye TSM Konseri Tüm gün</t>
   </si>
   <si>
     <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
   </si>
   <si>
-    <t>CHP İlçe Eğitim tüm gün</t>
-  </si>
-  <si>
-    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
-  </si>
-  <si>
-    <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
--Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
+  </si>
+  <si>
+    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>28 Şubat 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
+  </si>
+  <si>
+    <t>MAYIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>3 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
+  </si>
+  <si>
+    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
   <si>
+    <t>10 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
+  </si>
+  <si>
+    <t>21.30 konser provası Başkan ile</t>
+  </si>
+  <si>
+    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
+  </si>
+  <si>
     <t xml:space="preserve">HAZİRAN </t>
   </si>
   <si>
-    <t>MAYIS</t>
+    <t>11 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>16 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
   </si>
   <si>
     <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
@@ -320,34 +389,69 @@
     <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
   </si>
   <si>
+    <t>Bilgiç Anaokulu Prova 
+10.30-15.30</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
   </si>
   <si>
+    <t xml:space="preserve">Bilgiç Anaokulu Prova 
+10.30-15.30                                               </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
+    <t>-Bilgiç ortaokulu 09.00-12.00
+-Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
+  </si>
+  <si>
+    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
+"No Mans Land" Yetişkin Oyunu 20.00
+onaylandı.</t>
+  </si>
+  <si>
     <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
+  </si>
+  <si>
     <t>7 HAZİRAN 2026 PAZAR</t>
   </si>
   <si>
-    <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
+    <t>18 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
   </si>
   <si>
     <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
   </si>
   <si>
-    <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>3 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
+    <t>23 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t>24 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro</t>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
   </si>
   <si>
     <r>
@@ -372,6 +476,29 @@
         <rFont val="Arial"/>
         <color theme="1"/>
       </rPr>
+      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
+    </r>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
+  </si>
+  <si>
+    <t>BAYRAM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
       <t xml:space="preserve">Bilgiç İlkokulu 1. Sınıf Okuma Bayramı  prova 09.30-15.00                         </t>
     </r>
     <r>
@@ -388,42 +515,33 @@
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
   </si>
   <si>
-    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>10 MAYIS 2026 PAZAR</t>
+    <t>25 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
   </si>
   <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
   </si>
   <si>
-    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
+    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
   </si>
   <si>
     <t xml:space="preserve">8 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t>21.30 konser provası Başkan ile</t>
-  </si>
-  <si>
     <t xml:space="preserve">9 HAZİRAN 2026 SALI </t>
   </si>
   <si>
@@ -445,22 +563,7 @@
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00</t>
   </si>
   <si>
-    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
-  </si>
-  <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00                                                        "SEVGİLİ DOKTOR"  20.00</t>
-  </si>
-  <si>
-    <t>11 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
   </si>
   <si>
     <r>
@@ -481,15 +584,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t>16 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
     <t>-SERTUR KOOPERATİF TOPLANTISI HALUK BEY 05336460236 
 15.00'a kadar
 - Kent Enstitüsü Prova</t>
@@ -507,15 +601,15 @@
     <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
-  </si>
-  <si>
     <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
+    <t xml:space="preserve">TEMMUZ </t>
+  </si>
+  <si>
     <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
@@ -526,10 +620,6 @@
   </si>
   <si>
     <t>Atatürk Lisesi tiyatro prova</t>
-  </si>
-  <si>
-    <t>Bilgiç Anaokulu Prova 
-10.30-15.30</t>
   </si>
   <si>
     <t>Atatürk Lisesi Oyun Günü</t>
@@ -557,125 +647,35 @@
     <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">Bilgiç Anaokulu Prova 
-10.30-15.30                                               </t>
-  </si>
-  <si>
     <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
-    <t>-Bilgiç ortaokulu 09.00-12.00
--Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
-  </si>
-  <si>
     <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
     <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
-"No Mans Land" Yetişkin Oyunu 20.00
-onaylandı.</t>
-  </si>
-  <si>
     <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
-  </si>
-  <si>
-    <t>18 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t>23 MAYIS 2026 CUMARTESİ</t>
   </si>
   <si>
     <t>Reyhan Cici Piyano Dinletisi
 Ödendi. Dilekçe geldi. Tel no:5320631925 12.00-20.00</t>
   </si>
   <si>
-    <t>24 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
     <t>MHP 15. Olağan Kongre Toplantısı</t>
   </si>
   <si>
-    <t>Özhan Bakadur tiyatro</t>
-  </si>
-  <si>
     <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEMMUZ </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
-    </r>
-  </si>
-  <si>
-    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
-  </si>
-  <si>
-    <t>BAYRAM</t>
-  </si>
-  <si>
-    <t>25 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
   </si>
   <si>
     <t>Latin Katolik Kilisesi Ayin 
@@ -745,35 +745,16 @@
     <t>AĞUSTOS</t>
   </si>
   <si>
-    <t xml:space="preserve">EYLÜL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
-Haydar Ali tel no: 5527151935</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 AĞUSTOS 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">8 AĞUSTOS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
   </si>
   <si>
     <t>-Orkent Sitesi 11.00-13.00 ödendi.
@@ -799,6 +780,51 @@
     <t xml:space="preserve">22 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">Ritim 10.00-12.00 </t>
+  </si>
+  <si>
+    <t>Deniz Tatil Sitesi Toplantı 11.00-18.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 AĞUSTOS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 AĞUSTOS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 AĞUSTOS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORUK BELDESİ, ARSA VE YAPI KOOPERATİFİ                                 13.00-15.00  </t>
+  </si>
+  <si>
+    <t>-Saygun Sanat Şirinler Müzikali 2 seans 
+-Latin Katolik Kilisesi Ayin 
+18.30(farklı odalar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EYLÜL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
+Haydar Ali tel no: 5527151935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
@@ -812,9 +838,6 @@
   </si>
   <si>
     <t xml:space="preserve">19 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ritim 10.00-12.00 </t>
   </si>
   <si>
     <t xml:space="preserve">09:00-16:00 
@@ -833,39 +856,16 @@
     <t xml:space="preserve">21 EYLÜL 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t>Deniz Tatil Sitesi Toplantı 11.00-18.00</t>
-  </si>
-  <si>
     <t xml:space="preserve">22 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">24 AĞUSTOS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 AĞUSTOS 2026 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">26 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">29 AĞUSTOS 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t>Osman Uysal Konser Prova 18.00-22.00</t>
   </si>
   <si>
-    <t xml:space="preserve">DORUK BELDESİ, ARSA VE YAPI KOOPERATİFİ                                 13.00-15.00  </t>
-  </si>
-  <si>
-    <t>-Saygun Sanat Şirinler Müzikali 2 seans 
--Latin Katolik Kilisesi Ayin 
-18.30(farklı odalar)</t>
-  </si>
-  <si>
     <t>Osman Uysal Konser 20.30 (tüm gün)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
     <r>
@@ -1096,21 +1096,24 @@
     <t xml:space="preserve">26 KASIM 2026 PERŞEMBE </t>
   </si>
   <si>
+    <t xml:space="preserve">27 KASIM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 KASIM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 KASIM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Tuncay Hoca Çsm</t>
+  </si>
+  <si>
+    <t>30 KASIM 2026 PAZARTESİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARALIK </t>
   </si>
   <si>
-    <t xml:space="preserve">27 KASIM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 KASIM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 KASIM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Tuncay Hoca Çsm</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 ARALIK 2026 SALI </t>
   </si>
   <si>
@@ -1127,9 +1130,6 @@
   </si>
   <si>
     <t xml:space="preserve">6 ARALIK 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>30 KASIM 2026 PAZARTESİ</t>
   </si>
   <si>
     <t xml:space="preserve">7 ARALIK 2026 PAZARTESİ </t>
@@ -1224,6 +1224,13 @@
     </font>
     <font>
       <b/>
+      <sz val="13.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="14.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1232,19 +1239,7 @@
     <font/>
     <font>
       <b/>
-      <sz val="13.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1257,7 +1252,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1269,18 +1263,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFFFFFFF"/>
+      <b/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFEFEFEF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <color rgb="FF38761D"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FFEFEFEF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1336,14 +1336,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6B26B"/>
-        <bgColor rgb="FFF6B26B"/>
+        <fgColor rgb="FFE69138"/>
+        <bgColor rgb="FFE69138"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE69138"/>
-        <bgColor rgb="FFE69138"/>
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF6B26B"/>
       </patternFill>
     </fill>
     <fill>
@@ -1444,164 +1444,164 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="4" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="4" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1616,10 +1616,10 @@
     <xf borderId="4" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1628,10 +1628,10 @@
     <xf borderId="4" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1910,212 +1910,212 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="13">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="12">
         <v>46023.0</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>46024.0</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="12">
         <v>46026.0</v>
       </c>
     </row>
     <row r="4" ht="95.25" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="A5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="13">
         <v>46028.0</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <v>46029.0</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>46030.0</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>46031.0</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="12">
         <v>46033.0</v>
       </c>
     </row>
     <row r="6" ht="97.5" customHeight="1">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="21" t="s">
-        <v>18</v>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="24" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="A7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="13">
         <v>46035.0</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="25">
         <v>46036.0</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="25">
         <v>46037.0</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>46038.0</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="24">
+      <c r="F7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="27">
         <v>46040.0</v>
       </c>
     </row>
     <row r="8" ht="69.0" customHeight="1">
-      <c r="A8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>27</v>
+      <c r="A8" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="14">
+      <c r="A9" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="13">
         <v>46042.0</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="25">
         <v>46043.0</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="25">
         <v>46044.0</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <v>46045.0</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="12">
         <v>46047.0</v>
       </c>
     </row>
     <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="27"/>
+      <c r="A10" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="18"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="14">
+      <c r="A11" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="13">
         <v>46049.0</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="25">
         <v>46050.0</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="25">
         <v>46051.0</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <v>46052.0</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="11"/>
+      <c r="F11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="34"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2146,186 +2146,186 @@
       <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="64" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="18" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="16" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="4" ht="84.0" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="53" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="50" t="s">
         <v>251</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="G4" s="50" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="16" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="65" t="s">
         <v>259</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
       <c r="F6" s="66" t="s">
         <v>259</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="18"/>
       <c r="L6" s="67"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="16" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
       <c r="F8" s="68" t="s">
         <v>267</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="16" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="10" ht="100.5" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="G11" s="11"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="11"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2354,193 +2354,193 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="18" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="17" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="27"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="16" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="16" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>297</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>300</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="16" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="F11" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="G11" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="G11" s="15" t="s">
+    </row>
+    <row r="12" ht="103.5" customHeight="1">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="69" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="12" ht="103.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="69" t="s">
+    <row r="13">
+      <c r="A13" s="17" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
-      <c r="A14" s="27"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2571,175 +2571,175 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>308</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="48" t="s">
+        <v>313</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="C3" s="18" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="C3" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="D3" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="E3" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>318</v>
       </c>
+      <c r="G3" s="16" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="16" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="16" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="16" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>343</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2767,14 +2767,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="63.75" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -2791,14 +2791,14 @@
       <c r="T1" s="9"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -2815,13 +2815,13 @@
       <c r="T2" s="9"/>
     </row>
     <row r="3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="19">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="22">
         <v>46054.0</v>
       </c>
       <c r="H3" s="9"/>
@@ -2839,13 +2839,13 @@
       <c r="T3" s="9"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="17"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="15"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -2861,25 +2861,25 @@
       <c r="T4" s="9"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="28">
+      <c r="A5" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="32">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="32">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="32">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="32">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="19">
+      <c r="F5" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="22">
         <v>46061.0</v>
       </c>
       <c r="H5" s="9"/>
@@ -2897,18 +2897,18 @@
       <c r="T5" s="9"/>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>37</v>
+      <c r="A6" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
@@ -2925,25 +2925,25 @@
       <c r="T6" s="9"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="28">
+      <c r="A7" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="32">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="32">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="32">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="32">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="19">
+      <c r="F7" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="22">
         <v>46068.0</v>
       </c>
       <c r="H7" s="9"/>
@@ -2961,22 +2961,22 @@
       <c r="T7" s="9"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="32" t="s">
-        <v>46</v>
+      <c r="A8" s="19"/>
+      <c r="B8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="38" t="s">
+        <v>72</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -2993,25 +2993,25 @@
       <c r="T8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="28">
+      <c r="A9" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="32">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="32">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="32">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="32">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="F9" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="22">
         <v>46075.0</v>
       </c>
       <c r="H9" s="9"/>
@@ -3029,18 +3029,18 @@
       <c r="T9" s="9"/>
     </row>
     <row r="10" ht="89.25" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>57</v>
+      <c r="A10" s="15"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -3057,25 +3057,25 @@
       <c r="T10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="28">
+      <c r="A11" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="32">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="32">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="32">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="32">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="16"/>
+      <c r="F11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="19"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -3091,15 +3091,15 @@
       <c r="T11" s="9"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
@@ -24412,222 +24412,222 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="13">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="12">
         <v>46082.0</v>
       </c>
     </row>
     <row r="4" ht="69.0" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="17" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="13">
+        <v>46084.0</v>
+      </c>
+      <c r="C5" s="13">
+        <v>46085.0</v>
+      </c>
+      <c r="D5" s="13">
+        <v>46086.0</v>
+      </c>
+      <c r="E5" s="13">
+        <v>46087.0</v>
+      </c>
+      <c r="F5" s="16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="G5" s="12">
+        <v>46089.0</v>
+      </c>
+    </row>
+    <row r="6" ht="113.25" customHeight="1">
+      <c r="A6" s="10"/>
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="14">
-        <v>46084.0</v>
-      </c>
-      <c r="C5" s="14">
-        <v>46085.0</v>
-      </c>
-      <c r="D5" s="14">
-        <v>46086.0</v>
-      </c>
-      <c r="E5" s="14">
-        <v>46087.0</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="13">
-        <v>46089.0</v>
-      </c>
-    </row>
-    <row r="6" ht="113.25" customHeight="1">
-      <c r="A6" s="11"/>
-      <c r="B6" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="31"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="A7" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="13">
         <v>46091.0</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <v>46092.0</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>46093.0</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>46094.0</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="12">
         <v>46096.0</v>
       </c>
     </row>
     <row r="8" ht="87.0" customHeight="1">
-      <c r="A8" s="11"/>
-      <c r="B8" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="17" t="s">
+      <c r="A8" s="10"/>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="13">
+        <v>46098.0</v>
+      </c>
+      <c r="C9" s="12">
+        <v>46099.0</v>
+      </c>
+      <c r="D9" s="25">
+        <v>46100.0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>46101.0</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="12">
+        <v>46103.0</v>
+      </c>
+    </row>
+    <row r="10" ht="96.0" customHeight="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="13">
+        <v>46105.0</v>
+      </c>
+      <c r="C11" s="13">
+        <v>46106.0</v>
+      </c>
+      <c r="D11" s="13">
+        <v>46107.0</v>
+      </c>
+      <c r="E11" s="13">
+        <v>46108.0</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="12">
+        <v>46110.0</v>
+      </c>
+    </row>
+    <row r="12" ht="91.5" customHeight="1">
+      <c r="A12" s="10"/>
+      <c r="B12" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="11"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="14">
-        <v>46098.0</v>
-      </c>
-      <c r="C9" s="13">
-        <v>46099.0</v>
-      </c>
-      <c r="D9" s="23">
-        <v>46100.0</v>
-      </c>
-      <c r="E9" s="14">
-        <v>46101.0</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="13">
-        <v>46103.0</v>
-      </c>
-    </row>
-    <row r="10" ht="96.0" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="14">
-        <v>46105.0</v>
-      </c>
-      <c r="C11" s="14">
-        <v>46106.0</v>
-      </c>
-      <c r="D11" s="14">
-        <v>46107.0</v>
-      </c>
-      <c r="E11" s="14">
-        <v>46108.0</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="13">
-        <v>46110.0</v>
-      </c>
-    </row>
-    <row r="12" ht="91.5" customHeight="1">
-      <c r="A12" s="11"/>
-      <c r="B12" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>46112.0</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" ht="95.25" customHeight="1">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -24656,195 +24656,195 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="14">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="13">
         <v>46113.0</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>46114.0</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>46115.0</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="12">
         <v>46117.0</v>
       </c>
     </row>
     <row r="4" ht="99.75" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="11"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="13">
         <v>46119.0</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <v>46120.0</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>46121.0</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>46122.0</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>46124.0</v>
       </c>
     </row>
     <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="26" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="21.0" customHeight="1">
+      <c r="A7" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>46126.0</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="25">
         <v>46127.0</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>46128.0</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>46129.0</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="12">
         <v>46131.0</v>
       </c>
     </row>
     <row r="8" ht="80.25" customHeight="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="25" t="s">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="13">
+        <v>46133.0</v>
+      </c>
+      <c r="C9" s="13">
+        <v>46134.0</v>
+      </c>
+      <c r="D9" s="12">
+        <v>46135.0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>46136.0</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="12">
+        <v>46138.0</v>
+      </c>
+    </row>
+    <row r="10" ht="92.25" customHeight="1">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="14">
-        <v>46133.0</v>
-      </c>
-      <c r="C9" s="14">
-        <v>46134.0</v>
-      </c>
-      <c r="D9" s="13">
-        <v>46135.0</v>
-      </c>
-      <c r="E9" s="14">
-        <v>46136.0</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="13">
-        <v>46138.0</v>
-      </c>
-    </row>
-    <row r="10" ht="92.25" customHeight="1">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="B11" s="13">
+        <v>46140.0</v>
+      </c>
+      <c r="C11" s="13">
+        <v>46141.0</v>
+      </c>
+      <c r="D11" s="13">
+        <v>46142.0</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" ht="98.25" customHeight="1">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="14">
-        <v>46140.0</v>
-      </c>
-      <c r="C11" s="14">
-        <v>46141.0</v>
-      </c>
-      <c r="D11" s="14">
-        <v>46142.0</v>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13">
-      <c r="D13" s="39"/>
+      <c r="D13" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24875,224 +24875,224 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="15" t="s">
+      <c r="G3" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" customHeight="1">
+      <c r="A4" s="10"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="45"/>
+      <c r="G4" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" ht="20.25" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="G3" s="15" t="s">
+      <c r="F5" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="45" t="s">
+    <row r="6" ht="91.5" customHeight="1">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="25" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="45"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="F7" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="G7" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G5" s="15" t="s">
+    </row>
+    <row r="8" ht="97.5" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="49" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="F6" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="G6" s="46"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="C8" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="F9" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="G9" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="G7" s="15" t="s">
+    </row>
+    <row r="10" ht="93.75" customHeight="1">
+      <c r="A10" s="20" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="F8" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>175</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>175</v>
+      <c r="B10" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>183</v>
+      <c r="A11" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="54" t="s">
-        <v>175</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>175</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>175</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>175</v>
-      </c>
-      <c r="G12" s="54" t="s">
-        <v>175</v>
+      <c r="A12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -25122,219 +25122,219 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>91</v>
+      <c r="A3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="G4" s="17"/>
+      <c r="A4" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="15"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>117</v>
+      <c r="A5" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="6" ht="183.75" customHeight="1">
-      <c r="A6" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>131</v>
+      <c r="A6" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>139</v>
+      <c r="A7" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="8" ht="101.25" customHeight="1">
-      <c r="A8" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="B8" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>147</v>
+      <c r="A8" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>157</v>
+      <c r="A9" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="10" ht="99.75" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>167</v>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="A11" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25365,74 +25365,74 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="14">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="13">
         <v>46204.0</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>46205.0</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>46206.0</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="12">
         <v>46208.0</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="53" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="17"/>
+      <c r="G4" s="15"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <v>46211.0</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>46212.0</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>46213.0</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>46215.0</v>
       </c>
     </row>
@@ -25440,38 +25440,38 @@
       <c r="A6" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="53" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="20" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="25">
         <v>46218.0</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>46219.0</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>46220.0</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="16" t="s">
         <v>194</v>
       </c>
       <c r="G7" s="56">
@@ -25479,79 +25479,79 @@
       </c>
     </row>
     <row r="8" ht="88.5" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="53" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <v>46225.0</v>
       </c>
       <c r="D9" s="57">
         <v>46226.0</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <v>46227.0</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>46229.0</v>
       </c>
     </row>
     <row r="10" ht="77.25" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="50" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="G10" s="50" t="s">
+      <c r="G10" s="47" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <v>46232.0</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>46233.0</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25582,215 +25582,215 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="15" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G3" s="12">
+        <v>46236.0</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" customHeight="1">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="G3" s="13">
-        <v>46236.0</v>
-      </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="53" t="s">
+      <c r="C5" s="13">
+        <v>46239.0</v>
+      </c>
+      <c r="D5" s="13">
+        <v>46240.0</v>
+      </c>
+      <c r="E5" s="13">
+        <v>46241.0</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46243.0</v>
+      </c>
+    </row>
+    <row r="6" ht="84.0" customHeight="1">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="13">
+        <v>46246.0</v>
+      </c>
+      <c r="D7" s="13">
+        <v>46247.0</v>
+      </c>
+      <c r="E7" s="13">
+        <v>46248.0</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="G7" s="12">
+        <v>46250.0</v>
+      </c>
+    </row>
+    <row r="8" ht="93.75" customHeight="1">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="27"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="C5" s="14">
-        <v>46239.0</v>
-      </c>
-      <c r="D5" s="14">
-        <v>46240.0</v>
-      </c>
-      <c r="E5" s="14">
-        <v>46241.0</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="G5" s="13">
-        <v>46243.0</v>
-      </c>
-    </row>
-    <row r="6" ht="84.0" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="25" t="s">
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="13">
+        <v>46253.0</v>
+      </c>
+      <c r="D9" s="13">
+        <v>46254.0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>46255.0</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="G9" s="12">
+        <v>46257.0</v>
+      </c>
+    </row>
+    <row r="10" ht="93.75" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="C10" s="36"/>
+      <c r="D10" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G10" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="C7" s="14">
-        <v>46246.0</v>
-      </c>
-      <c r="D7" s="14">
-        <v>46247.0</v>
-      </c>
-      <c r="E7" s="14">
-        <v>46248.0</v>
-      </c>
-      <c r="F7" s="15" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="G7" s="13">
-        <v>46250.0</v>
-      </c>
-    </row>
-    <row r="8" ht="93.75" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="53" t="s">
-        <v>184</v>
-      </c>
-      <c r="G8" s="27"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="C11" s="13">
+        <v>46260.0</v>
+      </c>
+      <c r="D11" s="13">
+        <v>46261.0</v>
+      </c>
+      <c r="E11" s="13">
+        <v>46262.0</v>
+      </c>
+      <c r="F11" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="14">
-        <v>46253.0</v>
-      </c>
-      <c r="D9" s="14">
-        <v>46254.0</v>
-      </c>
-      <c r="E9" s="14">
-        <v>46255.0</v>
-      </c>
-      <c r="F9" s="15" t="s">
+      <c r="G11" s="12">
+        <v>46264.0</v>
+      </c>
+    </row>
+    <row r="12" ht="94.5" customHeight="1">
+      <c r="A12" s="18"/>
+      <c r="B12" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="G9" s="13">
-        <v>46257.0</v>
-      </c>
-    </row>
-    <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="53" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="53" t="s">
-        <v>226</v>
-      </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="53" t="s">
-        <v>184</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C11" s="14">
-        <v>46260.0</v>
-      </c>
-      <c r="D11" s="14">
-        <v>46261.0</v>
-      </c>
-      <c r="E11" s="14">
-        <v>46262.0</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="G11" s="13">
-        <v>46264.0</v>
-      </c>
-    </row>
-    <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="53" t="s">
-        <v>226</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="E12" s="53" t="s">
-        <v>226</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="G12" s="27"/>
+      <c r="E12" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="G12" s="18"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
+      <c r="A13" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
-      <c r="A14" s="27"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25821,62 +25821,62 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="48" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" s="14">
+      <c r="A3" s="10"/>
+      <c r="B3" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="13">
         <v>46267.0</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>46268.0</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>46269.0</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="G3" s="12">
         <v>46271.0</v>
       </c>
     </row>
     <row r="4" ht="85.5" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="58" t="s">
-        <v>209</v>
-      </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+        <v>226</v>
+      </c>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>212</v>
+      <c r="A5" s="17" t="s">
+        <v>227</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="C5" s="60">
         <v>46274.0</v>
@@ -25884,128 +25884,128 @@
       <c r="D5" s="61">
         <v>46275.0</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>46276.0</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="G5" s="12">
         <v>46278.0</v>
       </c>
     </row>
     <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
+      <c r="A6" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>223</v>
+      <c r="A7" s="17" t="s">
+        <v>231</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C7" s="60">
         <v>46281.0</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>46282.0</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>46283.0</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="G7" s="12">
         <v>46285.0</v>
       </c>
     </row>
     <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
+      <c r="A8" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C9" s="14">
+      <c r="A9" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" s="13">
         <v>46288.0</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <v>46289.0</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <v>46290.0</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="G9" s="12">
         <v>46292.0</v>
       </c>
     </row>
     <row r="10" ht="98.25" customHeight="1">
       <c r="A10" s="62" t="s">
-        <v>237</v>
-      </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
+        <v>240</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="62" t="s">
-        <v>240</v>
-      </c>
-      <c r="F10" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="F10" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="20" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <v>46295.0</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -58,56 +58,25 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
     <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
   </si>
   <si>
     <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
   </si>
   <si>
+    <t>5 Ocak 2026 Pazartesi</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
-  </si>
-  <si>
-    <t>*18 Mart Şehitleri Anma Günü Provası 
-*16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
-  </si>
-  <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
-  </si>
-  <si>
-    <t>5 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>CHP Eğitim 17.00-20.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
   </si>
   <si>
     <t>Çeşme Belediyesi Türk Halk Müziği Korosu “ Çeşme’den Türkü Akıyor” 2026 Kış Konseri
@@ -116,110 +85,168 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
+    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
+  </si>
+  <si>
+    <t>*18 Mart Şehitleri Anma Günü Provası 
+*16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+  </si>
+  <si>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
+  </si>
+  <si>
+    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
+  </si>
+  <si>
     <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
   </si>
   <si>
+    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+  </si>
+  <si>
     <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
   </si>
   <si>
+    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
   </si>
   <si>
+    <t>YARI YIL ETKİNLİKLERİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t>RAMAZAN BAYRAMI</t>
+  </si>
+  <si>
+    <t>19 Ocak 2026 Pazartesi</t>
+  </si>
+  <si>
     <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
   </si>
   <si>
     <t>13 Nisan 2026 Pazartesi</t>
   </si>
   <si>
-    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Ot Festivali ile ilgili toplantı 14.00</t>
   </si>
   <si>
     <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
-    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>RAMAZAN BAYRAMI</t>
-  </si>
-  <si>
-    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
-  </si>
-  <si>
-    <t>YARI YIL ETKİNLİKLERİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
-  </si>
-  <si>
-    <t>19 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
     <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
+    <t>CHP İlçe Eğitim tüm gün</t>
+  </si>
+  <si>
+    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
+  </si>
+  <si>
+    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
+  </si>
+  <si>
+    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
   </si>
   <si>
     <t>31 Ocak 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>Ot Festivali ile ilgili toplantı 14.00</t>
-  </si>
-  <si>
-    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim tüm gün</t>
-  </si>
-  <si>
-    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
-  </si>
-  <si>
-    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
-  </si>
-  <si>
-    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
   </si>
   <si>
     <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
 -Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
   </si>
   <si>
-    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
+    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
+  </si>
+  <si>
+    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
+  </si>
+  <si>
+    <t>Belediye TSM Konseri Tüm gün</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
   </si>
   <si>
     <r>
@@ -242,216 +269,85 @@
     <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
   </si>
   <si>
+    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
+    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
   </si>
   <si>
     <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
   </si>
   <si>
+    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
+  </si>
+  <si>
+    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
+  </si>
+  <si>
     <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
   </si>
   <si>
-    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>28 Şubat 2026 Cumartesi</t>
   </si>
   <si>
     <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
-  </si>
-  <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
+    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
   </si>
   <si>
     <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
   </si>
   <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
-  </si>
-  <si>
-    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>28 Şubat 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
+    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAZİRAN </t>
   </si>
   <si>
     <t>MAYIS</t>
   </si>
   <si>
+    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t>7 HAZİRAN 2026 PAZAR</t>
+  </si>
+  <si>
     <t>3 MAYIS 2026 PAZAR</t>
   </si>
   <si>
+    <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
+  </si>
+  <si>
     <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
-  </si>
-  <si>
-    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
-  </si>
-  <si>
-    <t>10 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
-  </si>
-  <si>
-    <t>21.30 konser provası Başkan ile</t>
-  </si>
-  <si>
-    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAZİRAN </t>
-  </si>
-  <si>
-    <t>11 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t>16 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t>Bilgiç Anaokulu Prova 
-10.30-15.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bilgiç Anaokulu Prova 
-10.30-15.30                                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t>-Bilgiç ortaokulu 09.00-12.00
--Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
-  </si>
-  <si>
-    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
-"No Mans Land" Yetişkin Oyunu 20.00
-onaylandı.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
-  </si>
-  <si>
-    <t>7 HAZİRAN 2026 PAZAR</t>
-  </si>
-  <si>
-    <t>18 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
-  </si>
-  <si>
-    <t>23 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t>24 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro</t>
-  </si>
-  <si>
-    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
   </si>
   <si>
     <r>
@@ -476,29 +372,6 @@
         <rFont val="Arial"/>
         <color theme="1"/>
       </rPr>
-      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
-    </r>
-  </si>
-  <si>
-    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
-  </si>
-  <si>
-    <t>BAYRAM</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
       <t xml:space="preserve">Bilgiç İlkokulu 1. Sınıf Okuma Bayramı  prova 09.30-15.00                         </t>
     </r>
     <r>
@@ -515,28 +388,31 @@
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
   </si>
   <si>
-    <t>25 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
+    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
   </si>
   <si>
-    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
+    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>10 MAYIS 2026 PAZAR</t>
   </si>
   <si>
     <t xml:space="preserve">8 HAZİRAN 2026 PAZARTESİ </t>
@@ -548,6 +424,9 @@
     <t xml:space="preserve">10 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
+    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
+  </si>
+  <si>
     <t xml:space="preserve">11 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
@@ -557,13 +436,25 @@
     <t>13 HAZİRAN 2026 CUMARTESİ</t>
   </si>
   <si>
+    <t>21.30 konser provası Başkan ile</t>
+  </si>
+  <si>
     <t xml:space="preserve">14 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00</t>
   </si>
   <si>
+    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
+  </si>
+  <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00                                                        "SEVGİLİ DOKTOR"  20.00</t>
+  </si>
+  <si>
+    <t>11 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
   </si>
   <si>
     <r>
@@ -584,14 +475,32 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
     <t>-SERTUR KOOPERATİF TOPLANTISI HALUK BEY 05336460236 
 15.00'a kadar
 - Kent Enstitüsü Prova</t>
   </si>
   <si>
+    <t>16 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
     <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
   </si>
   <si>
+    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
     <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
   </si>
   <si>
@@ -601,37 +510,66 @@
     <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
   </si>
   <si>
+    <t>Bilgiç Anaokulu Prova 
+10.30-15.30</t>
+  </si>
+  <si>
     <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
-    <t xml:space="preserve">TEMMUZ </t>
-  </si>
-  <si>
     <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">Bilgiç Anaokulu Prova 
+10.30-15.30                                               </t>
+  </si>
+  <si>
     <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
+    <t>-Bilgiç ortaokulu 09.00-12.00
+-Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
+  </si>
+  <si>
+    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
+"No Mans Land" Yetişkin Oyunu 20.00
+onaylandı.</t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
+  </si>
+  <si>
     <t>Atatürk Lisesi tiyatro prova</t>
   </si>
   <si>
+    <t>18 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
     <t>Atatürk Lisesi Oyun Günü</t>
   </si>
   <si>
+    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
+  </si>
+  <si>
     <t>Osman Uysal Prova opsiyon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
 sabahtan 21.00'a kadar</t>
   </si>
   <si>
+    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
     <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
   </si>
   <si>
@@ -641,25 +579,63 @@
     <t>Doğu Der Toplantı</t>
   </si>
   <si>
+    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>23 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t>24 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
     <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
+    <t>Özhan Bakadur tiyatro</t>
+  </si>
+  <si>
     <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
     <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
+    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
+  </si>
+  <si>
     <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
+    </r>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
+  </si>
+  <si>
+    <t>BAYRAM</t>
   </si>
   <si>
     <t>Reyhan Cici Piyano Dinletisi
@@ -669,10 +645,34 @@
     <t>MHP 15. Olağan Kongre Toplantısı</t>
   </si>
   <si>
+    <t>25 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMMUZ </t>
   </si>
   <si>
     <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
@@ -748,6 +748,12 @@
     <t xml:space="preserve">1 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">EYLÜL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -755,6 +761,9 @@
   </si>
   <si>
     <t xml:space="preserve">8 AĞUSTOS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>-Orkent Sitesi 11.00-13.00 ödendi.
@@ -768,15 +777,25 @@
     <t xml:space="preserve">11 AĞUSTOS 2026 SALI </t>
   </si>
   <si>
+    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
+Haydar Ali tel no: 5527151935</t>
+  </si>
+  <si>
     <t xml:space="preserve">15 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">17 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">18 AĞUSTOS 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">22 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
@@ -793,6 +812,12 @@
   </si>
   <si>
     <t xml:space="preserve">29 AĞUSTOS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>Belediye Meclis 15.00 Tüm alan</t>
   </si>
   <si>
     <t xml:space="preserve">DORUK BELDESİ, ARSA VE YAPI KOOPERATİFİ                                 13.00-15.00  </t>
@@ -804,31 +829,6 @@
   </si>
   <si>
     <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EYLÜL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
-Haydar Ali tel no: 5527151935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Belediye Meclis 15.00 Tüm alan</t>
   </si>
   <si>
     <t xml:space="preserve">14 EYLÜL 2026 PAZARTESİ </t>
@@ -1036,6 +1036,9 @@
     <t xml:space="preserve">6 KASIM 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">ARALIK </t>
+  </si>
+  <si>
     <t xml:space="preserve">7 KASIM 2026 CUMARTESİ </t>
   </si>
   <si>
@@ -1063,6 +1066,18 @@
     <t xml:space="preserve">15 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t xml:space="preserve">1 ARALIK 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 ARALIK 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 ARALIK 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 ARALIK 2026 CUMA </t>
+  </si>
+  <si>
     <t xml:space="preserve">16 KASIM 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -1072,12 +1087,18 @@
     <t xml:space="preserve">18 KASIM 2026 ÇARŞAMBA </t>
   </si>
   <si>
+    <t xml:space="preserve">5 ARALIK 2026 CUMA RTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">19 KASIM 2026 PERŞEMBE </t>
   </si>
   <si>
     <t xml:space="preserve">20 KASIM 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">6 ARALIK 2026 PAZAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">21 KASIM 2026 CUMARTESİ </t>
   </si>
   <si>
@@ -1093,91 +1114,70 @@
     <t xml:space="preserve">25 KASIM 2026 ÇARŞAMBA </t>
   </si>
   <si>
+    <t xml:space="preserve">7 ARALIK 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">26 KASIM 2026 PERŞEMBE </t>
   </si>
   <si>
+    <t xml:space="preserve">8 ARALIK 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">27 KASIM 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">9 ARALIK 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
     <t xml:space="preserve">28 KASIM 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">10 ARALIK 2026 PERŞEMBE </t>
+  </si>
+  <si>
     <t xml:space="preserve">29 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t xml:space="preserve">11 ARALIK 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 ARALIK 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 ARALIK 2026 PAZAR </t>
+  </si>
+  <si>
     <t>Tuncay Hoca Çsm</t>
   </si>
   <si>
+    <t xml:space="preserve">14 ARALIK 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 ARALIK 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 ARALIK 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 ARALIK 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 ARALIK 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 ARALIK 2026 CUARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 ARALIK 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 ARALIK 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 ARALIK 2026 SALI </t>
+  </si>
+  <si>
     <t>30 KASIM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARALIK </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 ARALIK 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 ARALIK 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 ARALIK 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 ARALIK 2026 CUMA RTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 ARALIK 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 ARALIK 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 ARALIK 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 ARALIK 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 ARALIK 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 ARALIK 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 ARALIK 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 ARALIK 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 ARALIK 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 ARALIK 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 ARALIK 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 ARALIK 2026 CUARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 ARALIK 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 ARALIK 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 ARALIK 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">23 ARALIK 2026 ÇARŞAMBA </t>
@@ -1269,13 +1269,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFFFFFFF"/>
+      <b/>
+      <color rgb="FF38761D"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF38761D"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1443,20 +1443,20 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -1466,55 +1466,70 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="4" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1522,29 +1537,14 @@
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1558,6 +1558,9 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
@@ -1568,14 +1571,20 @@
     <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="4" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1585,15 +1594,6 @@
     </xf>
     <xf borderId="4" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1637,7 +1637,7 @@
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="12" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="12" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1910,210 +1910,210 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
       <c r="D3" s="12">
         <v>46023.0</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="14">
         <v>46024.0</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>13</v>
+      <c r="F3" s="15" t="s">
+        <v>6</v>
       </c>
       <c r="G3" s="12">
         <v>46026.0</v>
       </c>
     </row>
     <row r="4" ht="95.25" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="14">
         <v>46028.0</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="14">
         <v>46029.0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="14">
         <v>46030.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="14">
         <v>46031.0</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>20</v>
+      <c r="F5" s="15" t="s">
+        <v>11</v>
       </c>
       <c r="G5" s="12">
         <v>46033.0</v>
       </c>
     </row>
     <row r="6" ht="97.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="24" t="s">
-        <v>29</v>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="20" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="14">
+        <v>46035.0</v>
+      </c>
+      <c r="C7" s="23">
+        <v>46036.0</v>
+      </c>
+      <c r="D7" s="23">
+        <v>46037.0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>46038.0</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="25">
+        <v>46040.0</v>
+      </c>
+    </row>
+    <row r="8" ht="69.0" customHeight="1">
+      <c r="A8" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="13">
-        <v>46035.0</v>
-      </c>
-      <c r="C7" s="25">
-        <v>46036.0</v>
-      </c>
-      <c r="D7" s="25">
-        <v>46037.0</v>
-      </c>
-      <c r="E7" s="13">
-        <v>46038.0</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="27">
-        <v>46040.0</v>
-      </c>
-    </row>
-    <row r="8" ht="69.0" customHeight="1">
-      <c r="A8" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="E8" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="15" t="s">
+      <c r="G8" s="29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="B9" s="14">
+        <v>46042.0</v>
+      </c>
+      <c r="C9" s="23">
+        <v>46043.0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>46044.0</v>
+      </c>
+      <c r="E9" s="14">
+        <v>46045.0</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>43</v>
-      </c>
-      <c r="B9" s="13">
-        <v>46042.0</v>
-      </c>
-      <c r="C9" s="25">
-        <v>46043.0</v>
-      </c>
-      <c r="D9" s="25">
-        <v>46044.0</v>
-      </c>
-      <c r="E9" s="13">
-        <v>46045.0</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>44</v>
       </c>
       <c r="G9" s="12">
         <v>46047.0</v>
       </c>
     </row>
     <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="18"/>
+      <c r="A10" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="21"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="13">
+      <c r="A11" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="14">
         <v>46049.0</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="23">
         <v>46050.0</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="23">
         <v>46051.0</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="14">
         <v>46052.0</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="10"/>
+      <c r="F11" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="15" t="s">
-        <v>55</v>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="G12" s="36"/>
     </row>
@@ -2146,186 +2146,186 @@
       <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="64" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="17" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="15" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="4" ht="84.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="50" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="53" t="s">
         <v>251</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="53" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="65" t="s">
         <v>259</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
       <c r="F6" s="66" t="s">
         <v>259</v>
       </c>
-      <c r="G6" s="18"/>
+      <c r="G6" s="21"/>
       <c r="L6" s="67"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="15" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
       <c r="F8" s="68" t="s">
         <v>267</v>
       </c>
-      <c r="G8" s="18"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="15" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="10" ht="100.5" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>276</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="G11" s="10"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2354,193 +2354,193 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="17" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="18" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="18"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="21"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="G5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>289</v>
       </c>
+      <c r="G5" s="15" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="B7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="E7" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>296</v>
       </c>
+      <c r="G7" s="15" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="F9" s="16" t="s">
+      <c r="A9" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="B9" s="18" t="s">
         <v>303</v>
       </c>
+      <c r="C9" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>310</v>
+      <c r="A11" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="69" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>312</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="A13" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
-      <c r="A14" s="18"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2571,175 +2571,175 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="48" t="s">
-        <v>313</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="A2" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="43"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="44"/>
+      <c r="B3" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="4" ht="91.5" customHeight="1">
+      <c r="A4" s="11"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>316</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="F3" s="16" t="s">
+      <c r="C5" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>320</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="F5" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="G5" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="G5" s="16" t="s">
+    </row>
+    <row r="6" ht="99.0" customHeight="1">
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="6" ht="99.0" customHeight="1">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>327</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>328</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="D7" s="18" t="s">
         <v>329</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="F7" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="G7" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="G7" s="16" t="s">
+    </row>
+    <row r="8" ht="96.0" customHeight="1">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="8" ht="96.0" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>334</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>336</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="18" t="s">
         <v>337</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="15" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2767,15 +2767,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="63.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
@@ -2791,15 +2791,15 @@
       <c r="T1" s="9"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
@@ -2815,13 +2815,13 @@
       <c r="T2" s="9"/>
     </row>
     <row r="3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="22">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="19">
         <v>46054.0</v>
       </c>
       <c r="H3" s="9"/>
@@ -2839,13 +2839,13 @@
       <c r="T3" s="9"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="15"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="17"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -2861,25 +2861,25 @@
       <c r="T4" s="9"/>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="32">
+      <c r="A5" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="27">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="27">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="27">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="27">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="22">
+      <c r="F5" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="19">
         <v>46061.0</v>
       </c>
       <c r="H5" s="9"/>
@@ -2897,18 +2897,18 @@
       <c r="T5" s="9"/>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>58</v>
+      <c r="A6" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>53</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
@@ -2925,25 +2925,25 @@
       <c r="T6" s="9"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="32">
+      <c r="A7" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="27">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="27">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="27">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="27">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="22">
+      <c r="F7" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="19">
         <v>46068.0</v>
       </c>
       <c r="H7" s="9"/>
@@ -2961,22 +2961,22 @@
       <c r="T7" s="9"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="19"/>
-      <c r="B8" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="19"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="16"/>
       <c r="G8" s="38" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -2993,25 +2993,25 @@
       <c r="T8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="32">
+      <c r="A9" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="27">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="27">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="27">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="27">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="22">
+      <c r="F9" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="19">
         <v>46075.0</v>
       </c>
       <c r="H9" s="9"/>
@@ -3029,18 +3029,18 @@
       <c r="T9" s="9"/>
     </row>
     <row r="10" ht="89.25" customHeight="1">
-      <c r="A10" s="15"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>78</v>
+      <c r="A10" s="17"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>75</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -3057,25 +3057,25 @@
       <c r="T10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="32">
+      <c r="A11" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="27">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="27">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="27">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="27">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="19"/>
+      <c r="F11" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="16"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -3091,15 +3091,15 @@
       <c r="T11" s="9"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
@@ -24412,222 +24412,222 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
       <c r="G3" s="12">
         <v>46082.0</v>
       </c>
     </row>
     <row r="4" ht="69.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="15" t="s">
-        <v>6</v>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="14">
         <v>46084.0</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="14">
         <v>46085.0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="14">
         <v>46086.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="14">
         <v>46087.0</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>9</v>
+      <c r="F5" s="15" t="s">
+        <v>12</v>
       </c>
       <c r="G5" s="12">
         <v>46089.0</v>
       </c>
     </row>
     <row r="6" ht="113.25" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="15" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="17"/>
+      <c r="G6" s="24"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="A7" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="14">
         <v>46091.0</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="14">
         <v>46092.0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="14">
         <v>46093.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="14">
         <v>46094.0</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>21</v>
+      <c r="F7" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="G7" s="12">
         <v>46096.0</v>
       </c>
     </row>
     <row r="8" ht="87.0" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="10"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="11"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="14">
         <v>46098.0</v>
       </c>
       <c r="C9" s="12">
         <v>46099.0</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="23">
         <v>46100.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <v>46101.0</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>33</v>
+      <c r="F9" s="15" t="s">
+        <v>37</v>
       </c>
       <c r="G9" s="12">
         <v>46103.0</v>
       </c>
     </row>
     <row r="10" ht="96.0" customHeight="1">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="33" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="6"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="13">
+      <c r="A11" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="14">
         <v>46105.0</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="14">
         <v>46106.0</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="14">
         <v>46107.0</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="14">
         <v>46108.0</v>
       </c>
-      <c r="F11" s="16" t="s">
-        <v>49</v>
+      <c r="F11" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="G11" s="12">
         <v>46110.0</v>
       </c>
     </row>
     <row r="12" ht="91.5" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="15" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
+      <c r="E12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="14">
         <v>46112.0</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" ht="95.25" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -24656,192 +24656,192 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="13">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="14">
         <v>46113.0</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="14">
         <v>46114.0</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="14">
         <v>46115.0</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>7</v>
+      <c r="F3" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="G3" s="12">
         <v>46117.0</v>
       </c>
     </row>
     <row r="4" ht="99.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="14">
         <v>46119.0</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="14">
         <v>46120.0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="14">
         <v>46121.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="14">
         <v>46122.0</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>12</v>
+      <c r="F5" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="G5" s="12">
         <v>46124.0</v>
       </c>
     </row>
     <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="20" t="s">
-        <v>27</v>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="17"/>
+      <c r="G6" s="28" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="A7" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="14">
         <v>46126.0</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="23">
         <v>46127.0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="14">
         <v>46128.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="14">
         <v>46129.0</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>32</v>
+      <c r="F7" s="15" t="s">
+        <v>47</v>
       </c>
       <c r="G7" s="12">
         <v>46131.0</v>
       </c>
     </row>
     <row r="8" ht="80.25" customHeight="1">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="20" t="s">
-        <v>60</v>
+      <c r="A8" s="33"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="17"/>
+      <c r="G8" s="28" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="14">
         <v>46133.0</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="14">
         <v>46134.0</v>
       </c>
       <c r="D9" s="12">
         <v>46135.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <v>46136.0</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>65</v>
+      <c r="F9" s="15" t="s">
+        <v>73</v>
       </c>
       <c r="G9" s="12">
         <v>46138.0</v>
       </c>
     </row>
     <row r="10" ht="92.25" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="13">
+      <c r="A11" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="14">
         <v>46140.0</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="14">
         <v>46141.0</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="14">
         <v>46142.0</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
       <c r="D12" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+        <v>81</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13">
       <c r="D13" s="40"/>
@@ -24875,224 +24875,224 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="A2" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>85</v>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="45"/>
-      <c r="G4" s="20" t="s">
-        <v>87</v>
+      <c r="A4" s="11"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="46"/>
+      <c r="G4" s="28" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>95</v>
+      <c r="A5" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="20" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="46"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" ht="97.5" customHeight="1">
+      <c r="A8" s="17"/>
+      <c r="B8" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" ht="93.75" customHeight="1">
+      <c r="A10" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="G6" s="45"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>133</v>
+      <c r="C10" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>143</v>
+      <c r="A11" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="B12" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>133</v>
+      <c r="A12" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="G12" s="54" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -25122,219 +25122,219 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+        <v>82</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" ht="91.5" customHeight="1">
+      <c r="A4" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="E4" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="B5" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D5" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F5" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="15" t="s">
+    </row>
+    <row r="6" ht="183.75" customHeight="1">
+      <c r="A6" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="G6" s="28" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="39" t="s">
+      <c r="C7" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="G4" s="15"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="17" t="s">
+    </row>
+    <row r="8" ht="101.25" customHeight="1">
+      <c r="A8" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="17" t="s">
+      <c r="B8" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="F5" s="16" t="s">
+      <c r="C8" s="53" t="s">
         <v>149</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" ht="183.75" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="D8" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="15" t="s">
+      <c r="E8" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="F8" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="G8" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="G6" s="20" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B7" s="17" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D7" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7" s="16" t="s">
+      <c r="C9" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="E9" s="18" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="8" ht="101.25" customHeight="1">
-      <c r="A8" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="B8" s="50" t="s">
+      <c r="F9" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="G9" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="G8" s="20" t="s">
+    </row>
+    <row r="10" ht="99.75" customHeight="1">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="28" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="G10" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" s="17" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="10" ht="99.75" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25365,37 +25365,37 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="A2" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="13">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="14">
         <v>46204.0</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="14">
         <v>46205.0</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="14">
         <v>46206.0</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>183</v>
       </c>
       <c r="G3" s="12">
@@ -25403,33 +25403,33 @@
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="50" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="15"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="14">
         <v>46211.0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="14">
         <v>46212.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="14">
         <v>46213.0</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>187</v>
       </c>
       <c r="G5" s="12">
@@ -25440,38 +25440,38 @@
       <c r="A6" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="50" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="53" t="s">
         <v>189</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="28" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="23">
         <v>46218.0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="14">
         <v>46219.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="14">
         <v>46220.0</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>194</v>
       </c>
       <c r="G7" s="56">
@@ -25479,33 +25479,33 @@
       </c>
     </row>
     <row r="8" ht="88.5" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="50" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="G8" s="18"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="14">
         <v>46225.0</v>
       </c>
       <c r="D9" s="57">
         <v>46226.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <v>46227.0</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>197</v>
       </c>
       <c r="G9" s="12">
@@ -25513,45 +25513,45 @@
       </c>
     </row>
     <row r="10" ht="77.25" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="47" t="s">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="G10" s="47" t="s">
+      <c r="G10" s="50" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="14">
         <v>46232.0</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="14">
         <v>46233.0</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="38"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25582,31 +25582,31 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="16" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G3" s="12">
@@ -25614,183 +25614,183 @@
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="50" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="21"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="C5" s="13">
+      <c r="A5" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="14">
         <v>46239.0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="14">
         <v>46240.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="14">
         <v>46241.0</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>207</v>
+      <c r="F5" s="15" t="s">
+        <v>209</v>
       </c>
       <c r="G5" s="12">
         <v>46243.0</v>
       </c>
     </row>
     <row r="6" ht="84.0" customHeight="1">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="G6" s="18"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="G6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="13">
+      <c r="A7" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" s="14">
         <v>46246.0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="14">
         <v>46247.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="14">
         <v>46248.0</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>211</v>
+      <c r="F7" s="15" t="s">
+        <v>215</v>
       </c>
       <c r="G7" s="12">
         <v>46250.0</v>
       </c>
     </row>
     <row r="8" ht="93.75" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="50" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="G8" s="18"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="C9" s="13">
+      <c r="A9" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="14">
         <v>46253.0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="14">
         <v>46254.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <v>46255.0</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>214</v>
+      <c r="F9" s="15" t="s">
+        <v>220</v>
       </c>
       <c r="G9" s="12">
         <v>46257.0</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="50" t="s">
-        <v>215</v>
+      <c r="A10" s="21"/>
+      <c r="B10" s="53" t="s">
+        <v>221</v>
       </c>
       <c r="C10" s="36"/>
-      <c r="D10" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="50" t="s">
+      <c r="D10" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="21"/>
+      <c r="F10" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="G10" s="20" t="s">
-        <v>216</v>
+      <c r="G10" s="28" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="13">
+      <c r="A11" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="14">
         <v>46260.0</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="14">
         <v>46261.0</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="14">
         <v>46262.0</v>
       </c>
-      <c r="F11" s="16" t="s">
-        <v>219</v>
+      <c r="F11" s="15" t="s">
+        <v>225</v>
       </c>
       <c r="G11" s="12">
         <v>46264.0</v>
       </c>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" s="20" t="s">
+      <c r="A12" s="21"/>
+      <c r="B12" s="53" t="s">
         <v>221</v>
       </c>
-      <c r="G12" s="18"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G12" s="21"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="A13" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
-      <c r="A14" s="18"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25821,62 +25821,62 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="48" t="s">
-        <v>223</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
+      <c r="A2" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="C3" s="13">
+      <c r="A3" s="11"/>
+      <c r="B3" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="14">
         <v>46267.0</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="14">
         <v>46268.0</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="14">
         <v>46269.0</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>225</v>
+      <c r="F3" s="15" t="s">
+        <v>210</v>
       </c>
       <c r="G3" s="12">
         <v>46271.0</v>
       </c>
     </row>
     <row r="4" ht="85.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="58" t="s">
-        <v>226</v>
-      </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+        <v>214</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>227</v>
+      <c r="A5" s="18" t="s">
+        <v>217</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C5" s="60">
         <v>46274.0</v>
@@ -25884,29 +25884,29 @@
       <c r="D5" s="61">
         <v>46275.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="14">
         <v>46276.0</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>229</v>
+      <c r="F5" s="15" t="s">
+        <v>226</v>
       </c>
       <c r="G5" s="12">
         <v>46278.0</v>
       </c>
     </row>
     <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
+      <c r="A6" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>231</v>
       </c>
       <c r="B7" s="59" t="s">
@@ -25915,13 +25915,13 @@
       <c r="C7" s="60">
         <v>46281.0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="14">
         <v>46282.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="14">
         <v>46283.0</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>233</v>
       </c>
       <c r="G7" s="12">
@@ -25929,37 +25929,37 @@
       </c>
     </row>
     <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="14">
         <v>46288.0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="14">
         <v>46289.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <v>46290.0</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>239</v>
       </c>
       <c r="G9" s="12">
@@ -25970,42 +25970,42 @@
       <c r="A10" s="62" t="s">
         <v>240</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="62" t="s">
         <v>241</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="28" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="14">
         <v>46295.0</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -24,12 +24,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="345">
   <si>
+    <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
   <si>
-    <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
-  </si>
-  <si>
     <t>OCAK</t>
   </si>
   <si>
@@ -37,9 +37,6 @@
   </si>
   <si>
     <t xml:space="preserve">MART </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
   </si>
   <si>
     <r>
@@ -64,25 +61,34 @@
     <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
+  </si>
+  <si>
     <t>5 Ocak 2026 Pazartesi</t>
   </si>
   <si>
-    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
   </si>
   <si>
     <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
   </si>
   <si>
     <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
   </si>
   <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
+    <t>CHP Eğitim 17.00-20.00</t>
   </si>
   <si>
     <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
@@ -94,7 +100,16 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
-    <t>CHP Eğitim 17.00-20.00</t>
+    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t>13 Nisan 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
   </si>
   <si>
     <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
@@ -103,68 +118,80 @@
     <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
   </si>
   <si>
-    <t>İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
-  </si>
-  <si>
-    <t>13 Nisan 2026 Pazartesi</t>
+    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
   </si>
   <si>
     <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
   </si>
   <si>
     <t>*18 Mart Şehitleri Anma Günü Provası 
 *16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
   </si>
   <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
+    <t>Ot Festivali ile ilgili toplantı 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
+  </si>
+  <si>
+    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
+  </si>
+  <si>
+    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
+  </si>
+  <si>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
+  </si>
+  <si>
+    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
   </si>
   <si>
     <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
   </si>
   <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
+  </si>
+  <si>
+    <t>YARI YIL ETKİNLİKLERİ</t>
   </si>
   <si>
     <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
-  </si>
-  <si>
-    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
+    <t>Belediye TSM Konseri Tüm gün</t>
   </si>
   <si>
     <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
   </si>
   <si>
-    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
-  </si>
-  <si>
     <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
-  </si>
-  <si>
-    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
-  </si>
-  <si>
-    <t>YARI YIL ETKİNLİKLERİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
   </si>
   <si>
     <r>
@@ -184,7 +211,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
+    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
   </si>
   <si>
     <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
@@ -196,306 +226,131 @@
     <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>Ot Festivali ile ilgili toplantı 14.00</t>
+    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>RAMAZAN BAYRAMI</t>
+  </si>
+  <si>
+    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
+  </si>
+  <si>
+    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
   </si>
   <si>
     <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
   </si>
   <si>
-    <t>RAMAZAN BAYRAMI</t>
+    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
   </si>
   <si>
     <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
-  </si>
-  <si>
-    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
-  </si>
-  <si>
     <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
   </si>
   <si>
+    <t>28 Şubat 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t>31 Ocak 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
+  </si>
+  <si>
+    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+  </si>
+  <si>
     <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
   </si>
   <si>
-    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
     <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
   </si>
   <si>
-    <t>31 Ocak 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
   </si>
   <si>
     <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
   </si>
   <si>
-    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
-  </si>
-  <si>
     <t>CHP İlçe Eğitim tüm gün</t>
   </si>
   <si>
     <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
   </si>
   <si>
-    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
-  </si>
-  <si>
     <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
   </si>
   <si>
     <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
 -Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
   </si>
   <si>
-    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
-  </si>
-  <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
-  </si>
-  <si>
     <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
-  </si>
-  <si>
-    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>28 Şubat 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
+    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
   <si>
     <t>MAYIS</t>
   </si>
   <si>
+    <t xml:space="preserve">HAZİRAN </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
     <t>3 MAYIS 2026 PAZAR</t>
   </si>
   <si>
+    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>7 HAZİRAN 2026 PAZAR</t>
+  </si>
+  <si>
     <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
   </si>
   <si>
+    <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
+  </si>
+  <si>
     <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>10 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
-  </si>
-  <si>
-    <t>21.30 konser provası Başkan ile</t>
-  </si>
-  <si>
-    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
-  </si>
-  <si>
-    <t>11 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t>16 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
-  </si>
-  <si>
-    <t>Bilgiç Anaokulu Prova 
-10.30-15.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bilgiç Anaokulu Prova 
-10.30-15.30                                               </t>
-  </si>
-  <si>
-    <t>-Bilgiç ortaokulu 09.00-12.00
--Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
-  </si>
-  <si>
-    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
-"No Mans Land" Yetişkin Oyunu 20.00
-onaylandı.</t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
-  </si>
-  <si>
-    <t>18 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t>23 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t>24 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro</t>
-  </si>
-  <si>
-    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAZİRAN </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
-    </r>
-  </si>
-  <si>
-    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
-  </si>
-  <si>
-    <t>BAYRAM</t>
-  </si>
-  <si>
-    <t>25 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>7 HAZİRAN 2026 PAZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
   </si>
   <si>
     <r>
@@ -515,9 +370,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">TEMMUZ </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -535,10 +387,37 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t>Bilgiç İlkokulu 13.00 1. Sınıf Okuma Bayramı 18.00
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
   </si>
   <si>
+    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>10 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
+  </si>
+  <si>
+    <t>21.30 konser provası Başkan ile</t>
+  </si>
+  <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
   </si>
   <si>
@@ -554,6 +433,9 @@
     <t xml:space="preserve">11 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
+    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
+  </si>
+  <si>
     <t xml:space="preserve">12 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
@@ -563,10 +445,28 @@
     <t xml:space="preserve">14 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
+    <t>11 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00</t>
   </si>
   <si>
-    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
+    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>16 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
   </si>
   <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00                                                        "SEVGİLİ DOKTOR"  20.00</t>
@@ -590,8 +490,7 @@
     </r>
   </si>
   <si>
-    <t>Latin Katolik Kilisesi Ayin 
-18.30</t>
+    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
   </si>
   <si>
     <t>-SERTUR KOOPERATİF TOPLANTISI HALUK BEY 05336460236 
@@ -602,37 +501,194 @@
     <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
   </si>
   <si>
+    <t>Bilgiç Anaokulu Prova 
+10.30-15.30</t>
+  </si>
+  <si>
+    <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilgiç Anaokulu Prova 
+10.30-15.30                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t>-Bilgiç ortaokulu 09.00-12.00
+-Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
+"No Mans Land" Yetişkin Oyunu 20.00
+onaylandı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>18 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>Atatürk Lisesi tiyatro prova</t>
+  </si>
+  <si>
+    <t>23 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t>24 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Atatürk Lisesi Oyun Günü</t>
+  </si>
+  <si>
+    <t>Osman Uysal Prova opsiyon</t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro</t>
+  </si>
+  <si>
+    <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
+sabahtan 21.00'a kadar</t>
+  </si>
+  <si>
+    <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
+  </si>
+  <si>
+    <t>Namık Kemal Okuma Bayramı</t>
+  </si>
+  <si>
+    <t>Doğu Der Toplantı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t>BAYRAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Reyhan Cici Piyano Dinletisi
+Ödendi. Dilekçe geldi. Tel no:5320631925 12.00-20.00</t>
+  </si>
+  <si>
+    <t>25 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t>MHP 15. Olağan Kongre Toplantısı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMMUZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>Latin Katolik Kilisesi Ayin 
+18.30</t>
+  </si>
+  <si>
     <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
-  </si>
-  <si>
     <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
     <t>-Çoklu İklim Krizinin Gölgesinde Orman Yangınları
@@ -640,78 +696,22 @@
 -Belediye Meclisi 17.00'dan sonra</t>
   </si>
   <si>
-    <t>Atatürk Lisesi tiyatro prova</t>
-  </si>
-  <si>
-    <t>Atatürk Lisesi Oyun Günü</t>
-  </si>
-  <si>
-    <t>Osman Uysal Prova opsiyon</t>
-  </si>
-  <si>
-    <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
-sabahtan 21.00'a kadar</t>
-  </si>
-  <si>
     <t>Belediye meclisi 16.00'dan sonra</t>
   </si>
   <si>
-    <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
-  </si>
-  <si>
-    <t>Namık Kemal Okuma Bayramı</t>
-  </si>
-  <si>
     <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
   </si>
   <si>
-    <t>Doğu Der Toplantı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
     <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
   </si>
   <si>
-    <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
     <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Reyhan Cici Piyano Dinletisi
-Ödendi. Dilekçe geldi. Tel no:5320631925 12.00-20.00</t>
-  </si>
-  <si>
-    <t>MHP 15. Olağan Kongre Toplantısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
@@ -748,6 +748,9 @@
     <t xml:space="preserve">1 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">EYLÜL </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -755,6 +758,9 @@
   </si>
   <si>
     <t xml:space="preserve">8 AĞUSTOS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
   </si>
   <si>
     <t>-Orkent Sitesi 11.00-13.00 ödendi.
@@ -768,6 +774,9 @@
     <t xml:space="preserve">11 AĞUSTOS 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">15 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
@@ -777,6 +786,10 @@
     <t xml:space="preserve">18 AĞUSTOS 2026 SALI </t>
   </si>
   <si>
+    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
+Haydar Ali tel no: 5527151935</t>
+  </si>
+  <si>
     <t xml:space="preserve">22 AĞUSTOS 2026 CUMARTESİ </t>
   </si>
   <si>
@@ -789,7 +802,13 @@
     <t xml:space="preserve">24 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">25 AĞUSTOS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">29 AĞUSTOS 2026 CUMARTESİ </t>
@@ -806,67 +825,6 @@
     <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">EYLÜL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EKİM </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t>3 EKİM 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
-Haydar Ali tel no: 5527151935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t>Yeni Parti Toplantı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
-    <t>5 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Hafifletici Sebepler opsiyon</t>
-  </si>
-  <si>
     <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
@@ -879,22 +837,7 @@
     <t xml:space="preserve">15 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t>12 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 EKİM 2026 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">19 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
   </si>
   <si>
     <t xml:space="preserve">09:00-16:00 
@@ -902,12 +845,6 @@
 Müdürlüğü   ( İzmir Yurttaş Meclisi) </t>
   </si>
   <si>
-    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">12:30-17:00
 İzmir Büyükşehir Belediyesi Sosyal Hizmetler Dairesi Başkanlığı Kentsel Adalet ve Eşitlik Şube
 Müdürlüğü   ( İzmir Yurttaş Meclisi) </t>
@@ -922,40 +859,13 @@
     <t xml:space="preserve">22 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t>İZMİR KENT TİYATROSU 05547273157</t>
-  </si>
-  <si>
     <t xml:space="preserve">26 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t>19 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
     <t>Osman Uysal Konser Prova 18.00-22.00</t>
   </si>
   <si>
-    <t xml:space="preserve">22 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
     <t>Osman Uysal Konser 20.30 (tüm gün)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
   </si>
   <si>
     <r>
@@ -977,15 +887,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">27 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -1003,18 +904,117 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">28 EYLÜL 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EKİM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t>3 EKİM 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Yeni Parti Toplantı</t>
+  </si>
+  <si>
+    <t>5 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Hafifletici Sebepler opsiyon</t>
+  </si>
+  <si>
+    <t>12 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>İZMİR KENT TİYATROSU 05547273157</t>
+  </si>
+  <si>
+    <t>19 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
     <t xml:space="preserve">30 EKİM 2026 CUMA </t>
   </si>
   <si>
     <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">28 EYLÜL 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">KASIM </t>
   </si>
   <si>
@@ -1066,6 +1066,9 @@
     <t xml:space="preserve">16 KASIM 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">ARALIK </t>
+  </si>
+  <si>
     <t xml:space="preserve">17 KASIM 2026 SALI </t>
   </si>
   <si>
@@ -1099,58 +1102,55 @@
     <t xml:space="preserve">27 KASIM 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">1 ARALIK 2026 SALI </t>
+  </si>
+  <si>
     <t xml:space="preserve">28 KASIM 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">29 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t xml:space="preserve">2 ARALIK 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 ARALIK 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 ARALIK 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 ARALIK 2026 CUMA RTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 ARALIK 2026 PAZAR </t>
+  </si>
+  <si>
     <t>Tuncay Hoca Çsm</t>
   </si>
   <si>
+    <t xml:space="preserve">7 ARALIK 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 ARALIK 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 ARALIK 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 ARALIK 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 ARALIK 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 ARALIK 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 ARALIK 2026 PAZAR </t>
+  </si>
+  <si>
     <t>30 KASIM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARALIK </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 ARALIK 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 ARALIK 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 ARALIK 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 ARALIK 2026 CUMA RTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 ARALIK 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 ARALIK 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 ARALIK 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 ARALIK 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 ARALIK 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 ARALIK 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 ARALIK 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 ARALIK 2026 PAZAR </t>
   </si>
   <si>
     <t xml:space="preserve">14 ARALIK 2026 PAZARTESİ </t>
@@ -1251,8 +1251,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1264,7 +1263,8 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFF0000"/>
+      <sz val="15.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1297,13 +1297,13 @@
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1330,14 +1330,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6B26B"/>
-        <bgColor rgb="FFF6B26B"/>
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor rgb="FFF9CB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9CB9C"/>
-        <bgColor rgb="FFF9CB9C"/>
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF6B26B"/>
       </patternFill>
     </fill>
     <fill>
@@ -1444,43 +1444,49 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1488,54 +1494,51 @@
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1543,19 +1546,19 @@
     <xf borderId="4" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1568,13 +1571,22 @@
     <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1583,44 +1595,35 @@
     <xf borderId="4" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="14" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1633,9 +1636,6 @@
     </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="12" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1911,7 +1911,7 @@
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1921,7 +1921,7 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3"/>
@@ -1935,16 +1935,16 @@
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="13">
+      <c r="D3" s="11">
         <v>46023.0</v>
       </c>
       <c r="E3" s="12">
         <v>46024.0</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="11">
         <v>46026.0</v>
       </c>
     </row>
@@ -1958,8 +1958,8 @@
       <c r="G4" s="9"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>8</v>
+      <c r="A5" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="B5" s="12">
         <v>46028.0</v>
@@ -1973,10 +1973,10 @@
       <c r="E5" s="12">
         <v>46031.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="11">
         <v>46033.0</v>
       </c>
     </row>
@@ -1985,135 +1985,135 @@
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
-      <c r="E6" s="20" t="s">
-        <v>16</v>
+      <c r="E6" s="25" t="s">
+        <v>18</v>
       </c>
       <c r="F6" s="9"/>
-      <c r="G6" s="20" t="s">
-        <v>18</v>
+      <c r="G6" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>19</v>
+      <c r="A7" s="19" t="s">
+        <v>24</v>
       </c>
       <c r="B7" s="12">
         <v>46035.0</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="26">
         <v>46036.0</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="26">
         <v>46037.0</v>
       </c>
       <c r="E7" s="12">
         <v>46038.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="27">
+      <c r="F7" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="31">
         <v>46040.0</v>
       </c>
     </row>
     <row r="8" ht="69.0" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>39</v>
+      <c r="A8" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>44</v>
+      <c r="A9" s="19" t="s">
+        <v>54</v>
       </c>
       <c r="B9" s="12">
         <v>46042.0</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <v>46043.0</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="26">
         <v>46044.0</v>
       </c>
       <c r="E9" s="12">
         <v>46045.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="11">
         <v>46047.0</v>
       </c>
     </row>
     <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="23"/>
+      <c r="A10" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>55</v>
+      <c r="A11" s="19" t="s">
+        <v>68</v>
       </c>
       <c r="B11" s="12">
         <v>46049.0</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <v>46050.0</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="26">
         <v>46051.0</v>
       </c>
       <c r="E11" s="12">
         <v>46052.0</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>59</v>
+      <c r="F11" s="19" t="s">
+        <v>70</v>
       </c>
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="16" t="s">
-        <v>63</v>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="18" t="s">
+        <v>75</v>
       </c>
       <c r="G12" s="38"/>
     </row>
@@ -2143,8 +2143,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="58" t="s">
-        <v>0</v>
+      <c r="A1" s="63" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2154,8 +2154,8 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="59" t="s">
-        <v>224</v>
+      <c r="A2" s="64" t="s">
+        <v>246</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2168,163 +2168,163 @@
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>230</v>
+      <c r="D3" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="4" ht="84.0" customHeight="1">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="49" t="s">
-        <v>233</v>
-      </c>
-      <c r="G4" s="49" t="s">
-        <v>233</v>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>241</v>
+      <c r="A5" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="64" t="s">
-        <v>242</v>
-      </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="65" t="s">
-        <v>242</v>
-      </c>
-      <c r="G6" s="23"/>
-      <c r="L6" s="66"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="65" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="66" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="27"/>
+      <c r="L6" s="67"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>255</v>
+      <c r="A7" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="67" t="s">
-        <v>260</v>
-      </c>
-      <c r="G8" s="23"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="F9" s="14" t="s">
+      <c r="A9" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="B9" s="19" t="s">
         <v>269</v>
       </c>
+      <c r="C9" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="10" ht="100.5" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="D11" s="17" t="s">
+      <c r="A11" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="B11" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="D11" s="19" t="s">
         <v>278</v>
       </c>
+      <c r="E11" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>280</v>
+      </c>
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
       <c r="G12" s="9"/>
     </row>
   </sheetData>
@@ -2352,7 +2352,7 @@
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2379,7 +2379,7 @@
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="19" t="s">
         <v>282</v>
       </c>
     </row>
@@ -2390,141 +2390,141 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="23"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="19" t="s">
         <v>285</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="19" t="s">
         <v>286</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="15" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="C9" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="E9" s="19" t="s">
         <v>302</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>303</v>
       </c>
+      <c r="G9" s="15" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="B11" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="C11" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="D11" s="19" t="s">
         <v>308</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="E11" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="G11" s="14" t="s">
-        <v>310</v>
+      <c r="F11" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
       <c r="G12" s="69" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>312</v>
+      <c r="A13" s="19" t="s">
+        <v>326</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -2534,7 +2534,7 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
-      <c r="A14" s="23"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -2569,7 +2569,7 @@
   <sheetData>
     <row r="1" ht="35.25" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2579,8 +2579,8 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>313</v>
+      <c r="A2" s="43" t="s">
+        <v>298</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2590,142 +2590,142 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="43"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="44"/>
+      <c r="B3" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>317</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
       <c r="A4" s="9"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>320</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="C5" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>326</v>
-      </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="19" t="s">
         <v>331</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="15" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="19" t="s">
         <v>336</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="15" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="19" t="s">
         <v>342</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="19" t="s">
         <v>344</v>
       </c>
       <c r="E11" s="9"/>
@@ -2733,10 +2733,10 @@
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
@@ -2767,8 +2767,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="63.75" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
+      <c r="A1" s="6" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2791,8 +2791,8 @@
       <c r="T1" s="10"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>6</v>
+      <c r="A2" s="14" t="s">
+        <v>5</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2815,13 +2815,13 @@
       <c r="T2" s="10"/>
     </row>
     <row r="3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="21">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="17">
         <v>46054.0</v>
       </c>
       <c r="H3" s="10"/>
@@ -2839,13 +2839,13 @@
       <c r="T3" s="10"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="16"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="18"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
@@ -2861,25 +2861,25 @@
       <c r="T4" s="10"/>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="32">
+      <c r="A5" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="24">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="24">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="24">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="24">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="21">
+      <c r="F5" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="17">
         <v>46061.0</v>
       </c>
       <c r="H5" s="10"/>
@@ -2897,18 +2897,18 @@
       <c r="T5" s="10"/>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>54</v>
+      <c r="A6" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
@@ -2925,25 +2925,25 @@
       <c r="T6" s="10"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="32">
+      <c r="A7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="24">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="24">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="24">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="24">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="21">
+      <c r="F7" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="17">
         <v>46068.0</v>
       </c>
       <c r="H7" s="10"/>
@@ -2961,22 +2961,22 @@
       <c r="T7" s="10"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="40" t="s">
-        <v>72</v>
+      <c r="A8" s="16"/>
+      <c r="B8" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="35" t="s">
+        <v>47</v>
       </c>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
@@ -2993,25 +2993,25 @@
       <c r="T8" s="10"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="32">
+      <c r="A9" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="24">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="24">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="24">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="24">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="21">
+      <c r="F9" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="17">
         <v>46075.0</v>
       </c>
       <c r="H9" s="10"/>
@@ -3029,18 +3029,18 @@
       <c r="T9" s="10"/>
     </row>
     <row r="10" ht="89.25" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>78</v>
+      <c r="A10" s="18"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>64</v>
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
@@ -3057,25 +3057,25 @@
       <c r="T10" s="10"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="32">
+      <c r="A11" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="24">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="24">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="24">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="24">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="18"/>
+      <c r="F11" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="16"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
@@ -3091,15 +3091,15 @@
       <c r="T11" s="10"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
@@ -24412,8 +24412,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>1</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -24423,7 +24423,7 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3"/>
@@ -24440,7 +24440,7 @@
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="13">
+      <c r="G3" s="11">
         <v>46082.0</v>
       </c>
     </row>
@@ -24451,13 +24451,13 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="18" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>11</v>
+      <c r="A5" s="19" t="s">
+        <v>12</v>
       </c>
       <c r="B5" s="12">
         <v>46084.0</v>
@@ -24471,31 +24471,31 @@
       <c r="E5" s="12">
         <v>46087.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="11">
         <v>46089.0</v>
       </c>
     </row>
     <row r="6" ht="113.25" customHeight="1">
       <c r="A6" s="9"/>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="26"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>27</v>
+      <c r="A7" s="19" t="s">
+        <v>39</v>
       </c>
       <c r="B7" s="12">
         <v>46091.0</v>
@@ -24509,67 +24509,67 @@
       <c r="E7" s="12">
         <v>46094.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="11">
         <v>46096.0</v>
       </c>
     </row>
     <row r="8" ht="87.0" customHeight="1">
       <c r="A8" s="9"/>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>37</v>
+      <c r="C8" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="E8" s="9"/>
-      <c r="F8" s="16" t="s">
-        <v>38</v>
+      <c r="F8" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="G8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>40</v>
+      <c r="A9" s="19" t="s">
+        <v>52</v>
       </c>
       <c r="B9" s="12">
         <v>46098.0</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="11">
         <v>46099.0</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="26">
         <v>46100.0</v>
       </c>
       <c r="E9" s="12">
         <v>46101.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="11">
         <v>46103.0</v>
       </c>
     </row>
     <row r="10" ht="96.0" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="35" t="s">
-        <v>51</v>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="36" t="s">
+        <v>62</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>58</v>
+      <c r="A11" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="B11" s="12">
         <v>46105.0</v>
@@ -24583,33 +24583,33 @@
       <c r="E11" s="12">
         <v>46108.0</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="13">
+      <c r="F11" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="11">
         <v>46110.0</v>
       </c>
     </row>
     <row r="12" ht="91.5" customHeight="1">
       <c r="A12" s="9"/>
-      <c r="B12" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
+      <c r="B12" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>73</v>
+      <c r="A13" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="B13" s="12">
         <v>46112.0</v>
@@ -24656,8 +24656,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="4" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -24667,7 +24667,7 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3"/>
@@ -24689,10 +24689,10 @@
       <c r="E3" s="12">
         <v>46115.0</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="11">
         <v>46117.0</v>
       </c>
     </row>
@@ -24702,12 +24702,12 @@
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
-      <c r="F4" s="16"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>10</v>
+      <c r="A5" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="12">
         <v>46119.0</v>
@@ -24721,10 +24721,10 @@
       <c r="E5" s="12">
         <v>46122.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="11">
         <v>46124.0</v>
       </c>
     </row>
@@ -24732,25 +24732,25 @@
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
-      <c r="D6" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="19" t="s">
+      <c r="D6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="G6" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="21.0" customHeight="1">
+      <c r="A7" s="19" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>22</v>
       </c>
       <c r="B7" s="12">
         <v>46126.0</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="26">
         <v>46127.0</v>
       </c>
       <c r="D7" s="12">
@@ -24759,31 +24759,31 @@
       <c r="E7" s="12">
         <v>46129.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="11">
         <v>46131.0</v>
       </c>
     </row>
     <row r="8" ht="80.25" customHeight="1">
       <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="19" t="s">
-        <v>43</v>
+      <c r="D8" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>45</v>
+      <c r="A9" s="19" t="s">
+        <v>55</v>
       </c>
       <c r="B9" s="12">
         <v>46133.0</v>
@@ -24791,16 +24791,16 @@
       <c r="C9" s="12">
         <v>46134.0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <v>46135.0</v>
       </c>
       <c r="E9" s="12">
         <v>46136.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="11">
         <v>46138.0</v>
       </c>
     </row>
@@ -24808,16 +24808,16 @@
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="19" t="s">
-        <v>50</v>
+      <c r="D10" s="21" t="s">
+        <v>65</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>52</v>
+      <c r="A11" s="19" t="s">
+        <v>67</v>
       </c>
       <c r="B11" s="12">
         <v>46140.0</v>
@@ -24836,15 +24836,15 @@
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
-      <c r="D12" s="36" t="s">
-        <v>56</v>
+      <c r="D12" s="37" t="s">
+        <v>73</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
     </row>
     <row r="13">
-      <c r="D13" s="37"/>
+      <c r="D13" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24873,7 +24873,7 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -24884,7 +24884,7 @@
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -24898,201 +24898,201 @@
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
-      <c r="E3" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="E3" s="15" t="s">
         <v>85</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
       <c r="A4" s="9"/>
-      <c r="B4" s="43"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
-      <c r="E4" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="45"/>
-      <c r="G4" s="19" t="s">
-        <v>87</v>
+      <c r="E4" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="46"/>
+      <c r="G4" s="21" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>94</v>
+      <c r="A5" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="G6" s="46"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" ht="97.5" customHeight="1">
+      <c r="A8" s="18"/>
+      <c r="B8" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" ht="93.75" customHeight="1">
+      <c r="A10" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" s="45"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="G10" s="50" t="s">
-        <v>124</v>
+      <c r="C10" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>131</v>
+      <c r="A11" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="F12" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" s="50" t="s">
-        <v>124</v>
+      <c r="A12" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="G12" s="54" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -25122,7 +25122,7 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -25132,8 +25132,8 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>121</v>
+      <c r="A2" s="43" t="s">
+        <v>84</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -25143,183 +25143,183 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" ht="91.5" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" ht="183.75" customHeight="1">
+      <c r="A6" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="17" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="B7" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="C7" s="19" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="D7" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="E7" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="G7" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="14" t="s">
+    </row>
+    <row r="8" ht="101.25" customHeight="1">
+      <c r="A8" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" ht="183.75" customHeight="1">
-      <c r="A6" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="B6" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="53" t="s">
+      <c r="B8" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="E6" s="22" t="s">
+      <c r="D8" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="F6" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="G6" s="19" t="s">
+      <c r="F8" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="21" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" s="17" t="s">
+    <row r="9">
+      <c r="A9" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="D7" s="17" t="s">
+      <c r="C9" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="D9" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="G7" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="8" ht="101.25" customHeight="1">
-      <c r="A8" s="49" t="s">
+      <c r="G9" s="15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" ht="99.75" customHeight="1">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="B8" s="49" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="49" t="s">
+      <c r="G10" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="F8" s="49" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>177</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="10" ht="99.75" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>194</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -25328,13 +25328,13 @@
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25363,7 +25363,7 @@
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -25373,8 +25373,8 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>141</v>
+      <c r="A2" s="43" t="s">
+        <v>182</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -25395,30 +25395,30 @@
       <c r="E3" s="12">
         <v>46206.0</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="11">
         <v>46208.0</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="G4" s="16"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="18"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>161</v>
+      <c r="A5" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>186</v>
       </c>
       <c r="C5" s="12">
         <v>46211.0</v>
@@ -25429,40 +25429,40 @@
       <c r="E5" s="12">
         <v>46213.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="11">
         <v>46215.0</v>
       </c>
     </row>
     <row r="6" ht="92.25" customHeight="1">
       <c r="A6" s="55" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>181</v>
+        <v>188</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="C7" s="24">
+      <c r="A7" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="26">
         <v>46218.0</v>
       </c>
       <c r="D7" s="12">
@@ -25471,29 +25471,29 @@
       <c r="E7" s="12">
         <v>46220.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>190</v>
+      <c r="F7" s="15" t="s">
+        <v>194</v>
       </c>
       <c r="G7" s="56">
         <v>46222.0</v>
       </c>
     </row>
     <row r="8" ht="88.5" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="G8" s="23"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="19" t="s">
         <v>196</v>
       </c>
       <c r="C9" s="12">
@@ -25505,31 +25505,31 @@
       <c r="E9" s="12">
         <v>46227.0</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="11">
         <v>46229.0</v>
       </c>
     </row>
     <row r="10" ht="77.25" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="47" t="s">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="G10" s="47" t="s">
+      <c r="G10" s="49" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="19" t="s">
         <v>201</v>
       </c>
       <c r="C11" s="12">
@@ -25538,18 +25538,18 @@
       <c r="D11" s="12">
         <v>46233.0</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="19" t="s">
         <v>202</v>
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="40"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="35"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
     </row>
@@ -25580,7 +25580,7 @@
   <sheetData>
     <row r="1" ht="34.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -25590,7 +25590,7 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="43" t="s">
         <v>203</v>
       </c>
       <c r="B2" s="3"/>
@@ -25606,10 +25606,10 @@
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="11">
         <v>46236.0</v>
       </c>
     </row>
@@ -25619,17 +25619,17 @@
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
-      <c r="F4" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="G4" s="23"/>
+      <c r="F4" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="A5" s="19" t="s">
         <v>206</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>207</v>
       </c>
       <c r="C5" s="12">
         <v>46239.0</v>
@@ -25640,30 +25640,30 @@
       <c r="E5" s="12">
         <v>46241.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="G5" s="11">
         <v>46243.0</v>
       </c>
     </row>
     <row r="6" ht="84.0" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="G6" s="23"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>210</v>
+      <c r="A7" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>212</v>
       </c>
       <c r="C7" s="12">
         <v>46246.0</v>
@@ -25674,30 +25674,30 @@
       <c r="E7" s="12">
         <v>46248.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7" s="11">
         <v>46250.0</v>
       </c>
     </row>
     <row r="8" ht="93.75" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="G8" s="23"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>213</v>
+      <c r="A9" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>216</v>
       </c>
       <c r="C9" s="12">
         <v>46253.0</v>
@@ -25708,36 +25708,36 @@
       <c r="E9" s="12">
         <v>46255.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="G9" s="11">
         <v>46257.0</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="49" t="s">
-        <v>215</v>
+      <c r="A10" s="27"/>
+      <c r="B10" s="53" t="s">
+        <v>219</v>
       </c>
       <c r="C10" s="38"/>
-      <c r="D10" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>216</v>
+      <c r="D10" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="27"/>
+      <c r="F10" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>218</v>
+      <c r="A11" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>223</v>
       </c>
       <c r="C11" s="12">
         <v>46260.0</v>
@@ -25748,33 +25748,33 @@
       <c r="E11" s="12">
         <v>46262.0</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="G11" s="11">
+        <v>46264.0</v>
+      </c>
+    </row>
+    <row r="12" ht="94.5" customHeight="1">
+      <c r="A12" s="27"/>
+      <c r="B12" s="53" t="s">
         <v>219</v>
       </c>
-      <c r="G11" s="13">
-        <v>46264.0</v>
-      </c>
-    </row>
-    <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="G12" s="23"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="G12" s="27"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>222</v>
+      <c r="A13" s="19" t="s">
+        <v>228</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -25784,7 +25784,7 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
-      <c r="A14" s="23"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -25819,7 +25819,7 @@
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -25829,8 +25829,8 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>223</v>
+      <c r="A2" s="43" t="s">
+        <v>205</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -25841,8 +25841,8 @@
     </row>
     <row r="3">
       <c r="A3" s="9"/>
-      <c r="B3" s="17" t="s">
-        <v>225</v>
+      <c r="B3" s="19" t="s">
+        <v>209</v>
       </c>
       <c r="C3" s="12">
         <v>46267.0</v>
@@ -25853,66 +25853,66 @@
       <c r="E3" s="12">
         <v>46269.0</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F3" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="G3" s="11">
         <v>46271.0</v>
       </c>
     </row>
     <row r="4" ht="85.5" customHeight="1">
       <c r="A4" s="9"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="60" t="s">
-        <v>231</v>
-      </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="B5" s="61" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="62">
+      <c r="A5" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="60">
         <v>46274.0</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="61">
         <v>46275.0</v>
       </c>
       <c r="E5" s="12">
         <v>46276.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="F5" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="G5" s="11">
         <v>46278.0</v>
       </c>
     </row>
     <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="A6" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="B7" s="61" t="s">
-        <v>246</v>
-      </c>
-      <c r="C7" s="62">
+      <c r="A7" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" s="60">
         <v>46281.0</v>
       </c>
       <c r="D7" s="12">
@@ -25921,34 +25921,34 @@
       <c r="E7" s="12">
         <v>46283.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="G7" s="11">
         <v>46285.0</v>
       </c>
     </row>
     <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
+      <c r="A8" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>259</v>
+      <c r="A9" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>238</v>
       </c>
       <c r="C9" s="12">
         <v>46288.0</v>
@@ -25959,36 +25959,36 @@
       <c r="E9" s="12">
         <v>46290.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="G9" s="11">
         <v>46292.0</v>
       </c>
     </row>
     <row r="10" ht="98.25" customHeight="1">
-      <c r="A10" s="68" t="s">
-        <v>265</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="68" t="s">
-        <v>270</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>276</v>
+      <c r="A10" s="62" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="62" t="s">
+        <v>241</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>280</v>
+      <c r="A11" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>245</v>
       </c>
       <c r="C11" s="12">
         <v>46295.0</v>
@@ -25999,9 +25999,9 @@
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -30,10 +30,10 @@
     <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
   </si>
   <si>
-    <t>OCAK</t>
-  </si>
-  <si>
     <t xml:space="preserve">NİSAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MART </t>
   </si>
   <si>
     <r>
@@ -55,25 +55,43 @@
     </r>
   </si>
   <si>
+    <t>OCAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MART </t>
-  </si>
-  <si>
     <t>5 Ocak 2026 Pazartesi</t>
   </si>
   <si>
+    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
+  </si>
+  <si>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
+  </si>
+  <si>
     <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
+    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>CHP Eğitim 17.00-20.00</t>
   </si>
   <si>
     <t>Çeşme Belediyesi Türk Halk Müziği Korosu “ Çeşme’den Türkü Akıyor” 2026 Kış Konseri
@@ -82,58 +100,52 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
+    <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
+  </si>
+  <si>
+    <t>Ot Festivali ile ilgili toplantı 14.00</t>
+  </si>
+  <si>
+    <t>13 Nisan 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
+  </si>
+  <si>
+    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
   </si>
   <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
-  </si>
-  <si>
     <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
   </si>
   <si>
-    <t>CHP Eğitim 17.00-20.00</t>
-  </si>
-  <si>
-    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
-  </si>
-  <si>
-    <t>13 Nisan 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
-    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
-  </si>
-  <si>
-    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
+  </si>
+  <si>
+    <t>Belediye TSM Konseri Tüm gün</t>
   </si>
   <si>
     <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
@@ -143,34 +155,46 @@
 *16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
   </si>
   <si>
-    <t>YARI YIL ETKİNLİKLERİ</t>
-  </si>
-  <si>
-    <t>19 Ocak 2026 Pazartesi</t>
+    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
   </si>
   <si>
     <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
     <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
   </si>
   <si>
+    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
   </si>
   <si>
-    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
-  </si>
-  <si>
-    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
+    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>RAMAZAN BAYRAMI</t>
+  </si>
+  <si>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
   </si>
   <si>
     <r>
@@ -190,148 +214,251 @@
     </r>
   </si>
   <si>
+    <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
+  </si>
+  <si>
+    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
+  </si>
+  <si>
+    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
+  </si>
+  <si>
+    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+  </si>
+  <si>
+    <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>YARI YIL ETKİNLİKLERİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>28 Şubat 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
+  </si>
+  <si>
+    <t>19 Ocak 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim tüm gün</t>
+  </si>
+  <si>
     <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
-  </si>
-  <si>
-    <t>Ot Festivali ile ilgili toplantı 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
+    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
   </si>
   <si>
     <t>31 Ocak 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
-  </si>
-  <si>
-    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
-  </si>
-  <si>
-    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
-  </si>
-  <si>
-    <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
-  </si>
-  <si>
-    <t>RAMAZAN BAYRAMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim tüm gün</t>
-  </si>
-  <si>
-    <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
   </si>
   <si>
     <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
 -Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
   </si>
   <si>
-    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
+    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+  </si>
+  <si>
+    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
   </si>
   <si>
     <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
   </si>
   <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
-  </si>
-  <si>
-    <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>28 Şubat 2026 Cumartesi</t>
-  </si>
-  <si>
-    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
+    <t>MAYIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>3 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
+  </si>
+  <si>
+    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>10 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
+  </si>
+  <si>
+    <t>21.30 konser provası Başkan ile</t>
+  </si>
+  <si>
+    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
+  </si>
+  <si>
+    <t>11 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
   <si>
-    <t>MAYIS</t>
+    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>16 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t>Bilgiç Anaokulu Prova 
+10.30-15.30</t>
   </si>
   <si>
     <t xml:space="preserve">HAZİRAN </t>
   </si>
   <si>
-    <t xml:space="preserve">1 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>3 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t>RESMİ TATİL SEBEBİYLE KAPALI</t>
+    <t xml:space="preserve">Bilgiç Anaokulu Prova 
+10.30-15.30                                               </t>
+  </si>
+  <si>
+    <t>-Bilgiç ortaokulu 09.00-12.00
+-Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
+  </si>
+  <si>
+    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
+"No Mans Land" Yetişkin Oyunu 20.00
+onaylandı.</t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
+  </si>
+  <si>
+    <t>18 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t>23 MAYIS 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t>24 MAYIS 2026 PAZAR</t>
+  </si>
+  <si>
+    <t>Özhan Bakadur tiyatro</t>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
   </si>
   <si>
     <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
+    </r>
+  </si>
+  <si>
+    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
   </si>
   <si>
+    <t>BAYRAM</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
@@ -341,40 +468,34 @@
     <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
-    <t>"7 KOCALI HÜRMÜZ"  TİYATRO OYUNU.    20.00     İZBB BALÇOVA ÇAĞDAŞ YAŞAM DERNEĞİ</t>
+    <t>25 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
   </si>
   <si>
     <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
     <t>7 HAZİRAN 2026 PAZAR</t>
   </si>
   <si>
-    <t xml:space="preserve">4 MAYIS 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>10 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
-    <t>Çeşme seyahat genel kurul toplantısı onaylandı. 13.00-17.00</t>
   </si>
   <si>
     <r>
@@ -411,40 +532,19 @@
     </r>
   </si>
   <si>
-    <t>21.30 konser provası Başkan ile</t>
-  </si>
-  <si>
     <t>Bilgiç İlkokulu 13.00 1. Sınıf Okuma Bayramı 18.00
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
   </si>
   <si>
-    <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
-  </si>
-  <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
   </si>
   <si>
-    <t>11 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
     <t xml:space="preserve">8 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">14 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t xml:space="preserve">9 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">15 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
     <t xml:space="preserve">10 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
@@ -460,16 +560,7 @@
     <t xml:space="preserve">14 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
-    <t>16 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -CHP Eğitim 17.00-20.00</t>
   </si>
   <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00                                                        "SEVGİLİ DOKTOR"  20.00</t>
@@ -498,107 +589,37 @@
 - Kent Enstitüsü Prova</t>
   </si>
   <si>
-    <t>Bilgiç Anaokulu Prova 
-10.30-15.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bilgiç Anaokulu Prova 
-10.30-15.30                                               </t>
-  </si>
-  <si>
     <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
   </si>
   <si>
-    <t>-Bilgiç ortaokulu 09.00-12.00
--Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
-  </si>
-  <si>
-    <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
-"No Mans Land" Yetişkin Oyunu 20.00
-onaylandı.</t>
-  </si>
-  <si>
-    <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
-  </si>
-  <si>
-    <t>18 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
     <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
   </si>
   <si>
-    <t xml:space="preserve">19 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
     <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">21 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
     <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t>23 MAYIS 2026 CUMARTESİ</t>
-  </si>
-  <si>
     <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
-    <t>24 MAYIS 2026 PAZAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
-    <t>Özhan Bakadur tiyatro</t>
-  </si>
-  <si>
     <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
     <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
-  </si>
-  <si>
     <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">Yabancı Dil Gecesi Provası Bilgiç Ortaokulu                                                                                               </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>16.00' dan sonra KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ PROVALARI</t>
-    </r>
-  </si>
-  <si>
     <t>Atatürk Lisesi tiyatro prova</t>
   </si>
   <si>
-    <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
-  </si>
-  <si>
     <t>Atatürk Lisesi Oyun Günü</t>
-  </si>
-  <si>
-    <t>BAYRAM</t>
   </si>
   <si>
     <t>Osman Uysal Prova opsiyon</t>
@@ -614,37 +635,16 @@
     <t>Namık Kemal Okuma Bayramı</t>
   </si>
   <si>
-    <t>25 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
     <t>Doğu Der Toplantı</t>
   </si>
   <si>
-    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
     <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
     <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
   </si>
   <si>
     <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
@@ -860,6 +860,9 @@
   </si>
   <si>
     <t xml:space="preserve">26 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EKİM </t>
   </si>
   <si>
     <t>Osman Uysal Konser Prova 18.00-22.00</t>
@@ -908,9 +911,6 @@
   </si>
   <si>
     <t xml:space="preserve">29 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EKİM </t>
   </si>
   <si>
     <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
@@ -1244,7 +1244,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1257,13 +1256,14 @@
     </font>
     <font>
       <b/>
+      <sz val="15.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1324,8 +1324,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF6B26B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE69138"/>
+        <bgColor rgb="FFE69138"/>
       </patternFill>
     </fill>
     <fill>
@@ -1336,32 +1348,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6B26B"/>
-        <bgColor rgb="FFF6B26B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE69138"/>
-        <bgColor rgb="FFE69138"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF93C47D"/>
         <bgColor rgb="FF93C47D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1437,9 +1437,6 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1448,93 +1445,96 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1546,20 +1546,17 @@
     <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1568,13 +1565,7 @@
     <xf borderId="4" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1583,19 +1574,28 @@
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="3" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1610,13 +1610,13 @@
     <xf borderId="4" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1904,212 +1904,212 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="19">
         <v>46023.0</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="16">
         <v>46024.0</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="11">
+      <c r="F3" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="19">
         <v>46026.0</v>
       </c>
     </row>
     <row r="4" ht="95.25" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="16">
         <v>46028.0</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="16">
         <v>46029.0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="16">
         <v>46030.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="16">
         <v>46031.0</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="F5" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="19">
         <v>46033.0</v>
       </c>
     </row>
     <row r="6" ht="97.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="20" t="s">
-        <v>13</v>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="26" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="A7" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="16">
         <v>46035.0</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="28">
         <v>46036.0</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="28">
         <v>46037.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="16">
         <v>46038.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="25">
+      <c r="F7" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="33">
         <v>46040.0</v>
       </c>
     </row>
     <row r="8" ht="69.0" customHeight="1">
-      <c r="A8" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>33</v>
+      <c r="A8" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="16">
         <v>46042.0</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="28">
         <v>46043.0</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="28">
         <v>46044.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="16">
         <v>46045.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="F9" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="19">
         <v>46047.0</v>
       </c>
     </row>
     <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="26"/>
+      <c r="A10" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="13">
+      <c r="A11" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="16">
         <v>46049.0</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="28">
         <v>46050.0</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="28">
         <v>46051.0</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="16">
         <v>46052.0</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="10"/>
+      <c r="F11" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="35"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2137,189 +2137,189 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="64" t="s">
-        <v>246</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+        <v>240</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="17" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="18" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="4" ht="84.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="52" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="49" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="18" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="65" t="s">
         <v>259</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
       <c r="F6" s="66" t="s">
         <v>259</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="L6" s="67"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="18" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
       <c r="F8" s="68" t="s">
         <v>267</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="21" t="s">
         <v>269</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="18" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="10" ht="100.5" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="G11" s="10"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2348,193 +2348,193 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="17" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="21" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="26"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="18" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="18" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="18" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="21" t="s">
         <v>307</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="18" t="s">
         <v>309</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="18" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
       <c r="G12" s="69" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="21" t="s">
         <v>312</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
-      <c r="A14" s="26"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="27"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2565,175 +2565,175 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="50" t="s">
         <v>313</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="18" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="18" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="21" t="s">
         <v>330</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="18" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="18" t="s">
         <v>339</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="18" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="21" t="s">
         <v>344</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2761,15 +2761,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="63.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -2785,15 +2785,15 @@
       <c r="T1" s="6"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -2809,13 +2809,13 @@
       <c r="T2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="19">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12">
         <v>46054.0</v>
       </c>
       <c r="H3" s="6"/>
@@ -2833,13 +2833,13 @@
       <c r="T3" s="6"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="18"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="17"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
@@ -2855,25 +2855,25 @@
       <c r="T4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="30">
+      <c r="A5" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="22">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="22">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="22">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="22">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="19">
+      <c r="F5" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="12">
         <v>46061.0</v>
       </c>
       <c r="H5" s="6"/>
@@ -2891,18 +2891,18 @@
       <c r="T5" s="6"/>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>54</v>
+      <c r="A6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -2919,25 +2919,25 @@
       <c r="T6" s="6"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="30">
+      <c r="A7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="22">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="22">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="22">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="22">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="19">
+      <c r="F7" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="12">
         <v>46068.0</v>
       </c>
       <c r="H7" s="6"/>
@@ -2955,22 +2955,22 @@
       <c r="T7" s="6"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="40" t="s">
-        <v>73</v>
+      <c r="A8" s="11"/>
+      <c r="B8" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="31" t="s">
+        <v>34</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -2987,25 +2987,25 @@
       <c r="T8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="30">
+      <c r="A9" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="22">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="22">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="22">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="22">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="F9" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="12">
         <v>46075.0</v>
       </c>
       <c r="H9" s="6"/>
@@ -3023,18 +3023,18 @@
       <c r="T9" s="6"/>
     </row>
     <row r="10" ht="89.25" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>78</v>
+      <c r="A10" s="17"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -3051,25 +3051,25 @@
       <c r="T10" s="6"/>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="30">
+      <c r="A11" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="22">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="22">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="22">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="22">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="15"/>
+      <c r="F11" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="11"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
@@ -3085,15 +3085,15 @@
       <c r="T11" s="6"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
@@ -24406,222 +24406,222 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="11">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="19">
         <v>46082.0</v>
       </c>
     </row>
     <row r="4" ht="69.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="18" t="s">
-        <v>17</v>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="17" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="16">
+        <v>46084.0</v>
+      </c>
+      <c r="C5" s="16">
+        <v>46085.0</v>
+      </c>
+      <c r="D5" s="16">
+        <v>46086.0</v>
+      </c>
+      <c r="E5" s="16">
+        <v>46087.0</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="13">
-        <v>46084.0</v>
-      </c>
-      <c r="C5" s="13">
-        <v>46085.0</v>
-      </c>
-      <c r="D5" s="13">
-        <v>46086.0</v>
-      </c>
-      <c r="E5" s="13">
-        <v>46087.0</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="G5" s="19">
         <v>46089.0</v>
       </c>
     </row>
     <row r="6" ht="113.25" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="31"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="17"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="A7" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="16">
         <v>46091.0</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="16">
         <v>46092.0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="16">
         <v>46093.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="16">
         <v>46094.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="11">
+      <c r="F7" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="19">
         <v>46096.0</v>
       </c>
     </row>
     <row r="8" ht="87.0" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="18" t="s">
+      <c r="A8" s="8"/>
+      <c r="B8" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="10"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="8"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="16">
         <v>46098.0</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="19">
         <v>46099.0</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="28">
         <v>46100.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="16">
         <v>46101.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="F9" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="19">
         <v>46103.0</v>
       </c>
     </row>
     <row r="10" ht="96.0" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="5"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="13">
+      <c r="A11" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="16">
         <v>46105.0</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="16">
         <v>46106.0</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="16">
         <v>46107.0</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="16">
         <v>46108.0</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="11">
+      <c r="F11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="19">
         <v>46110.0</v>
       </c>
     </row>
     <row r="12" ht="91.5" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>68</v>
+      <c r="A12" s="8"/>
+      <c r="B12" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="F12" s="39"/>
       <c r="G12" s="39"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="16">
         <v>46112.0</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" ht="95.25" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -24650,192 +24650,192 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="13">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="16">
         <v>46113.0</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="16">
         <v>46114.0</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="16">
         <v>46115.0</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="19">
         <v>46117.0</v>
       </c>
     </row>
     <row r="4" ht="99.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="10"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="16">
         <v>46119.0</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="16">
         <v>46120.0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="16">
         <v>46121.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="16">
         <v>46122.0</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="19">
         <v>46124.0</v>
       </c>
     </row>
     <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="21" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="17"/>
+      <c r="G6" s="23" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="A7" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="16">
         <v>46126.0</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="28">
         <v>46127.0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="16">
         <v>46128.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="16">
         <v>46129.0</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="11">
+      <c r="F7" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="19">
         <v>46131.0</v>
       </c>
     </row>
     <row r="8" ht="80.25" customHeight="1">
-      <c r="A8" s="28"/>
+      <c r="A8" s="30"/>
       <c r="B8" s="32"/>
-      <c r="C8" s="10"/>
+      <c r="C8" s="8"/>
       <c r="D8" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="21" t="s">
         <v>46</v>
       </c>
+      <c r="E8" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="17"/>
+      <c r="G8" s="23" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="16">
         <v>46133.0</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="16">
         <v>46134.0</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="19">
         <v>46135.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="16">
         <v>46136.0</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="F9" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="19">
         <v>46138.0</v>
       </c>
     </row>
     <row r="10" ht="92.25" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="13">
+      <c r="A11" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="16">
         <v>46140.0</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="16">
         <v>46141.0</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="16">
         <v>46142.0</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
       <c r="D12" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+        <v>67</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13">
       <c r="D13" s="38"/>
@@ -24869,224 +24869,224 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="14" t="s">
+    </row>
+    <row r="4" ht="94.5" customHeight="1">
+      <c r="A4" s="8"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="F4" s="45"/>
+      <c r="G4" s="23" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="45" t="s">
+    <row r="5" ht="20.25" customHeight="1">
+      <c r="A5" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="21" t="s">
+      <c r="B5" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="17" t="s">
+    <row r="6" ht="91.5" customHeight="1">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="G6" s="45"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="B7" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="C7" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="E7" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="F7" s="18" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="21" t="s">
+      <c r="G7" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="47" t="s">
-        <v>108</v>
-      </c>
-      <c r="F6" s="49" t="s">
+    </row>
+    <row r="8" ht="97.5" customHeight="1">
+      <c r="A8" s="17"/>
+      <c r="B8" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="G6" s="46"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="F8" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="17" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="C9" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E9" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G9" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" ht="93.75" customHeight="1">
+      <c r="A10" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="G7" s="14" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="52" t="s">
+      <c r="F10" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="C11" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="F8" s="49" t="s">
+      <c r="D11" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="F11" s="18" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="G11" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="G12" s="54" t="s">
-        <v>158</v>
+      <c r="A12" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -25116,219 +25116,219 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>96</v>
+      <c r="A3" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>16</v>
+      <c r="A4" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>17</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="G4" s="18"/>
+        <v>143</v>
+      </c>
+      <c r="G4" s="17"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>123</v>
+      <c r="A5" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="6" ht="183.75" customHeight="1">
-      <c r="A6" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>138</v>
+      <c r="A6" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>153</v>
+      <c r="A7" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="8" ht="101.25" customHeight="1">
-      <c r="A8" s="52" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="52" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="G8" s="21" t="s">
+      <c r="A8" s="49" t="s">
         <v>164</v>
       </c>
+      <c r="B8" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>169</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="17" t="s">
+      <c r="A9" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="C9" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="18" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="10" ht="99.75" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="21" t="s">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="23" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25359,74 +25359,74 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="13">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="16">
         <v>46204.0</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="16">
         <v>46205.0</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="16">
         <v>46206.0</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="19">
         <v>46208.0</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="52" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="16">
         <v>46211.0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="16">
         <v>46212.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="16">
         <v>46213.0</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="19">
         <v>46215.0</v>
       </c>
     </row>
@@ -25434,38 +25434,38 @@
       <c r="A6" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="52" t="s">
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="23" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="28">
         <v>46218.0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="16">
         <v>46219.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="16">
         <v>46220.0</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="18" t="s">
         <v>194</v>
       </c>
       <c r="G7" s="56">
@@ -25473,79 +25473,79 @@
       </c>
     </row>
     <row r="8" ht="88.5" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="52" t="s">
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="16">
         <v>46225.0</v>
       </c>
       <c r="D9" s="57">
         <v>46226.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="16">
         <v>46227.0</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="19">
         <v>46229.0</v>
       </c>
     </row>
     <row r="10" ht="77.25" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="49" t="s">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="47" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="16">
         <v>46232.0</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="16">
         <v>46233.0</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25576,215 +25576,215 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="50" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="14" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="19">
         <v>46236.0</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="52" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="16">
         <v>46239.0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="16">
         <v>46240.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="16">
         <v>46241.0</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="19">
         <v>46243.0</v>
       </c>
     </row>
     <row r="6" ht="84.0" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="21" t="s">
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="16">
         <v>46246.0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="16">
         <v>46247.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="16">
         <v>46248.0</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="19">
         <v>46250.0</v>
       </c>
     </row>
     <row r="8" ht="93.75" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="52" t="s">
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="16">
         <v>46253.0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="16">
         <v>46254.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="16">
         <v>46255.0</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="19">
         <v>46257.0</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="52" t="s">
+      <c r="A10" s="27"/>
+      <c r="B10" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="52" t="s">
+      <c r="C10" s="40"/>
+      <c r="D10" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="52" t="s">
+      <c r="E10" s="27"/>
+      <c r="F10" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="23" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="16">
         <v>46260.0</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="16">
         <v>46261.0</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="16">
         <v>46262.0</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="19">
         <v>46264.0</v>
       </c>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="52" t="s">
+      <c r="A12" s="27"/>
+      <c r="B12" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="21" t="s">
+      <c r="C12" s="27"/>
+      <c r="D12" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
-      <c r="A14" s="26"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="27"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25815,58 +25815,58 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="50" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="16">
         <v>46267.0</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="16">
         <v>46268.0</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="16">
         <v>46269.0</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="19">
         <v>46271.0</v>
       </c>
     </row>
     <row r="4" ht="85.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
       <c r="E4" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="21" t="s">
         <v>227</v>
       </c>
       <c r="B5" s="59" t="s">
@@ -25878,29 +25878,29 @@
       <c r="D5" s="61">
         <v>46275.0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="16">
         <v>46276.0</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="19">
         <v>46278.0</v>
       </c>
     </row>
     <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="21" t="s">
         <v>231</v>
       </c>
       <c r="B7" s="59" t="s">
@@ -25909,97 +25909,97 @@
       <c r="C7" s="60">
         <v>46281.0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="16">
         <v>46282.0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="16">
         <v>46283.0</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="19">
         <v>46285.0</v>
       </c>
     </row>
     <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="16">
         <v>46288.0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="16">
         <v>46289.0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="16">
         <v>46290.0</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="19">
         <v>46292.0</v>
       </c>
     </row>
     <row r="10" ht="98.25" customHeight="1">
-      <c r="A10" s="62" t="s">
-        <v>240</v>
-      </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="62" t="s">
+      <c r="A10" s="63" t="s">
         <v>241</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="63" t="s">
         <v>242</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="F10" s="23" t="s">
         <v>243</v>
       </c>
+      <c r="G10" s="23" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="C11" s="13">
+      <c r="B11" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="16">
         <v>46295.0</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,12 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="348">
+  <si>
+    <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
+  </si>
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
   <si>
-    <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
+    <t>OCAK</t>
   </si>
   <si>
     <t xml:space="preserve">NİSAN </t>
@@ -55,43 +58,25 @@
     </r>
   </si>
   <si>
-    <t>OCAK</t>
+    <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
   </si>
   <si>
     <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
+    <t>5 Ocak 2026 Pazartesi</t>
   </si>
   <si>
     <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve"> 3 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>5 Ocak 2026 Pazartesi</t>
+    <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
   </si>
   <si>
     <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
   </si>
   <si>
     <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
-  </si>
-  <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>CHP Eğitim 17.00-20.00</t>
   </si>
   <si>
     <t>Çeşme Belediyesi Türk Halk Müziği Korosu “ Çeşme’den Türkü Akıyor” 2026 Kış Konseri
@@ -100,52 +85,43 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
+    <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
   </si>
   <si>
+    <t>CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
     <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
   </si>
   <si>
-    <t>Ot Festivali ile ilgili toplantı 14.00</t>
-  </si>
-  <si>
     <t>13 Nisan 2026 Pazartesi</t>
   </si>
   <si>
-    <t>İstiklal Marşı Kabulü Provası</t>
-  </si>
-  <si>
-    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
-  </si>
-  <si>
-    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
-  </si>
-  <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
   </si>
   <si>
     <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
@@ -155,46 +131,49 @@
 *16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
   </si>
   <si>
-    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
+  </si>
+  <si>
+    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
+  </si>
+  <si>
+    <t>Ot Festivali ile ilgili toplantı 14.00</t>
   </si>
   <si>
     <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
   </si>
   <si>
+    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+  </si>
+  <si>
+    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
+  </si>
+  <si>
+    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
+  </si>
+  <si>
+    <t>YARI YIL ETKİNLİKLERİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
     <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
   </si>
   <si>
-    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>RAMAZAN BAYRAMI</t>
-  </si>
-  <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+    <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
   </si>
   <si>
     <r>
@@ -214,92 +193,113 @@
     </r>
   </si>
   <si>
+    <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
+  </si>
+  <si>
     <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
   </si>
   <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+    <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
+  </si>
+  <si>
+    <t>19 Ocak 2026 Pazartesi</t>
   </si>
   <si>
     <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+  </si>
+  <si>
+    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Belediye TSM Konseri Tüm gün</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>RAMAZAN BAYRAMI</t>
+  </si>
+  <si>
+    <t>31 Ocak 2026 Cumartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+  </si>
+  <si>
+    <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
+  </si>
+  <si>
+    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
+  </si>
+  <si>
     <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
     <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
   </si>
   <si>
-    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
     <t>Edebiyat Dostları Derneği "Lüküs Hayat" için Onaylanlandı. Dilekçe geldi.                     Serap Hanım: 05359751764</t>
   </si>
   <si>
-    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
-  </si>
-  <si>
-    <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
+    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
   </si>
   <si>
     <t xml:space="preserve">23 Şubat 2026 Pazartesi </t>
   </si>
   <si>
-    <t>YARI YIL ETKİNLİKLERİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
+    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
   </si>
   <si>
     <t>28 Şubat 2026 Cumartesi</t>
   </si>
   <si>
-    <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
-  </si>
-  <si>
-    <t>19 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
     <t>CHP İlçe Eğitim tüm gün</t>
   </si>
   <si>
-    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
     <t>Kaymakamlık 18 Mart Etkinliği Provası</t>
   </si>
   <si>
     <t xml:space="preserve">Kaymakamlık 18 Mart Etkinliği 8.30-13.00 arası </t>
-  </si>
-  <si>
-    <t>31 Ocak 2026 Cumartesi</t>
   </si>
   <si>
     <t>-Taşınmazın Pazarlıkla Satışı Adliye 11.00 
 -Çeşme Kaymakamlığı Himayesi Türk Halk Müziği Konseri 20.00</t>
   </si>
   <si>
-    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
-  </si>
-  <si>
-    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
+    <t>Ot festivali gıda ve ot stant toplantıları için opsiyonlandı</t>
   </si>
   <si>
     <t xml:space="preserve">30 Mart 2026 Pazartesi </t>
@@ -357,9 +357,6 @@
   </si>
   <si>
     <t xml:space="preserve">12 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
   <si>
     <t xml:space="preserve">13 MAYIS 2026 ÇARŞAMBA </t>
@@ -382,9 +379,6 @@
   <si>
     <t>Bilgiç Anaokulu Prova 
 10.30-15.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAZİRAN </t>
   </si>
   <si>
     <t xml:space="preserve">Bilgiç Anaokulu Prova 
@@ -428,9 +422,6 @@
   </si>
   <si>
     <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
     <r>
@@ -453,12 +444,42 @@
     <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
   </si>
   <si>
+    <t>BAYRAM</t>
+  </si>
+  <si>
+    <t>25 MAYIS 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAZİRAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
   </si>
   <si>
-    <t>BAYRAM</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
@@ -468,28 +489,7 @@
     <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
-    <t>25 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
   </si>
   <si>
     <t>7 HAZİRAN 2026 PAZAR</t>
@@ -534,6 +534,9 @@
   <si>
     <t>Bilgiç İlkokulu 13.00 1. Sınıf Okuma Bayramı 18.00
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMMUZ </t>
   </si>
   <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
@@ -584,6 +587,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t>-SERTUR KOOPERATİF TOPLANTISI HALUK BEY 05336460236 
 15.00'a kadar
 - Kent Enstitüsü Prova</t>
@@ -598,6 +604,10 @@
     <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t>Latin Katolik Kilisesi Ayin 
+18.30</t>
+  </si>
+  <si>
     <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
   </si>
   <si>
@@ -614,6 +624,12 @@
   </si>
   <si>
     <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
   </si>
   <si>
     <t>Atatürk Lisesi tiyatro prova</t>
@@ -629,6 +645,9 @@
 sabahtan 21.00'a kadar</t>
   </si>
   <si>
+    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
   </si>
   <si>
@@ -636,59 +655,6 @@
   </si>
   <si>
     <t>Doğu Der Toplantı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Reyhan Cici Piyano Dinletisi
-Ödendi. Dilekçe geldi. Tel no:5320631925 12.00-20.00</t>
-  </si>
-  <si>
-    <t>MHP 15. Olağan Kongre Toplantısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEMMUZ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Latin Katolik Kilisesi Ayin 
-18.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
   </si>
   <si>
     <t>-Çoklu İklim Krizinin Gölgesinde Orman Yangınları
@@ -696,19 +662,53 @@
 -Belediye Meclisi 17.00'dan sonra</t>
   </si>
   <si>
+    <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 HAZİRAN 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t>Belediye meclisi 16.00'dan sonra</t>
   </si>
   <si>
+    <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
+  </si>
+  <si>
     <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
   </si>
   <si>
     <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
   </si>
   <si>
+    <t>Reyhan Cici Piyano Dinletisi
+Ödendi. Dilekçe geldi. Tel no:5320631925 12.00-20.00</t>
+  </si>
+  <si>
     <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t>MHP 15. Olağan Kongre Toplantısı</t>
+  </si>
+  <si>
     <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
   </si>
   <si>
     <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
@@ -809,35 +809,125 @@
     <t xml:space="preserve">EYLÜL </t>
   </si>
   <si>
+    <t xml:space="preserve">EKİM </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t>3 EKİM 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>Yeni Parti Toplantı</t>
   </si>
   <si>
     <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
 Haydar Ali tel no: 5527151935</t>
   </si>
   <si>
+    <t>5 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
+  </si>
+  <si>
     <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
   </si>
   <si>
+    <t>Hafifletici Sebepler opsiyon</t>
+  </si>
+  <si>
+    <t>12 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
+    <t>KENT KONSEYİ OPSİYON (HER HAFTA ÇARŞAMBA 20.00 - 230.00 ARASI KULLANIM İÇİN DİLEKÇE YAZILACAK)</t>
+  </si>
+  <si>
     <t>Belediye Meclis 15.00 Tüm alan</t>
   </si>
   <si>
+    <t>İZMİR KENT TİYATROSU 05547273157</t>
+  </si>
+  <si>
     <t xml:space="preserve">14 EYLÜL 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t>19 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">15 EYLÜL 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">20 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
     <t xml:space="preserve">19 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
   </si>
   <si>
     <t xml:space="preserve">09:00-16:00 
@@ -845,14 +935,38 @@
 Müdürlüğü   ( İzmir Yurttaş Meclisi) </t>
   </si>
   <si>
+    <t>KENT KONSEYİ OPSİYON</t>
+  </si>
+  <si>
     <t xml:space="preserve">12:30-17:00
 İzmir Büyükşehir Belediyesi Sosyal Hizmetler Dairesi Başkanlığı Kentsel Adalet ve Eşitlik Şube
 Müdürlüğü   ( İzmir Yurttaş Meclisi) </t>
   </si>
   <si>
+    <t>KENT ENS. TİYATRO KURSİYER OYUNU "SEVGİLİ DOKTOR" AYSEL GÜZEL</t>
+  </si>
+  <si>
     <t>Çeşme Belediyespor Tekwando velileri toplantı 16.00-17.00</t>
   </si>
   <si>
+    <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">21 EYLÜL 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -860,9 +974,6 @@
   </si>
   <si>
     <t xml:space="preserve">26 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EKİM </t>
   </si>
   <si>
     <t>Osman Uysal Konser Prova 18.00-22.00</t>
@@ -911,108 +1022,6 @@
   </si>
   <si>
     <t xml:space="preserve">29 EYLÜL 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t>3 EKİM 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Yeni Parti Toplantı</t>
-  </si>
-  <si>
-    <t>5 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Hafifletici Sebepler opsiyon</t>
-  </si>
-  <si>
-    <t>12 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>İZMİR KENT TİYATROSU 05547273157</t>
-  </si>
-  <si>
-    <t>19 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">KASIM </t>
@@ -1244,6 +1253,7 @@
     </font>
     <font>
       <b/>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1256,14 +1266,13 @@
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="15.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1297,13 +1306,13 @@
     </font>
     <font>
       <b/>
+      <sz val="13.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1324,14 +1333,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6B26B"/>
-        <bgColor rgb="FFF6B26B"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor rgb="FFF9CB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF6B26B"/>
       </patternFill>
     </fill>
     <fill>
@@ -1342,26 +1357,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9CB9C"/>
-        <bgColor rgb="FFF9CB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF93C47D"/>
         <bgColor rgb="FF93C47D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -1433,112 +1442,115 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1546,17 +1558,14 @@
     <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1574,62 +1583,65 @@
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="15" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1904,212 +1916,212 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="19">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="11">
         <v>46023.0</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="12">
         <v>46024.0</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="19">
+      <c r="F3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="11">
         <v>46026.0</v>
       </c>
     </row>
     <row r="4" ht="95.25" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="12">
+        <v>46028.0</v>
+      </c>
+      <c r="C5" s="12">
+        <v>46029.0</v>
+      </c>
+      <c r="D5" s="12">
+        <v>46030.0</v>
+      </c>
+      <c r="E5" s="12">
+        <v>46031.0</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="16">
-        <v>46028.0</v>
-      </c>
-      <c r="C5" s="16">
-        <v>46029.0</v>
-      </c>
-      <c r="D5" s="16">
-        <v>46030.0</v>
-      </c>
-      <c r="E5" s="16">
-        <v>46031.0</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="19">
+      <c r="G5" s="11">
         <v>46033.0</v>
       </c>
     </row>
     <row r="6" ht="97.5" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="26" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="18.0" customHeight="1">
+      <c r="A7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="16">
+      <c r="B7" s="12">
         <v>46035.0</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="25">
         <v>46036.0</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="25">
         <v>46037.0</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>46038.0</v>
       </c>
-      <c r="F7" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="33">
+      <c r="F7" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="28">
         <v>46040.0</v>
       </c>
     </row>
     <row r="8" ht="69.0" customHeight="1">
       <c r="A8" s="17" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="E8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="12">
+        <v>46042.0</v>
+      </c>
+      <c r="C9" s="25">
+        <v>46043.0</v>
+      </c>
+      <c r="D9" s="25">
+        <v>46044.0</v>
+      </c>
+      <c r="E9" s="12">
+        <v>46045.0</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="11">
+        <v>46047.0</v>
+      </c>
+    </row>
+    <row r="10" ht="78.75" customHeight="1">
+      <c r="A10" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="27"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="B11" s="12">
+        <v>46049.0</v>
+      </c>
+      <c r="C11" s="25">
+        <v>46050.0</v>
+      </c>
+      <c r="D11" s="25">
+        <v>46051.0</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46052.0</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="16">
-        <v>46042.0</v>
-      </c>
-      <c r="C9" s="28">
-        <v>46043.0</v>
-      </c>
-      <c r="D9" s="28">
-        <v>46044.0</v>
-      </c>
-      <c r="E9" s="16">
-        <v>46045.0</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="19">
-        <v>46047.0</v>
-      </c>
-    </row>
-    <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="27"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="16">
-        <v>46049.0</v>
-      </c>
-      <c r="C11" s="28">
-        <v>46050.0</v>
-      </c>
-      <c r="D11" s="28">
-        <v>46051.0</v>
-      </c>
-      <c r="E11" s="16">
-        <v>46052.0</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="8"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
       <c r="A12" s="17"/>
       <c r="B12" s="17" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
       <c r="F12" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="40"/>
+        <v>68</v>
+      </c>
+      <c r="G12" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2137,189 +2149,197 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="64" t="s">
-        <v>240</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="59" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>250</v>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="4" ht="84.0" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="27"/>
       <c r="E4" s="27"/>
-      <c r="F4" s="49" t="s">
-        <v>251</v>
+      <c r="F4" s="60" t="s">
+        <v>231</v>
       </c>
       <c r="G4" s="49" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>258</v>
+      <c r="A5" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="65" t="s">
-        <v>259</v>
+      <c r="C6" s="63" t="s">
+        <v>242</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="27"/>
-      <c r="F6" s="66" t="s">
-        <v>259</v>
+      <c r="F6" s="60" t="s">
+        <v>242</v>
       </c>
       <c r="G6" s="27"/>
-      <c r="L6" s="67"/>
+      <c r="L6" s="65"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>266</v>
+      <c r="A7" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
+      <c r="C8" s="67" t="s">
+        <v>251</v>
+      </c>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="68" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>274</v>
+      <c r="A9" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="10" ht="100.5" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
+      <c r="C10" s="60" t="s">
+        <v>265</v>
+      </c>
       <c r="D10" s="27"/>
       <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="F10" s="67" t="s">
+        <v>267</v>
+      </c>
       <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="G11" s="8"/>
+      <c r="A11" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
+      <c r="C12" s="60" t="s">
+        <v>265</v>
+      </c>
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
       <c r="F12" s="27"/>
-      <c r="G12" s="8"/>
+      <c r="G12" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2346,67 +2366,67 @@
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="42" t="s">
-        <v>281</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="21" t="s">
-        <v>282</v>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="19" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
       <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="D5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>286</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="B5" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>288</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>289</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
@@ -2419,26 +2439,26 @@
       <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="D7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="B7" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>296</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
@@ -2451,26 +2471,26 @@
       <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="D9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="B9" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>302</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>303</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
@@ -2483,26 +2503,26 @@
       <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="D11" s="21" t="s">
+      <c r="A11" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="B11" s="19" t="s">
         <v>308</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>310</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
@@ -2512,29 +2532,29 @@
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
       <c r="F12" s="27"/>
-      <c r="G12" s="69" t="s">
-        <v>311</v>
+      <c r="G12" s="70" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="A13" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
       <c r="A14" s="27"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2563,49 +2583,49 @@
   <sheetData>
     <row r="1" ht="35.25" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="50" t="s">
-        <v>313</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="51" t="s">
+        <v>316</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="43"/>
-      <c r="B3" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="E3" s="21" t="s">
+      <c r="B3" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>319</v>
       </c>
+      <c r="E3" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="8"/>
+      <c r="A4" s="9"/>
       <c r="B4" s="27"/>
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
@@ -2614,26 +2634,26 @@
       <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="D5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="B5" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>326</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
@@ -2646,26 +2666,26 @@
       <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="D7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="B7" s="19" t="s">
         <v>331</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>333</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
@@ -2678,26 +2698,26 @@
       <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="D9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="B9" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>340</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
@@ -2710,30 +2730,30 @@
       <c r="G10" s="27"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="D11" s="21" t="s">
+      <c r="A11" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="B11" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2762,13 +2782,13 @@
   <sheetData>
     <row r="1" ht="63.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2785,14 +2805,14 @@
       <c r="T1" s="6"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -2809,13 +2829,13 @@
       <c r="T2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="18">
         <v>46054.0</v>
       </c>
       <c r="H3" s="6"/>
@@ -2833,12 +2853,12 @@
       <c r="T3" s="6"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="17"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -2855,25 +2875,25 @@
       <c r="T4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="22">
+      <c r="A5" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="26">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="26">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="26">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="26">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="12">
+      <c r="F5" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="18">
         <v>46061.0</v>
       </c>
       <c r="H5" s="6"/>
@@ -2892,17 +2912,17 @@
     </row>
     <row r="6" ht="93.75" customHeight="1">
       <c r="A6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+        <v>33</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
       <c r="F6" s="17" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -2919,25 +2939,25 @@
       <c r="T6" s="6"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="22">
+      <c r="A7" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="26">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="26">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="26">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="26">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="12">
+      <c r="F7" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="18">
         <v>46068.0</v>
       </c>
       <c r="H7" s="6"/>
@@ -2955,22 +2975,22 @@
       <c r="T7" s="6"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="11"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="31" t="s">
-        <v>34</v>
+        <v>55</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="35" t="s">
+        <v>57</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -2987,25 +3007,25 @@
       <c r="T8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="22">
+      <c r="A9" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="26">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="26">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="26">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="26">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="12">
+      <c r="F9" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="18">
         <v>46075.0</v>
       </c>
       <c r="H9" s="6"/>
@@ -3024,17 +3044,17 @@
     </row>
     <row r="10" ht="89.25" customHeight="1">
       <c r="A10" s="17"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="17" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -3051,25 +3071,25 @@
       <c r="T10" s="6"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="A11" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="26">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="26">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="26">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="26">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="11"/>
+      <c r="F11" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="16"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
@@ -3085,15 +3105,15 @@
       <c r="T11" s="6"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
       <c r="D12" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+        <v>80</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
@@ -24406,147 +24426,147 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
       <c r="A2" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="19">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="11">
         <v>46082.0</v>
       </c>
     </row>
     <row r="4" ht="69.0" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
       <c r="G4" s="17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="16">
+      <c r="A5" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12">
         <v>46084.0</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="12">
         <v>46085.0</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="12">
         <v>46086.0</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>46087.0</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="11">
         <v>46089.0</v>
       </c>
     </row>
     <row r="6" ht="113.25" customHeight="1">
-      <c r="A6" s="8"/>
+      <c r="A6" s="9"/>
       <c r="B6" s="27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="17" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F6" s="17"/>
-      <c r="G6" s="29"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="16">
+      <c r="A7" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="12">
         <v>46091.0</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="12">
         <v>46092.0</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="12">
         <v>46093.0</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>46094.0</v>
       </c>
-      <c r="F7" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="19">
+      <c r="F7" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="11">
         <v>46096.0</v>
       </c>
     </row>
     <row r="8" ht="87.0" customHeight="1">
-      <c r="A8" s="8"/>
+      <c r="A8" s="9"/>
       <c r="B8" s="27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="8"/>
+        <v>45</v>
+      </c>
+      <c r="E8" s="9"/>
       <c r="F8" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="8"/>
+        <v>47</v>
+      </c>
+      <c r="G8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="16">
+      <c r="A9" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="12">
         <v>46098.0</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="11">
         <v>46099.0</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="25">
         <v>46100.0</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>46101.0</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="F9" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="11">
         <v>46103.0</v>
       </c>
     </row>
@@ -24554,74 +24574,74 @@
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
-      <c r="D10" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="D10" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
       <c r="G10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="16">
+      <c r="A11" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="12">
         <v>46105.0</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="12">
         <v>46106.0</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="12">
         <v>46107.0</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="12">
         <v>46108.0</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="19">
+      <c r="F11" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="11">
         <v>46110.0</v>
       </c>
     </row>
     <row r="12" ht="91.5" customHeight="1">
-      <c r="A12" s="8"/>
+      <c r="A12" s="9"/>
       <c r="B12" s="17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
+        <v>79</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="12">
         <v>46112.0</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" ht="95.25" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -24650,195 +24670,195 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="16">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="12">
         <v>46113.0</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="12">
         <v>46114.0</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="12">
         <v>46115.0</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="19">
+      <c r="F3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="11">
         <v>46117.0</v>
       </c>
     </row>
     <row r="4" ht="99.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="17"/>
-      <c r="G4" s="8"/>
+      <c r="G4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="16">
+      <c r="A5" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="12">
         <v>46119.0</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="12">
         <v>46120.0</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="12">
         <v>46121.0</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>46122.0</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="11">
         <v>46124.0</v>
       </c>
     </row>
     <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>17</v>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>20</v>
       </c>
       <c r="F6" s="17"/>
-      <c r="G6" s="23" t="s">
-        <v>20</v>
+      <c r="G6" s="22" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="16">
+      <c r="A7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="12">
         <v>46126.0</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="25">
         <v>46127.0</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="12">
         <v>46128.0</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>46129.0</v>
       </c>
-      <c r="F7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="19">
+      <c r="F7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="11">
         <v>46131.0</v>
       </c>
     </row>
     <row r="8" ht="80.25" customHeight="1">
       <c r="A8" s="30"/>
       <c r="B8" s="32"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="34" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="17"/>
+      <c r="G8" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="23" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="16">
+      <c r="A9" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="12">
         <v>46133.0</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="12">
         <v>46134.0</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="11">
         <v>46135.0</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>46136.0</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="11">
+        <v>46138.0</v>
+      </c>
+    </row>
+    <row r="10" ht="92.25" customHeight="1">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="19">
-        <v>46138.0</v>
-      </c>
-    </row>
-    <row r="10" ht="92.25" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="16">
+      <c r="A11" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="12">
         <v>46140.0</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="12">
         <v>46141.0</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="12">
         <v>46142.0</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13">
-      <c r="D13" s="38"/>
+      <c r="D13" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24867,84 +24887,84 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="18" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="15" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="8"/>
+      <c r="A4" s="9"/>
       <c r="B4" s="43"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
       <c r="E4" s="44" t="s">
         <v>86</v>
       </c>
       <c r="F4" s="45"/>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="22" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="15" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="23" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="9"/>
       <c r="E6" s="46" t="s">
         <v>96</v>
       </c>
@@ -24954,139 +24974,139 @@
       <c r="G6" s="45"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="E7" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="F7" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="G7" s="15" t="s">
         <v>104</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
       <c r="A8" s="17"/>
       <c r="B8" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="D8" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="E8" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="G8" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F8" s="47" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="B9" s="15" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="s">
+      <c r="C9" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="E9" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="F9" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="G9" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F9" s="18" t="s">
+    </row>
+    <row r="10" ht="93.75" customHeight="1">
+      <c r="A10" s="22" t="s">
         <v>118</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="23" t="s">
-        <v>120</v>
       </c>
       <c r="B10" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="F10" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="B11" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="F10" s="51" t="s">
+      <c r="C11" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="51" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>137</v>
+      <c r="E11" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>126</v>
+      <c r="A12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -25116,51 +25136,51 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="18" t="s">
+      <c r="A3" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="D3" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>139</v>
       </c>
       <c r="B4" s="17" t="s">
@@ -25173,126 +25193,126 @@
         <v>142</v>
       </c>
       <c r="E4" s="52" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G4" s="17"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="B5" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="C5" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="D5" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="15" t="s">
         <v>150</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="6" ht="183.75" customHeight="1">
       <c r="A6" s="53" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="E6" s="25" t="s">
         <v>154</v>
       </c>
+      <c r="E6" s="24" t="s">
+        <v>156</v>
+      </c>
       <c r="F6" s="54" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="21" t="s">
+      <c r="B7" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>163</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="8" ht="101.25" customHeight="1">
       <c r="A8" s="49" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>166</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>168</v>
+        <v>171</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>174</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>169</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>177</v>
+      <c r="A9" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="10" ht="99.75" customHeight="1">
@@ -25301,25 +25321,25 @@
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
       <c r="E10" s="27"/>
-      <c r="F10" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>179</v>
+      <c r="F10" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="A11" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
       <c r="A12" s="27"/>
@@ -25357,115 +25377,115 @@
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="50" t="s">
-        <v>182</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="16">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="12">
         <v>46204.0</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="12">
         <v>46205.0</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="12">
         <v>46206.0</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="G3" s="19">
+      <c r="F3" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="G3" s="11">
         <v>46208.0</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
       <c r="E4" s="27"/>
       <c r="F4" s="49" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="G4" s="17"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="C5" s="16">
+      <c r="A5" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="12">
         <v>46211.0</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="12">
         <v>46212.0</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>46213.0</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="G5" s="19">
+      <c r="F5" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="G5" s="11">
         <v>46215.0</v>
       </c>
     </row>
     <row r="6" ht="92.25" customHeight="1">
       <c r="A6" s="55" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="27"/>
       <c r="D6" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="E6" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="G6" s="23" t="s">
+      <c r="B7" s="19" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="C7" s="28">
+      <c r="C7" s="25">
         <v>46218.0</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="12">
         <v>46219.0</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>46220.0</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="15" t="s">
         <v>194</v>
       </c>
       <c r="G7" s="56">
@@ -25479,30 +25499,30 @@
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="49" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="12">
         <v>46225.0</v>
       </c>
       <c r="D9" s="57">
         <v>46226.0</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>46227.0</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="11">
         <v>46229.0</v>
       </c>
     </row>
@@ -25520,32 +25540,32 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="12">
         <v>46232.0</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="12">
         <v>46233.0</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25574,70 +25594,70 @@
   <sheetData>
     <row r="1" ht="34.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="18" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="11">
         <v>46236.0</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="49" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="12">
         <v>46239.0</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="12">
         <v>46240.0</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>46241.0</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="11">
         <v>46243.0</v>
       </c>
     </row>
@@ -25647,31 +25667,31 @@
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
       <c r="E6" s="27"/>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="22" t="s">
         <v>208</v>
       </c>
       <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="12">
         <v>46246.0</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="12">
         <v>46247.0</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>46248.0</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="11">
         <v>46250.0</v>
       </c>
     </row>
@@ -25682,30 +25702,30 @@
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="49" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="12">
         <v>46253.0</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="12">
         <v>46254.0</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>46255.0</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="11">
         <v>46257.0</v>
       </c>
     </row>
@@ -25714,38 +25734,38 @@
       <c r="B10" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="C10" s="40"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="49" t="s">
         <v>215</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="G10" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="G10" s="22" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="12">
         <v>46260.0</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="12">
         <v>46261.0</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="12">
         <v>46262.0</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="11">
         <v>46264.0</v>
       </c>
     </row>
@@ -25755,36 +25775,36 @@
         <v>215</v>
       </c>
       <c r="C12" s="27"/>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="22" t="s">
         <v>220</v>
       </c>
       <c r="E12" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="22" t="s">
         <v>221</v>
       </c>
       <c r="G12" s="27"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
       <c r="A14" s="27"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25813,84 +25833,84 @@
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="C3" s="16">
+      <c r="A3" s="9"/>
+      <c r="B3" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="12">
         <v>46267.0</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="12">
         <v>46268.0</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="12">
         <v>46269.0</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="G3" s="19">
+      <c r="F3" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="G3" s="11">
         <v>46271.0</v>
       </c>
     </row>
     <row r="4" ht="85.5" customHeight="1">
-      <c r="A4" s="8"/>
+      <c r="A4" s="9"/>
       <c r="B4" s="27"/>
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
-      <c r="E4" s="58" t="s">
-        <v>226</v>
+      <c r="E4" s="61" t="s">
+        <v>232</v>
       </c>
       <c r="F4" s="27"/>
       <c r="G4" s="27"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" s="60">
+      <c r="A5" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="64">
         <v>46274.0</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="66">
         <v>46275.0</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>46276.0</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="G5" s="19">
+      <c r="F5" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="G5" s="11">
         <v>46278.0</v>
       </c>
     </row>
     <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="23" t="s">
-        <v>230</v>
+      <c r="A6" s="22" t="s">
+        <v>252</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="27"/>
@@ -25900,37 +25920,37 @@
       <c r="G6" s="27"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" s="60">
+      <c r="A7" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="64">
         <v>46281.0</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="12">
         <v>46282.0</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>46283.0</v>
       </c>
-      <c r="F7" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="G7" s="19">
+      <c r="F7" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="11">
         <v>46285.0</v>
       </c>
     </row>
     <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>236</v>
+      <c r="A8" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>268</v>
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
@@ -25938,68 +25958,68 @@
       <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="C9" s="16">
+      <c r="A9" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="12">
         <v>46288.0</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="12">
         <v>46289.0</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>46290.0</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="F9" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="G9" s="11">
         <v>46292.0</v>
       </c>
     </row>
     <row r="10" ht="98.25" customHeight="1">
-      <c r="A10" s="63" t="s">
-        <v>241</v>
+      <c r="A10" s="69" t="s">
+        <v>278</v>
       </c>
       <c r="B10" s="27"/>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
-      <c r="E10" s="63" t="s">
-        <v>242</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>244</v>
+      <c r="E10" s="69" t="s">
+        <v>279</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="C11" s="16">
+      <c r="A11" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="C11" s="12">
         <v>46295.0</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
       <c r="C12" s="27"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -24,19 +24,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="348">
   <si>
+    <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
+  </si>
+  <si>
+    <t>OCAK</t>
+  </si>
+  <si>
     <t>2026 YILI ÇAKABEY KÜLTÜR MERKEZİ</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
-  </si>
-  <si>
-    <t>OCAK</t>
-  </si>
-  <si>
     <t xml:space="preserve">NİSAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MART </t>
   </si>
   <si>
     <r>
@@ -64,19 +61,13 @@
     <t xml:space="preserve">4 Nisan 2026 Cumartesi </t>
   </si>
   <si>
+    <t xml:space="preserve">MART </t>
+  </si>
+  <si>
     <t>5 Ocak 2026 Pazartesi</t>
   </si>
   <si>
-    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
     <t xml:space="preserve">10 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
   </si>
   <si>
     <t>Çeşme Belediyesi Türk Halk Müziği Korosu “ Çeşme’den Türkü Akıyor” 2026 Kış Konseri
@@ -85,92 +76,113 @@
 Çakabey Kültür Merkezi</t>
   </si>
   <si>
+    <t xml:space="preserve">6 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t>Germiyan Köy Tiyatrosu Prova</t>
+  </si>
+  <si>
+    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
+  </si>
+  <si>
+    <t>CHP Eğitim 17.00-20.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
+  </si>
+  <si>
+    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
+  </si>
+  <si>
+    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
+  </si>
+  <si>
+    <t>Saygun Sanat Kırmızı Balık Müzikali 14.00 ve 16.00 2 seans dilekçe ve ödeme geldi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>YARI YIL ETKİNLİKLERİ</t>
+  </si>
+  <si>
+    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 Mart 2026 Pazartesi </t>
   </si>
   <si>
-    <t>Germiyan Köy Tiyatrosu Prova</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Esnaf ve Sanatkarlar odası toplantısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Ocak 2026 Pazartesi </t>
+    <t>13 Nisan 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t>19 Ocak 2026 Pazartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
   </si>
   <si>
     <t xml:space="preserve">7 Mart 2026 Cumartesi </t>
   </si>
   <si>
-    <t>CHP Eğitim 17.00-20.00</t>
+    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
   </si>
   <si>
     <t>İstiklal Marşı Kabulü Provası</t>
   </si>
   <si>
-    <t>Disk Dev EmekliSen Serdar Şahinkaya söyleşisi 15.00-18.00</t>
-  </si>
-  <si>
-    <t>13 Nisan 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 Nisan 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Şubat 2026 Cumartesi </t>
+    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
   </si>
   <si>
     <t>*İstiklal Marşı Kabulü Provası 09.30-14.30                            *Müdahil yetişkin oyunu dilekçe geldi ödeme alındı.</t>
+  </si>
+  <si>
+    <t>Ot Festivali ile ilgili toplantı 14.00</t>
+  </si>
+  <si>
+    <t>31 Ocak 2026 Cumartesi</t>
   </si>
   <si>
     <t>*18 Mart Şehitleri Anma Günü Provası 
 *16.00'dan sonra Dünyada Bir Yerde Oyunu Çeşme kent konseyi Deniz Karaman tel no:5356820132 Dilekçe geldi ödendi.</t>
   </si>
   <si>
-    <t>İZBB Rahim Ağzı Kanseri ile ilgili konferans 13.30-15.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijital Tarım Toplantısı 15.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarım Müdürü Şerif Bey için ayrıldı. Kavun Çalıştayı </t>
-  </si>
-  <si>
-    <t>Çeşme Kent Enstitüsü Tiyatro Çalışması</t>
-  </si>
-  <si>
-    <t>Ot Festivali ile ilgili toplantı 14.00</t>
+    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
+  </si>
+  <si>
+    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+  </si>
+  <si>
+    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
+  </si>
+  <si>
+    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
   </si>
   <si>
     <t xml:space="preserve">9 Mart 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>İstanbul PAYE Çocuk Tiyatrosu Halil Soner Özaytekin tel no: 053340803734 seans onaylandı. Ödeme alındı.</t>
-  </si>
-  <si>
-    <t>İzmir Kent Tiyatrosu İlknur Barjit Çatal Tel No:05547273157         *14.00 Clown Sirki                       *20.00 Hafifletici Sebepler</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KENT ENS. TİYATRO DERSİ (PAZARTESİ YAPILAMADIĞI İÇİN)</t>
-  </si>
-  <si>
-    <t>Atatürkçü Düşünce Derneği Olağan Genel Kurul Toplantısı Deniz Ahilik Tel no: 05323416330</t>
-  </si>
-  <si>
-    <t>YARI YIL ETKİNLİKLERİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
   </si>
   <si>
     <t xml:space="preserve">14 Şubat 2026 Cumartesi </t>
@@ -193,79 +205,67 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">14 Mart 2026 Cumartesi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
+  </si>
+  <si>
+    <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
+  </si>
+  <si>
+    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
+  </si>
+  <si>
+    <t>18 Mart Provası sabahtan İstiklal Marşı Kabulü Provası</t>
+  </si>
+  <si>
+    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
+  </si>
+  <si>
     <t>İstiklal Marşı Kabulü Kaymakamlık Etkinliği</t>
   </si>
   <si>
-    <t>Artiz Mektebi 20.00                             Tiyatro Tirad Ücretsiz Oyun   Vedat Mehmet Korkmaz 05052926998</t>
+    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
   </si>
   <si>
     <t>Gezgin Kültür Sanat Hologram Çocuk Festivali 13.00-17.00 Deniz Gökpınar Tel no: 05072859296 Dilekçe geldi ve Ödendi. Onaylandı.</t>
   </si>
   <si>
-    <t>19 Ocak 2026 Pazartesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 Nisan 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Sözleşmeli Personel Yemin Töreni Provası11.00                      *CHP İlçe Eğitim 17.00 Betül Araz tel no: 05539119496    </t>
-  </si>
-  <si>
     <t xml:space="preserve">16 Mart 2026 Pazartesi </t>
   </si>
   <si>
-    <t>CHP İlçe Eğitim Betül Araz tel no: 05539119496</t>
-  </si>
-  <si>
-    <t>Tarladan Sofraya Gıda Güvenliği İZBB 14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 Ocak 2026 Cumartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *İnsan Kaynakları Yemin töreni 14.00</t>
+    <t>Belediye TSM Konseri Tüm gün</t>
   </si>
   <si>
     <t xml:space="preserve">25 Nisan 2026 Cumartesi </t>
   </si>
   <si>
-    <t>Belediye TSM Konseri Tüm gün</t>
-  </si>
-  <si>
     <t xml:space="preserve">21 Mart 2026 Cumartesi </t>
   </si>
   <si>
     <t>İZMİR AŞKINA PROVA SAATİ BELLİ OLDUĞUNDA BİLGİ VERİLECEK</t>
   </si>
   <si>
+    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
+  </si>
+  <si>
     <t xml:space="preserve">27 Nisan 2026 Pazartesi </t>
   </si>
   <si>
-    <t xml:space="preserve">26 Ocak 2026 Pazartesi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Şubat 2026 Pazartesi </t>
-  </si>
-  <si>
     <t>RAMAZAN BAYRAMI</t>
   </si>
   <si>
-    <t>31 Ocak 2026 Cumartesi</t>
-  </si>
-  <si>
     <t xml:space="preserve">21 Şubat 2026 Cumartesi </t>
   </si>
   <si>
-    <t>İZBB Aronya Yetiştiriciliği Eğitimi</t>
+    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
   </si>
   <si>
     <t>"Sokratesin Savunması".          Ödeme Geldi. Deniz Karaman: +90 (535) 682 01 32 İPTAL</t>
-  </si>
-  <si>
-    <t>İZBB Hayal Kasabası Çocuk Tiyatrosu 14.00</t>
-  </si>
-  <si>
-    <t>CHP İlçe Eğitim için onaylandı. Betül Araz Tel no: 05539119496</t>
   </si>
   <si>
     <t>Çeşme Şoförler ve Otomobilciler Esnaf Odası Olağan Genel Kurulu Seçimi Tel No: 05326361993</t>
@@ -350,7 +350,13 @@
     <t>21.30 konser provası Başkan ile</t>
   </si>
   <si>
+    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
+  </si>
+  <si>
     <t>İZBB Germiyan Köy Tiyatrosu "Hanginiz Deli" Vedat Güzel Hoca 05324341990 20.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAZİRAN </t>
   </si>
   <si>
     <t>11 MAYIS 2026 PAZARTESİ</t>
@@ -381,12 +387,21 @@
 10.30-15.30</t>
   </si>
   <si>
+    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">Bilgiç Anaokulu Prova 
 10.30-15.30                                               </t>
   </si>
   <si>
+    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
     <t>-Bilgiç ortaokulu 09.00-12.00
 -Bilgiç Anaokulu Gösteri Günü Yıl sonu gösterisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
     <t>Tiyatro Kök35 Güneşi Kim Söndürdü Çocuk Oyunu 14.00
@@ -394,12 +409,24 @@
 onaylandı.</t>
   </si>
   <si>
+    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
     <t>Özhan Bakadur tiyatro provası 16.00'a kadar</t>
   </si>
   <si>
+    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t>18 MAYIS 2026 PAZARTESİ</t>
   </si>
   <si>
+    <t>7 HAZİRAN 2026 PAZAR</t>
+  </si>
+  <si>
     <t xml:space="preserve">19 MAYIS 2026 SALI </t>
   </si>
   <si>
@@ -412,6 +439,9 @@
     <t xml:space="preserve">22 MAYIS 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
+  </si>
+  <si>
     <t>23 MAYIS 2026 CUMARTESİ</t>
   </si>
   <si>
@@ -422,6 +452,23 @@
   </si>
   <si>
     <t>Yabancı Dil Gecesi Provası Bilgiç Ortaokulu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Bilgiç İlkokulu 1. Sınıf Okuma Bayramı  prova 09.30-15.00                                   </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>15.00 sonra  KENT ENSTİTÜSÜ TİYATRO(BAŞKANLI PROVA)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -444,75 +491,7 @@
     <t>Yabancı Dil Gecesi Bilgiç Ortaokulu GÖSTERİ</t>
   </si>
   <si>
-    <t>BAYRAM</t>
-  </si>
-  <si>
-    <t>25 MAYIS 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 YILI  ÇAKABEY KÜLTÜR MERKEZİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAZİRAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 HAZİRAN 2025 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>7 HAZİRAN 2026 PAZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GÜZELBAHÇE BELEDİYESİ "NAAŞI MUHTEREMLER" SAAT 20.00 ÜCRETSİZ                                                    Selin Hn.‎0 506 225 85 48 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">Bilgiç İlkokulu 1. Sınıf Okuma Bayramı  prova 09.30-15.00                                   </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>15.00 sonra  KENT ENSTİTÜSÜ TİYATRO(BAŞKANLI PROVA)</t>
-    </r>
+    <t xml:space="preserve">TEMMUZ </t>
   </si>
   <si>
     <r>
@@ -536,24 +515,48 @@
 Çeşme Blediyespor Genel Kurul Toplantısı (bilgiçten sonra 1 saat)</t>
   </si>
   <si>
-    <t xml:space="preserve">TEMMUZ </t>
+    <t>BAYRAM</t>
+  </si>
+  <si>
+    <t>25 MAYIS 2026 PAZARTESİ</t>
   </si>
   <si>
     <t>İPTAL Lüküs Hayat Kabare onaylandı. Dilekçe ve ödeme geldi. İrem Özer tel no: 5359660071</t>
   </si>
   <si>
+    <t xml:space="preserve">26 MAYIS 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 MAYIS 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 MAYIS 2026 PERŞEMBE </t>
+  </si>
+  <si>
     <t xml:space="preserve">8 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">29 MAYIS 2026 CUMA </t>
+  </si>
+  <si>
     <t xml:space="preserve">9 HAZİRAN 2026 SALI </t>
   </si>
   <si>
+    <t xml:space="preserve">30 MAYIS 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">10 HAZİRAN 2026 ÇARŞAMBA </t>
   </si>
   <si>
+    <t xml:space="preserve">31 MAYIS 2026 PAZAR </t>
+  </si>
+  <si>
     <t xml:space="preserve">11 HAZİRAN 2026 PERŞEMBE </t>
   </si>
   <si>
+    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">12 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
@@ -564,6 +567,10 @@
   </si>
   <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00</t>
+  </si>
+  <si>
+    <t>Latin Katolik Kilisesi Ayin 
+18.30</t>
   </si>
   <si>
     <t>KENT ENSTİTÜSÜ TİYATRO YIL SONU GÖSTERİLERİ 13.00-22.00                                                        "SEVGİLİ DOKTOR"  20.00</t>
@@ -587,74 +594,24 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">4 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
     <t>-SERTUR KOOPERATİF TOPLANTISI HALUK BEY 05336460236 
 15.00'a kadar
 - Kent Enstitüsü Prova</t>
   </si>
   <si>
+    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
     <t>KENT ENSTİTÜSÜ YIL SONU MÜZİK BRANŞLARI GÖSTERİLERİ -                        -11.00 Gitar Dinletisi               - 12.30 Keman Dinletisi          -14.00 Yan Flüt Dinletisi                - 15.30 Piyano Dinletisi       - 17.30 Bağlama Dinletisi</t>
   </si>
   <si>
+    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t>ÜCRETSİZ OYUN.                      "Cadı Avı"                                  İLETİŞİM: Av.Onur Bey: +90 542 699 09 34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t>Latin Katolik Kilisesi Ayin 
-18.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
-    <t>Atatürk Lisesi tiyatro prova</t>
-  </si>
-  <si>
-    <t>Atatürk Lisesi Oyun Günü</t>
-  </si>
-  <si>
-    <t>Osman Uysal Prova opsiyon</t>
-  </si>
-  <si>
-    <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
-sabahtan 21.00'a kadar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
-  </si>
-  <si>
-    <t>Namık Kemal Okuma Bayramı</t>
-  </si>
-  <si>
-    <t>Doğu Der Toplantı</t>
   </si>
   <si>
     <t>-Çoklu İklim Krizinin Gölgesinde Orman Yangınları
@@ -662,6 +619,64 @@
 -Belediye Meclisi 17.00'dan sonra</t>
   </si>
   <si>
+    <t xml:space="preserve">15 HAZİRAN 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 HAZİRAN 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 HAZİRAN 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 HAZİRAN 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 HAZİRAN 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 HAZİRAN 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 HAZİRAN 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Belediye meclisi 16.00'dan sonra</t>
+  </si>
+  <si>
+    <t>Atatürk Lisesi tiyatro prova</t>
+  </si>
+  <si>
+    <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
+  </si>
+  <si>
+    <t>Atatürk Lisesi Oyun Günü</t>
+  </si>
+  <si>
+    <t>Osman Uysal Prova opsiyon</t>
+  </si>
+  <si>
+    <t>Namık Kemal 2-a sınıfı Okuma Bayramı 
+sabahtan 21.00'a kadar</t>
+  </si>
+  <si>
+    <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
+  </si>
+  <si>
+    <t>-Namık Kemal Prova Okuma Bayramı 12.00'da bitecek                            -Thm Konseri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t>Namık Kemal Okuma Bayramı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
+  </si>
+  <si>
+    <t>Doğu Der Toplantı</t>
+  </si>
+  <si>
     <t xml:space="preserve">22 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -677,44 +692,29 @@
     <t xml:space="preserve">26 HAZİRAN 2026 CUMA </t>
   </si>
   <si>
+    <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">27 HAZİRAN 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t>Belediye meclisi 16.00'dan sonra</t>
-  </si>
-  <si>
     <t xml:space="preserve">28 HAZİRAN 2026 PAZAR </t>
-  </si>
-  <si>
-    <t>Saygın Sanat Arı Maya Müzikali.  2 seans 15.00-21.00</t>
-  </si>
-  <si>
-    <t>Dem Parti Olağan Kurul 5445442823 Ali Güleser 19.00-22.00</t>
   </si>
   <si>
     <t>Reyhan Cici Piyano Dinletisi
 Ödendi. Dilekçe geldi. Tel no:5320631925 12.00-20.00</t>
   </si>
   <si>
-    <t xml:space="preserve">13 TEMMUZ 2026 PAZARTESİ </t>
-  </si>
-  <si>
     <t>MHP 15. Olağan Kongre Toplantısı</t>
   </si>
   <si>
-    <t xml:space="preserve">14 TEMMUZ 2026 SALI </t>
-  </si>
-  <si>
     <t xml:space="preserve">29 HAZİRAN 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
+  </si>
+  <si>
     <t xml:space="preserve">30 HAZİRAN 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 TEMMUZ 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 TEMMUZ 2026 PAZARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">21 TEMMUZ 2026 SALI </t>
@@ -803,131 +803,47 @@
 18.30(farklı odalar)</t>
   </si>
   <si>
+    <t xml:space="preserve">EYLÜL </t>
+  </si>
+  <si>
     <t xml:space="preserve">31 AĞUSTOS 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">EYLÜL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EKİM </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t>3 EKİM 2026 CUMARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 EYLÜL 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t>Yeni Parti Toplantı</t>
   </si>
   <si>
     <t>Tiyatro Kıvılcım Keloğlan Etkinliği ödendi
 Haydar Ali tel no: 5527151935</t>
   </si>
   <si>
-    <t>5 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
-  </si>
-  <si>
     <t xml:space="preserve">7 EYLÜL 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">8 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t>Hafifletici Sebepler opsiyon</t>
-  </si>
-  <si>
-    <t>12 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
+    <t xml:space="preserve">EKİM </t>
   </si>
   <si>
     <t xml:space="preserve">12 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t>KENT KONSEYİ OPSİYON (HER HAFTA ÇARŞAMBA 20.00 - 230.00 ARASI KULLANIM İÇİN DİLEKÇE YAZILACAK)</t>
-  </si>
-  <si>
     <t>Belediye Meclis 15.00 Tüm alan</t>
   </si>
   <si>
-    <t>İZMİR KENT TİYATROSU 05547273157</t>
-  </si>
-  <si>
     <t xml:space="preserve">14 EYLÜL 2026 PAZARTESİ </t>
   </si>
   <si>
-    <t>19 EKİM 2026 PAZARTESİ</t>
-  </si>
-  <si>
     <t xml:space="preserve">15 EYLÜL 2026 SALI </t>
   </si>
   <si>
-    <t xml:space="preserve">20 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
     <t xml:space="preserve">19 EYLÜL 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t xml:space="preserve">23 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 EKİM 2026 CUMARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
+    <t xml:space="preserve">1 EKİM  2026 PERŞEMBE </t>
   </si>
   <si>
     <t xml:space="preserve">09:00-16:00 
@@ -935,7 +851,7 @@
 Müdürlüğü   ( İzmir Yurttaş Meclisi) </t>
   </si>
   <si>
-    <t>KENT KONSEYİ OPSİYON</t>
+    <t xml:space="preserve">2 EKİM 2026 CUMA </t>
   </si>
   <si>
     <t xml:space="preserve">12:30-17:00
@@ -943,28 +859,13 @@
 Müdürlüğü   ( İzmir Yurttaş Meclisi) </t>
   </si>
   <si>
-    <t>KENT ENS. TİYATRO KURSİYER OYUNU "SEVGİLİ DOKTOR" AYSEL GÜZEL</t>
-  </si>
-  <si>
     <t>Çeşme Belediyespor Tekwando velileri toplantı 16.00-17.00</t>
   </si>
   <si>
-    <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 EKİM 2026 SALI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 EKİM 2026 ÇARŞAMBA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 EKİM 2026 PERŞEMBE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 EKİM 2026 CUMA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
+    <t>3 EKİM 2026 CUMARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
   </si>
   <si>
     <t xml:space="preserve">21 EYLÜL 2026 PAZARTESİ </t>
@@ -974,6 +875,9 @@
   </si>
   <si>
     <t xml:space="preserve">26 EYLÜL 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>Yeni Parti Toplantı</t>
   </si>
   <si>
     <t>Osman Uysal Konser Prova 18.00-22.00</t>
@@ -1021,7 +925,103 @@
     <t xml:space="preserve">28 EYLÜL 2026 PAZARTESİ </t>
   </si>
   <si>
+    <t>5 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
     <t xml:space="preserve">29 EYLÜL 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Hafifletici Sebepler opsiyon</t>
+  </si>
+  <si>
+    <t>12 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>KENT KONSEYİ OPSİYON (HER HAFTA ÇARŞAMBA 20.00 - 230.00 ARASI KULLANIM İÇİN DİLEKÇE YAZILACAK)</t>
+  </si>
+  <si>
+    <t>İZMİR KENT TİYATROSU 05547273157</t>
+  </si>
+  <si>
+    <t>19 EKİM 2026 PAZARTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>KENT KONSEYİ OPSİYON</t>
+  </si>
+  <si>
+    <t>KENT ENS. TİYATRO KURSİYER OYUNU "SEVGİLİ DOKTOR" AYSEL GÜZEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 EKİM 2026 SALI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 EKİM 2026 ÇARŞAMBA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 EKİM 2026 PERŞEMBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 EKİM 2026 CUMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
   </si>
   <si>
     <t xml:space="preserve">KASIM </t>
@@ -1238,7 +1238,6 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font/>
     <font>
       <b/>
       <sz val="14.0"/>
@@ -1246,6 +1245,7 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font/>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1306,13 +1306,13 @@
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1446,41 +1446,38 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1488,57 +1485,63 @@
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="4" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1549,19 +1552,16 @@
     <xf borderId="4" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1577,6 +1577,9 @@
     <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1584,9 +1587,6 @@
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1607,41 +1607,41 @@
     <xf borderId="4" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="14" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="4" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1916,41 +1916,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>46023.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="13">
         <v>46024.0</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="11">
+      <c r="F3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="10">
         <v>46026.0</v>
       </c>
     </row>
@@ -1964,25 +1964,25 @@
       <c r="G4" s="9"/>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="13">
         <v>46028.0</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="13">
         <v>46029.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <v>46030.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>46031.0</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="F5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="10">
         <v>46033.0</v>
       </c>
     </row>
@@ -1991,137 +1991,137 @@
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="18.0" customHeight="1">
+      <c r="A7" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="B7" s="13">
         <v>46035.0</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="21">
         <v>46036.0</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="21">
         <v>46037.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>46038.0</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="28">
+      <c r="F7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="23">
         <v>46040.0</v>
       </c>
     </row>
     <row r="8" ht="69.0" customHeight="1">
       <c r="A8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="17" t="s">
+      <c r="B9" s="13">
+        <v>46042.0</v>
+      </c>
+      <c r="C9" s="21">
+        <v>46043.0</v>
+      </c>
+      <c r="D9" s="21">
+        <v>46044.0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>46045.0</v>
+      </c>
+      <c r="F9" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="G9" s="10">
+        <v>46047.0</v>
+      </c>
+    </row>
+    <row r="10" ht="78.75" customHeight="1">
+      <c r="A10" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="31"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="12">
-        <v>46042.0</v>
-      </c>
-      <c r="C9" s="25">
-        <v>46043.0</v>
-      </c>
-      <c r="D9" s="25">
-        <v>46044.0</v>
-      </c>
-      <c r="E9" s="12">
-        <v>46045.0</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="11">
-        <v>46047.0</v>
-      </c>
-    </row>
-    <row r="10" ht="78.75" customHeight="1">
-      <c r="A10" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="27"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="B11" s="13">
         <v>46049.0</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="21">
         <v>46050.0</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="21">
         <v>46051.0</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>46052.0</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>64</v>
+      <c r="F11" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="93.75" customHeight="1">
       <c r="A12" s="17"/>
       <c r="B12" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
+        <v>41</v>
+      </c>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="38"/>
+        <v>43</v>
+      </c>
+      <c r="G12" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2149,196 +2149,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="59" t="s">
-        <v>224</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="A2" s="63" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>229</v>
+      <c r="D3" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="4" ht="84.0" customHeight="1">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="60" t="s">
-        <v>231</v>
-      </c>
-      <c r="G4" s="49" t="s">
-        <v>231</v>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="G4" s="50" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>240</v>
+      <c r="A5" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="63" t="s">
-        <v>242</v>
-      </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="60" t="s">
-        <v>242</v>
-      </c>
-      <c r="G6" s="27"/>
-      <c r="L6" s="65"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="66" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="65" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="31"/>
+      <c r="L6" s="67"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>249</v>
+      <c r="A7" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="67" t="s">
-        <v>251</v>
-      </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="G8" s="27"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="69" t="s">
+        <v>268</v>
+      </c>
+      <c r="G8" s="31"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>263</v>
+      <c r="A9" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="10" ht="100.5" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="60" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="67" t="s">
-        <v>267</v>
-      </c>
-      <c r="G10" s="27"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="65" t="s">
+        <v>276</v>
+      </c>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="68" t="s">
+        <v>277</v>
+      </c>
+      <c r="G10" s="31"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>274</v>
+      <c r="A11" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>283</v>
       </c>
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="60" t="s">
-        <v>265</v>
-      </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="65" t="s">
+        <v>276</v>
+      </c>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
       <c r="G12" s="9"/>
     </row>
   </sheetData>
@@ -2366,25 +2366,25 @@
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="42" t="s">
         <v>284</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="9"/>
@@ -2393,7 +2393,7 @@
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="16" t="s">
         <v>285</v>
       </c>
     </row>
@@ -2404,140 +2404,140 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="27"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
       <c r="G12" s="70" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="16" t="s">
         <v>315</v>
       </c>
       <c r="B13" s="9"/>
@@ -2548,7 +2548,7 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" ht="90.75" customHeight="1">
-      <c r="A14" s="27"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -2583,163 +2583,163 @@
   <sheetData>
     <row r="1" ht="35.25" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="48" t="s">
         <v>316</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="43"/>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
       <c r="A4" s="9"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="16" t="s">
         <v>341</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>344</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="16" t="s">
         <v>346</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="16" t="s">
         <v>347</v>
       </c>
       <c r="E11" s="9"/>
@@ -2747,10 +2747,10 @@
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="90.0" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
@@ -2781,15 +2781,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="63.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -2805,15 +2805,15 @@
       <c r="T1" s="6"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="A2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -2829,13 +2829,13 @@
       <c r="T2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="18">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="19">
         <v>46054.0</v>
       </c>
       <c r="H3" s="6"/>
@@ -2853,12 +2853,12 @@
       <c r="T3" s="6"/>
     </row>
     <row r="4" ht="86.25" customHeight="1">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="20"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="17"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -2875,25 +2875,25 @@
       <c r="T4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="26">
+      <c r="A5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="28">
         <v>46056.0</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="28">
         <v>46057.0</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="28">
         <v>46058.0</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="28">
         <v>46059.0</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="18">
+      <c r="F5" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="19">
         <v>46061.0</v>
       </c>
       <c r="H5" s="6"/>
@@ -2912,17 +2912,17 @@
     </row>
     <row r="6" ht="93.75" customHeight="1">
       <c r="A6" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+        <v>37</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -2939,25 +2939,25 @@
       <c r="T6" s="6"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="26">
+      <c r="A7" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="28">
         <v>46063.0</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="28">
         <v>46064.0</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="28">
         <v>46065.0</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="28">
         <v>46066.0</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="18">
+      <c r="F7" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="19">
         <v>46068.0</v>
       </c>
       <c r="H7" s="6"/>
@@ -2975,7 +2975,7 @@
       <c r="T7" s="6"/>
     </row>
     <row r="8" ht="105.75" customHeight="1">
-      <c r="A8" s="16"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="17" t="s">
         <v>50</v>
       </c>
@@ -2983,14 +2983,14 @@
         <v>52</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="35" t="s">
         <v>57</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="36" t="s">
+        <v>60</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -3007,25 +3007,25 @@
       <c r="T8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="26">
+      <c r="A9" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="28">
         <v>46070.0</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="28">
         <v>46071.0</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="28">
         <v>46072.0</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="28">
         <v>46073.0</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="18">
+      <c r="F9" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="19">
         <v>46075.0</v>
       </c>
       <c r="H9" s="6"/>
@@ -3044,11 +3044,11 @@
     </row>
     <row r="10" ht="89.25" customHeight="1">
       <c r="A10" s="17"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
       <c r="E10" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>70</v>
@@ -3071,25 +3071,25 @@
       <c r="T10" s="6"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="28">
         <v>46077.0</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="28">
         <v>46078.0</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="28">
         <v>46079.0</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="28">
         <v>46080.0</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="16"/>
+      <c r="G11" s="15"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
@@ -3105,15 +3105,15 @@
       <c r="T11" s="6"/>
     </row>
     <row r="12" ht="98.25" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
       <c r="D12" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
@@ -24426,26 +24426,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="A2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
       <c r="A3" s="9"/>
@@ -24454,7 +24454,7 @@
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <v>46082.0</v>
       </c>
     </row>
@@ -24466,107 +24466,107 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="17" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="13">
         <v>46084.0</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="13">
         <v>46085.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <v>46086.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>46087.0</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="F5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="10">
         <v>46089.0</v>
       </c>
     </row>
     <row r="6" ht="113.25" customHeight="1">
       <c r="A6" s="9"/>
-      <c r="B6" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="27"/>
+      <c r="B6" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="31"/>
       <c r="D6" s="17" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F6" s="17"/>
-      <c r="G6" s="31"/>
+      <c r="G6" s="33"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="13">
         <v>46091.0</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="13">
         <v>46092.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <v>46093.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>46094.0</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="11">
+      <c r="F7" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="10">
         <v>46096.0</v>
       </c>
     </row>
     <row r="8" ht="87.0" customHeight="1">
       <c r="A8" s="9"/>
-      <c r="B8" s="27" t="s">
-        <v>21</v>
+      <c r="B8" s="31" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="17" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="13">
         <v>46098.0</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>46099.0</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="21">
         <v>46100.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>46101.0</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="F9" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="10">
         <v>46103.0</v>
       </c>
     </row>
@@ -24574,33 +24574,33 @@
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
-      <c r="D10" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
+      <c r="D10" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="13">
         <v>46105.0</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <v>46106.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <v>46107.0</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>46108.0</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <v>46110.0</v>
       </c>
     </row>
@@ -24622,10 +24622,10 @@
       <c r="G12" s="40"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="13">
         <v>46112.0</v>
       </c>
       <c r="C13" s="9"/>
@@ -24670,43 +24670,43 @@
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="12">
+      <c r="C3" s="13">
         <v>46113.0</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="13">
         <v>46114.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="13">
         <v>46115.0</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="11">
+      <c r="F3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="10">
         <v>46117.0</v>
       </c>
     </row>
@@ -24720,25 +24720,25 @@
       <c r="G4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="13">
         <v>46119.0</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="13">
         <v>46120.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <v>46121.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>46122.0</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="F5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="10">
         <v>46124.0</v>
       </c>
     </row>
@@ -24746,75 +24746,75 @@
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
-      <c r="D6" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>20</v>
+      <c r="D6" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>19</v>
       </c>
       <c r="F6" s="17"/>
-      <c r="G6" s="22" t="s">
-        <v>22</v>
+      <c r="G6" s="24" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="13">
         <v>46126.0</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="21">
         <v>46127.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <v>46128.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>46129.0</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="11">
+      <c r="F7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="10">
         <v>46131.0</v>
       </c>
     </row>
     <row r="8" ht="80.25" customHeight="1">
-      <c r="A8" s="30"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="32"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="22" t="s">
+      <c r="D8" s="35" t="s">
         <v>44</v>
       </c>
+      <c r="E8" s="24" t="s">
+        <v>48</v>
+      </c>
       <c r="F8" s="17"/>
-      <c r="G8" s="22" t="s">
-        <v>46</v>
+      <c r="G8" s="24" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="13">
         <v>46133.0</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="13">
         <v>46134.0</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>46135.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>46136.0</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="F9" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="10">
         <v>46138.0</v>
       </c>
     </row>
@@ -24822,24 +24822,24 @@
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="22" t="s">
-        <v>59</v>
+      <c r="D10" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="13">
         <v>46140.0</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <v>46141.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <v>46142.0</v>
       </c>
       <c r="E11" s="9"/>
@@ -24850,8 +24850,8 @@
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
-      <c r="D12" s="37" t="s">
-        <v>67</v>
+      <c r="D12" s="38" t="s">
+        <v>69</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
@@ -24887,38 +24887,38 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>85</v>
       </c>
     </row>
@@ -24931,37 +24931,37 @@
         <v>86</v>
       </c>
       <c r="F4" s="45"/>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="24" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D6" s="9"/>
@@ -24969,144 +24969,144 @@
         <v>96</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G6" s="45"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="19" t="s">
+      <c r="A7" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="B7" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="C7" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="D7" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>104</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8" ht="97.5" customHeight="1">
       <c r="A8" s="17"/>
-      <c r="B8" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="22" t="s">
+      <c r="B8" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="C8" s="50" t="s">
         <v>108</v>
       </c>
+      <c r="D8" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>112</v>
+      </c>
       <c r="F8" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>110</v>
+        <v>114</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>117</v>
+      <c r="A9" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="22" t="s">
-        <v>118</v>
+      <c r="A10" s="24" t="s">
+        <v>128</v>
       </c>
       <c r="B10" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="G10" s="50" t="s">
-        <v>122</v>
+      <c r="C10" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>129</v>
+      <c r="A11" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="12" ht="109.5" customHeight="1">
-      <c r="A12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="F12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="G12" s="50" t="s">
-        <v>122</v>
+      <c r="A12" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -25136,204 +25136,204 @@
   <sheetData>
     <row r="1" ht="58.5" customHeight="1">
       <c r="A1" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" ht="30.0" customHeight="1">
+      <c r="A2" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" ht="91.5" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="C4" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D4" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" s="15" t="s">
+      <c r="E4" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="38" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="4" ht="91.5" customHeight="1">
-      <c r="A4" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="17" t="s">
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="37" t="s">
+      <c r="B5" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>151</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="6" ht="183.75" customHeight="1">
       <c r="A6" s="53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E6" s="24" t="s">
         <v>156</v>
       </c>
+      <c r="E6" s="25" t="s">
+        <v>157</v>
+      </c>
       <c r="F6" s="54" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>158</v>
+        <v>160</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="E7" s="19" t="s">
+      <c r="A7" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>166</v>
       </c>
+      <c r="D7" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="8" ht="101.25" customHeight="1">
-      <c r="A8" s="49" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="D8" s="22" t="s">
+      <c r="A8" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="B8" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="C8" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>176</v>
       </c>
+      <c r="E8" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="F9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="B9" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>185</v>
       </c>
+      <c r="D9" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="10" ht="99.75" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>190</v>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>193</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>195</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -25342,13 +25342,13 @@
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="107.25" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25377,161 +25377,161 @@
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="A2" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="12">
+      <c r="C3" s="13">
         <v>46204.0</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="13">
         <v>46205.0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="13">
         <v>46206.0</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="11">
+      <c r="F3" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="G3" s="10">
         <v>46208.0</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="49" t="s">
-        <v>160</v>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="50" t="s">
+        <v>154</v>
       </c>
       <c r="G4" s="17"/>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" s="12">
+      <c r="A5" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="13">
         <v>46211.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <v>46212.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>46213.0</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="F5" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5" s="10">
         <v>46215.0</v>
       </c>
     </row>
     <row r="6" ht="92.25" customHeight="1">
       <c r="A6" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="G6" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>187</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="25">
+      <c r="A7" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="21">
         <v>46218.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <v>46219.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>46220.0</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>194</v>
+      <c r="F7" s="14" t="s">
+        <v>188</v>
       </c>
       <c r="G7" s="56">
         <v>46222.0</v>
       </c>
     </row>
     <row r="8" ht="88.5" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="G8" s="27"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="G8" s="31"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="13">
         <v>46225.0</v>
       </c>
       <c r="D9" s="57">
         <v>46226.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>46227.0</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <v>46229.0</v>
       </c>
     </row>
     <row r="10" ht="77.25" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="47" t="s">
         <v>198</v>
       </c>
@@ -25540,30 +25540,30 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <v>46232.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <v>46233.0</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="16" t="s">
         <v>202</v>
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="90.75" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="35"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="36"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
     </row>
@@ -25594,25 +25594,25 @@
   <sheetData>
     <row r="1" ht="34.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.75" customHeight="1">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="9"/>
@@ -25620,10 +25620,10 @@
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <v>46236.0</v>
       </c>
     </row>
@@ -25633,162 +25633,162 @@
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
-      <c r="F4" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="G4" s="27"/>
+      <c r="F4" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="G4" s="31"/>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="13">
         <v>46239.0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <v>46240.0</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>46241.0</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>46243.0</v>
       </c>
     </row>
     <row r="6" ht="84.0" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="22" t="s">
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="13">
         <v>46246.0</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <v>46247.0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>46248.0</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <v>46250.0</v>
       </c>
     </row>
     <row r="8" ht="93.75" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="G8" s="27"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="G8" s="31"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="13">
         <v>46253.0</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="13">
         <v>46254.0</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>46255.0</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <v>46257.0</v>
       </c>
     </row>
     <row r="10" ht="93.75" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="49" t="s">
+      <c r="A10" s="31"/>
+      <c r="B10" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="49" t="s">
+      <c r="C10" s="34"/>
+      <c r="D10" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="G10" s="22" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="G10" s="24" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <v>46260.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <v>46261.0</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>46262.0</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <v>46264.0</v>
       </c>
     </row>
     <row r="12" ht="94.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="49" t="s">
+      <c r="A12" s="31"/>
+      <c r="B12" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="22" t="s">
+      <c r="C12" s="31"/>
+      <c r="D12" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="E12" s="49" t="s">
+      <c r="E12" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="31"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="s">
-        <v>222</v>
+      <c r="A13" s="16" t="s">
+        <v>223</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -25798,7 +25798,7 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" ht="91.5" customHeight="1">
-      <c r="A14" s="27"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -25833,178 +25833,178 @@
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="A2" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="9"/>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="13">
+        <v>46267.0</v>
+      </c>
+      <c r="D3" s="13">
+        <v>46268.0</v>
+      </c>
+      <c r="E3" s="13">
+        <v>46269.0</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="C3" s="12">
-        <v>46267.0</v>
-      </c>
-      <c r="D3" s="12">
-        <v>46268.0</v>
-      </c>
-      <c r="E3" s="12">
-        <v>46269.0</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <v>46271.0</v>
       </c>
     </row>
     <row r="4" ht="85.5" customHeight="1">
       <c r="A4" s="9"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="61" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="61">
+        <v>46274.0</v>
+      </c>
+      <c r="D5" s="62">
+        <v>46275.0</v>
+      </c>
+      <c r="E5" s="13">
+        <v>46276.0</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="G5" s="10">
+        <v>46278.0</v>
+      </c>
+    </row>
+    <row r="6" ht="95.25" customHeight="1">
+      <c r="A6" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="s">
+      <c r="B7" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="61">
+        <v>46281.0</v>
+      </c>
+      <c r="D7" s="13">
+        <v>46282.0</v>
+      </c>
+      <c r="E7" s="13">
+        <v>46283.0</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="G7" s="10">
+        <v>46285.0</v>
+      </c>
+    </row>
+    <row r="8" ht="94.5" customHeight="1">
+      <c r="A8" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B5" s="62" t="s">
-        <v>241</v>
-      </c>
-      <c r="C5" s="64">
-        <v>46274.0</v>
-      </c>
-      <c r="D5" s="66">
-        <v>46275.0</v>
-      </c>
-      <c r="E5" s="12">
-        <v>46276.0</v>
-      </c>
-      <c r="F5" s="15" t="s">
+      <c r="C8" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="13">
+        <v>46288.0</v>
+      </c>
+      <c r="D9" s="13">
+        <v>46289.0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>46290.0</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" s="10">
+        <v>46292.0</v>
+      </c>
+    </row>
+    <row r="10" ht="98.25" customHeight="1">
+      <c r="A10" s="64" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="64" t="s">
+        <v>247</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="G5" s="11">
-        <v>46278.0</v>
-      </c>
-    </row>
-    <row r="6" ht="95.25" customHeight="1">
-      <c r="A6" s="22" t="s">
+      <c r="B11" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" s="64">
-        <v>46281.0</v>
-      </c>
-      <c r="D7" s="12">
-        <v>46282.0</v>
-      </c>
-      <c r="E7" s="12">
-        <v>46283.0</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="G7" s="11">
-        <v>46285.0</v>
-      </c>
-    </row>
-    <row r="8" ht="94.5" customHeight="1">
-      <c r="A8" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>266</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="C9" s="12">
-        <v>46288.0</v>
-      </c>
-      <c r="D9" s="12">
-        <v>46289.0</v>
-      </c>
-      <c r="E9" s="12">
-        <v>46290.0</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="G9" s="11">
-        <v>46292.0</v>
-      </c>
-    </row>
-    <row r="10" ht="98.25" customHeight="1">
-      <c r="A10" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="69" t="s">
-        <v>279</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <v>46295.0</v>
       </c>
       <c r="D11" s="9"/>
@@ -26013,9 +26013,9 @@
       <c r="G11" s="9"/>
     </row>
     <row r="12" ht="108.0" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -973,7 +973,7 @@
     <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
   </si>
   <si>
-    <t>KENT KONSEYİ OPSİYON (HER HAFTA ÇARŞAMBA 20.00 - 230.00 ARASI KULLANIM İÇİN DİLEKÇE YAZILACAK)</t>
+    <t>KENT KONSEYİ OPSİYON (HER HAFTA ÇARŞAMBA 20.00 - 23.00 ARASI KULLANIM İÇİN DİLEKÇE YAZILACAK)</t>
   </si>
   <si>
     <t>İZMİR KENT TİYATROSU 05547273157</t>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="350">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -927,6 +927,9 @@
     <t xml:space="preserve">4 EKİM 2026 PAZAR </t>
   </si>
   <si>
+    <t>Yeni Parti Toplantı Hazırlığı</t>
+  </si>
+  <si>
     <t>Yeni Parti Toplantı</t>
   </si>
   <si>
@@ -978,6 +981,10 @@
     <t>Hafifletici Sebepler İlknur Çatal 05547273157</t>
   </si>
   <si>
+    <t>opsiyon Dedim İyi Fikir 
+Tel No:5334080373</t>
+  </si>
+  <si>
     <t>19 EKİM 2026 PAZARTESİ</t>
   </si>
   <si>
@@ -1021,6 +1028,10 @@
   </si>
   <si>
     <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>Gülay Canikli opsiyon 
+Tel no: 5056884720</t>
   </si>
   <si>
     <t xml:space="preserve">KASIM </t>
@@ -1662,7 +1673,7 @@
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="11" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2267,7 +2278,7 @@
         <v>251</v>
       </c>
       <c r="G4" s="70" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H4" s="64"/>
       <c r="I4" s="64"/>
@@ -2287,25 +2298,25 @@
     </row>
     <row r="5">
       <c r="A5" s="67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B5" s="67" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" s="67" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D5" s="67" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F5" s="68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G5" s="68" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H5" s="64"/>
       <c r="I5" s="64"/>
@@ -2349,25 +2360,25 @@
     </row>
     <row r="7">
       <c r="A7" s="67" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C7" s="67" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E7" s="67" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F7" s="68" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G7" s="68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H7" s="64"/>
       <c r="I7" s="64"/>
@@ -2389,14 +2400,16 @@
       <c r="A8" s="69"/>
       <c r="B8" s="69"/>
       <c r="C8" s="72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D8" s="69"/>
       <c r="E8" s="69"/>
       <c r="F8" s="73" t="s">
-        <v>267</v>
-      </c>
-      <c r="G8" s="69"/>
+        <v>268</v>
+      </c>
+      <c r="G8" s="74" t="s">
+        <v>269</v>
+      </c>
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
       <c r="J8" s="64"/>
@@ -2415,25 +2428,25 @@
     </row>
     <row r="9">
       <c r="A9" s="67" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E9" s="67" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F9" s="68" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
@@ -2455,12 +2468,16 @@
       <c r="A10" s="69"/>
       <c r="B10" s="69"/>
       <c r="C10" s="74" t="s">
-        <v>275</v>
-      </c>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
+        <v>277</v>
+      </c>
+      <c r="D10" s="74" t="s">
+        <v>269</v>
+      </c>
+      <c r="E10" s="74" t="s">
+        <v>269</v>
+      </c>
       <c r="F10" s="72" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G10" s="69"/>
       <c r="H10" s="64"/>
@@ -2481,22 +2498,22 @@
     </row>
     <row r="11">
       <c r="A11" s="67" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E11" s="67" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F11" s="68" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G11" s="66"/>
       <c r="H11" s="64"/>
@@ -2519,11 +2536,13 @@
       <c r="A12" s="69"/>
       <c r="B12" s="69"/>
       <c r="C12" s="74" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D12" s="69"/>
       <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
+      <c r="F12" s="74" t="s">
+        <v>285</v>
+      </c>
       <c r="G12" s="66"/>
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
@@ -25881,7 +25900,7 @@
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="42" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -25898,7 +25917,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="9" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
@@ -25912,25 +25931,25 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
@@ -25944,25 +25963,25 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
@@ -25976,25 +25995,25 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
@@ -26008,25 +26027,25 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
@@ -26037,12 +26056,12 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="75" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -26098,7 +26117,7 @@
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -26110,22 +26129,22 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
@@ -26139,25 +26158,25 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
@@ -26171,25 +26190,25 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
@@ -26203,25 +26222,25 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
@@ -26235,16 +26254,16 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="350">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -954,6 +954,9 @@
     <t xml:space="preserve">11 EKİM 2026 PAZAR </t>
   </si>
   <si>
+    <t>Kent Ens.Tiyatro Kursu Saat 14:00-22:00</t>
+  </si>
+  <si>
     <t>12 EKİM 2026 PAZARTESİ</t>
   </si>
   <si>
@@ -975,10 +978,11 @@
     <t xml:space="preserve">18 EKİM 2026 PAZAR </t>
   </si>
   <si>
-    <t>KENT KONSEYİ OPSİYON (HER HAFTA ÇARŞAMBA 20.00 - 23.00 ARASI KULLANIM İÇİN DİLEKÇE YAZILACAK)</t>
+    <t>Kent Konseyi (Her Çarşamba 20.00 - 23.00)</t>
   </si>
   <si>
-    <t>Hafifletici Sebepler İlknur Çatal 05547273157</t>
+    <t>Hafifletici Sebepler İlknur Çatal 05547273157
+Ödeme Gelecek.</t>
   </si>
   <si>
     <t>opsiyon Dedim İyi Fikir 
@@ -1006,10 +1010,7 @@
     <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
   </si>
   <si>
-    <t>KENT KONSEYİ OPSİYON</t>
-  </si>
-  <si>
-    <t>KENT ENS. TİYATRO KURSİYER OYUNU "SEVGİLİ DOKTOR" AYSEL GÜZEL</t>
+    <t>Kent Ens. Tiyatro Kursiyer Oyunu "Sevgili Doktor" Aysel Güzel</t>
   </si>
   <si>
     <t xml:space="preserve">26 EKİM 2026 PAZARTESİ </t>
@@ -1467,7 +1468,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1667,13 +1668,16 @@
     <xf borderId="4" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="4" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="8" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="11" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2338,15 +2342,17 @@
       <c r="A6" s="69"/>
       <c r="B6" s="69"/>
       <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
+      <c r="D6" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
+      <c r="F6" s="72"/>
       <c r="G6" s="69"/>
       <c r="H6" s="64"/>
       <c r="I6" s="64"/>
       <c r="J6" s="64"/>
       <c r="K6" s="64"/>
-      <c r="L6" s="71"/>
+      <c r="L6" s="73"/>
       <c r="M6" s="64"/>
       <c r="N6" s="64"/>
       <c r="O6" s="64"/>
@@ -2360,25 +2366,25 @@
     </row>
     <row r="7">
       <c r="A7" s="67" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C7" s="67" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E7" s="67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F7" s="68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G7" s="68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H7" s="64"/>
       <c r="I7" s="64"/>
@@ -2399,16 +2405,18 @@
     <row r="8" ht="97.5" customHeight="1">
       <c r="A8" s="69"/>
       <c r="B8" s="69"/>
-      <c r="C8" s="72" t="s">
-        <v>267</v>
-      </c>
-      <c r="D8" s="69"/>
+      <c r="C8" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E8" s="69"/>
-      <c r="F8" s="73" t="s">
-        <v>268</v>
-      </c>
-      <c r="G8" s="74" t="s">
+      <c r="F8" s="74" t="s">
         <v>269</v>
+      </c>
+      <c r="G8" s="75" t="s">
+        <v>270</v>
       </c>
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
@@ -2428,25 +2436,25 @@
     </row>
     <row r="9">
       <c r="A9" s="67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E9" s="67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F9" s="68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
@@ -2467,16 +2475,16 @@
     <row r="10" ht="100.5" customHeight="1">
       <c r="A10" s="69"/>
       <c r="B10" s="69"/>
-      <c r="C10" s="74" t="s">
-        <v>277</v>
-      </c>
-      <c r="D10" s="74" t="s">
-        <v>269</v>
-      </c>
-      <c r="E10" s="74" t="s">
-        <v>269</v>
-      </c>
-      <c r="F10" s="72" t="s">
+      <c r="C10" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="75" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10" s="71" t="s">
         <v>278</v>
       </c>
       <c r="G10" s="69"/>
@@ -2535,12 +2543,14 @@
     <row r="12" ht="94.5" customHeight="1">
       <c r="A12" s="69"/>
       <c r="B12" s="69"/>
-      <c r="C12" s="74" t="s">
-        <v>277</v>
-      </c>
-      <c r="D12" s="69"/>
+      <c r="C12" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E12" s="69"/>
-      <c r="F12" s="74" t="s">
+      <c r="F12" s="75" t="s">
         <v>285</v>
       </c>
       <c r="G12" s="66"/>
@@ -25955,8 +25965,12 @@
     <row r="6" ht="98.25" customHeight="1">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
+      <c r="C6" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
@@ -25987,8 +26001,12 @@
     <row r="8" ht="98.25" customHeight="1">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
+      <c r="C8" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -26019,8 +26037,12 @@
     <row r="10" ht="107.25" customHeight="1">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
+      <c r="C10" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -26051,11 +26073,15 @@
     <row r="12" ht="103.5" customHeight="1">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
+      <c r="C12" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
-      <c r="G12" s="75" t="s">
+      <c r="G12" s="76" t="s">
         <v>316</v>
       </c>
     </row>
@@ -26150,8 +26176,12 @@
     <row r="4" ht="91.5" customHeight="1">
       <c r="A4" s="5"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
+      <c r="C4" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
@@ -26182,8 +26212,12 @@
     <row r="6" ht="99.0" customHeight="1">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
+      <c r="C6" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
@@ -26214,8 +26248,12 @@
     <row r="8" ht="96.0" customHeight="1">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
+      <c r="C8" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -26246,8 +26284,12 @@
     <row r="10" ht="96.75" customHeight="1">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
+      <c r="C10" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -26272,8 +26314,12 @@
     <row r="12" ht="90.0" customHeight="1">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
+      <c r="C12" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="71" t="s">
+        <v>260</v>
+      </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="350">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -985,10 +985,6 @@
 Ödeme Gelecek.</t>
   </si>
   <si>
-    <t>opsiyon Dedim İyi Fikir 
-Tel No:5334080373</t>
-  </si>
-  <si>
     <t>19 EKİM 2026 PAZARTESİ</t>
   </si>
   <si>
@@ -1008,6 +1004,10 @@
   </si>
   <si>
     <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>opsiyon Dedim İyi Fikir 
+Tel No:5334080373</t>
   </si>
   <si>
     <t>Kent Ens. Tiyatro Kursiyer Oyunu "Sevgili Doktor" Aysel Güzel</t>
@@ -2415,9 +2415,7 @@
       <c r="F8" s="74" t="s">
         <v>269</v>
       </c>
-      <c r="G8" s="75" t="s">
-        <v>270</v>
-      </c>
+      <c r="G8" s="69"/>
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
       <c r="J8" s="64"/>
@@ -2436,25 +2434,25 @@
     </row>
     <row r="9">
       <c r="A9" s="67" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="67" t="s">
         <v>271</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="C9" s="67" t="s">
         <v>272</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="D9" s="67" t="s">
         <v>273</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="E9" s="67" t="s">
         <v>274</v>
       </c>
-      <c r="E9" s="67" t="s">
+      <c r="F9" s="68" t="s">
         <v>275</v>
       </c>
-      <c r="F9" s="68" t="s">
+      <c r="G9" s="68" t="s">
         <v>276</v>
-      </c>
-      <c r="G9" s="68" t="s">
-        <v>277</v>
       </c>
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
@@ -2482,7 +2480,7 @@
         <v>260</v>
       </c>
       <c r="E10" s="75" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F10" s="71" t="s">
         <v>278</v>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="353">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -1062,6 +1062,10 @@
     <t xml:space="preserve">8 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t>Yaşar Eğitim Kültür Vakfı
+12.00-16.00 Prova</t>
+  </si>
+  <si>
     <t>9 KASIM 2026 PAZARTESİ</t>
   </si>
   <si>
@@ -1081,6 +1085,14 @@
   </si>
   <si>
     <t xml:space="preserve">15 KASIM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Yaşar Eğitim Kültür Vakfı
+08.30-16.00 Prova</t>
+  </si>
+  <si>
+    <t>Yaşar Eğitim Kültür Vakfı
+10 Kasım Anma Günü Programı</t>
   </si>
   <si>
     <t xml:space="preserve">16 KASIM 2026 PAZARTESİ </t>
@@ -25888,8 +25900,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.88"/>
-    <col customWidth="1" min="2" max="2" width="23.38"/>
+    <col customWidth="1" min="1" max="1" width="23.5"/>
+    <col customWidth="1" min="2" max="2" width="24.25"/>
     <col customWidth="1" min="3" max="4" width="22.75"/>
     <col customWidth="1" min="5" max="6" width="23.0"/>
     <col customWidth="1" min="7" max="7" width="24.75"/>
@@ -25961,44 +25973,54 @@
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
+      <c r="A6" s="49" t="s">
+        <v>295</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>295</v>
+      </c>
       <c r="C6" s="71" t="s">
         <v>268</v>
       </c>
       <c r="D6" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="E6" s="15"/>
+      <c r="E6" s="49" t="s">
+        <v>295</v>
+      </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
+      <c r="A8" s="49" t="s">
+        <v>303</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>304</v>
+      </c>
       <c r="C8" s="71" t="s">
         <v>268</v>
       </c>
@@ -26011,25 +26033,25 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
@@ -26047,25 +26069,25 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
@@ -26080,12 +26102,12 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="76" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -26141,7 +26163,7 @@
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -26153,22 +26175,22 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
@@ -26186,25 +26208,25 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
@@ -26222,25 +26244,25 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
@@ -26258,25 +26280,25 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
@@ -26294,16 +26316,16 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="354">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -985,6 +985,9 @@
 Ödeme Gelecek.</t>
   </si>
   <si>
+    <t>Yeni Parti İl Kongresi</t>
+  </si>
+  <si>
     <t>19 EKİM 2026 PAZARTESİ</t>
   </si>
   <si>
@@ -1031,7 +1034,8 @@
     <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
   </si>
   <si>
-    <t>Gülay Canikli opsiyon 
+    <t>Gülay Canikli Çeşme Eğitim-Sen
+Gölgesinde Çınarın Oyunu
 Tel no: 5056884720</t>
   </si>
   <si>
@@ -2427,7 +2431,9 @@
       <c r="F8" s="74" t="s">
         <v>269</v>
       </c>
-      <c r="G8" s="69"/>
+      <c r="G8" s="70" t="s">
+        <v>270</v>
+      </c>
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
       <c r="J8" s="64"/>
@@ -2446,25 +2452,25 @@
     </row>
     <row r="9">
       <c r="A9" s="67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E9" s="67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F9" s="68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
@@ -2492,10 +2498,10 @@
         <v>260</v>
       </c>
       <c r="E10" s="75" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F10" s="71" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G10" s="69"/>
       <c r="H10" s="64"/>
@@ -2516,22 +2522,22 @@
     </row>
     <row r="11">
       <c r="A11" s="67" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E11" s="67" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F11" s="68" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G11" s="66"/>
       <c r="H11" s="64"/>
@@ -2560,8 +2566,8 @@
         <v>260</v>
       </c>
       <c r="E12" s="69"/>
-      <c r="F12" s="75" t="s">
-        <v>285</v>
+      <c r="F12" s="70" t="s">
+        <v>286</v>
       </c>
       <c r="G12" s="66"/>
       <c r="H12" s="64"/>
@@ -25920,7 +25926,7 @@
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="42" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -25937,7 +25943,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
@@ -25951,33 +25957,33 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
       <c r="A6" s="49" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C6" s="71" t="s">
         <v>268</v>
@@ -25986,40 +25992,40 @@
         <v>260</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
       <c r="A8" s="49" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C8" s="71" t="s">
         <v>268</v>
@@ -26033,25 +26039,25 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
@@ -26069,25 +26075,25 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
@@ -26102,12 +26108,12 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="76" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -26163,7 +26169,7 @@
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -26175,22 +26181,22 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
@@ -26208,25 +26214,25 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
@@ -26244,25 +26250,25 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
@@ -26280,25 +26286,25 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
@@ -26316,16 +26322,16 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="354">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -981,10 +981,6 @@
     <t>Kent Konseyi (Her Çarşamba 20.00 - 23.00)</t>
   </si>
   <si>
-    <t>Hafifletici Sebepler İlknur Çatal 05547273157
-Ödeme Gelecek.</t>
-  </si>
-  <si>
     <t>Yeni Parti İl Kongresi</t>
   </si>
   <si>
@@ -1009,8 +1005,9 @@
     <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
   </si>
   <si>
-    <t>opsiyon Dedim İyi Fikir 
-Tel No:5334080373</t>
+    <t xml:space="preserve"> Dedim İyi Fikir Oyunu
+Tel No:5334080373
+Halil Soner Özaytekin ödendi</t>
   </si>
   <si>
     <t>Kent Ens. Tiyatro Kursiyer Oyunu "Sevgili Doktor" Aysel Güzel</t>
@@ -1032,6 +1029,9 @@
   </si>
   <si>
     <t xml:space="preserve">31 EKİM 2026 CUMARTESİ </t>
+  </si>
+  <si>
+    <t>CUMHURİYET BAYRAMI RESMİ TATİL</t>
   </si>
   <si>
     <t>Gülay Canikli Çeşme Eğitim-Sen
@@ -1366,7 +1366,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1425,6 +1425,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00FF00"/>
         <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
     <fill>
@@ -1693,13 +1699,13 @@
     <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="11" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="11" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="12" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2428,11 +2434,9 @@
         <v>260</v>
       </c>
       <c r="E8" s="69"/>
-      <c r="F8" s="74" t="s">
+      <c r="F8" s="74"/>
+      <c r="G8" s="70" t="s">
         <v>269</v>
-      </c>
-      <c r="G8" s="70" t="s">
-        <v>270</v>
       </c>
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
@@ -2452,25 +2456,25 @@
     </row>
     <row r="9">
       <c r="A9" s="67" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="67" t="s">
         <v>271</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="C9" s="67" t="s">
         <v>272</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="D9" s="67" t="s">
         <v>273</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="E9" s="67" t="s">
         <v>274</v>
       </c>
-      <c r="E9" s="67" t="s">
+      <c r="F9" s="68" t="s">
         <v>275</v>
       </c>
-      <c r="F9" s="68" t="s">
+      <c r="G9" s="68" t="s">
         <v>276</v>
-      </c>
-      <c r="G9" s="68" t="s">
-        <v>277</v>
       </c>
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
@@ -2497,11 +2501,11 @@
       <c r="D10" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="E10" s="75" t="s">
+      <c r="E10" s="71" t="s">
+        <v>277</v>
+      </c>
+      <c r="F10" s="71" t="s">
         <v>278</v>
-      </c>
-      <c r="F10" s="71" t="s">
-        <v>279</v>
       </c>
       <c r="G10" s="69"/>
       <c r="H10" s="64"/>
@@ -2522,22 +2526,22 @@
     </row>
     <row r="11">
       <c r="A11" s="67" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" s="67" t="s">
         <v>280</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="C11" s="67" t="s">
         <v>281</v>
       </c>
-      <c r="C11" s="67" t="s">
+      <c r="D11" s="67" t="s">
         <v>282</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="E11" s="67" t="s">
         <v>283</v>
       </c>
-      <c r="E11" s="67" t="s">
+      <c r="F11" s="68" t="s">
         <v>284</v>
-      </c>
-      <c r="F11" s="68" t="s">
-        <v>285</v>
       </c>
       <c r="G11" s="66"/>
       <c r="H11" s="64"/>
@@ -2562,8 +2566,8 @@
       <c r="C12" s="71" t="s">
         <v>268</v>
       </c>
-      <c r="D12" s="71" t="s">
-        <v>260</v>
+      <c r="D12" s="75" t="s">
+        <v>285</v>
       </c>
       <c r="E12" s="69"/>
       <c r="F12" s="70" t="s">

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="355">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -981,6 +981,9 @@
     <t>Kent Konseyi (Her Çarşamba 20.00 - 23.00)</t>
   </si>
   <si>
+    <t>YENİ PARTİ KONGRE HAZIRLIK 17:00-20:00</t>
+  </si>
+  <si>
     <t>Yeni Parti İl Kongresi</t>
   </si>
   <si>
@@ -1699,7 +1702,7 @@
     <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2434,9 +2437,11 @@
         <v>260</v>
       </c>
       <c r="E8" s="69"/>
-      <c r="F8" s="74"/>
+      <c r="F8" s="74" t="s">
+        <v>269</v>
+      </c>
       <c r="G8" s="70" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
@@ -2456,25 +2461,25 @@
     </row>
     <row r="9">
       <c r="A9" s="67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E9" s="67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F9" s="68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
@@ -2502,10 +2507,10 @@
         <v>260</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F10" s="71" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G10" s="69"/>
       <c r="H10" s="64"/>
@@ -2526,22 +2531,22 @@
     </row>
     <row r="11">
       <c r="A11" s="67" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E11" s="67" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F11" s="68" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G11" s="66"/>
       <c r="H11" s="64"/>
@@ -2567,11 +2572,11 @@
         <v>268</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E12" s="69"/>
       <c r="F12" s="70" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G12" s="66"/>
       <c r="H12" s="64"/>
@@ -25930,7 +25935,7 @@
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="42" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -25947,7 +25952,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
@@ -25961,33 +25966,33 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
       <c r="A6" s="49" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C6" s="71" t="s">
         <v>268</v>
@@ -25996,40 +26001,40 @@
         <v>260</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
       <c r="A8" s="49" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C8" s="71" t="s">
         <v>268</v>
@@ -26043,25 +26048,25 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
@@ -26079,25 +26084,25 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
@@ -26112,12 +26117,12 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="76" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -26173,7 +26178,7 @@
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -26185,22 +26190,22 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
@@ -26218,25 +26223,25 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
@@ -26254,25 +26259,25 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
@@ -26290,25 +26295,25 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
@@ -26326,16 +26331,16 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="358">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -1010,7 +1010,7 @@
   <si>
     <t xml:space="preserve"> Dedim İyi Fikir Oyunu
 Tel No:5334080373
-Halil Soner Özaytekin ödendi</t>
+Halil Soner Özaytekin ödendi                                        Dans Salonunda pilates 9:00-10:30 arası</t>
   </si>
   <si>
     <t>Kent Ens. Tiyatro Kursiyer Oyunu "Sevgili Doktor" Aysel Güzel</t>
@@ -1035,6 +1035,9 @@
   </si>
   <si>
     <t>CUMHURİYET BAYRAMI RESMİ TATİL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dans Salonunda pilates 9:00-10:30 arası</t>
   </si>
   <si>
     <t>Gülay Canikli Çeşme Eğitim-Sen
@@ -1071,6 +1074,15 @@
   <si>
     <t>Yaşar Eğitim Kültür Vakfı
 12.00-16.00 Prova</t>
+  </si>
+  <si>
+    <t>Yaşar Eğitim Kültür Vakfı
+12.00-16.00 Prova                                        Dans Salonunda pilates 9:00-10:30 arası</t>
+  </si>
+  <si>
+    <t>Rüya Takımı 
+Gülümsten Hatıralar
+Halil Soner Özaytekin Tel no:5334080373</t>
   </si>
   <si>
     <t>9 KASIM 2026 PAZARTESİ</t>
@@ -1493,7 +1505,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1707,6 +1719,9 @@
     </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="12" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -2574,9 +2589,11 @@
       <c r="D12" s="75" t="s">
         <v>286</v>
       </c>
-      <c r="E12" s="69"/>
+      <c r="E12" s="71" t="s">
+        <v>287</v>
+      </c>
       <c r="F12" s="70" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G12" s="66"/>
       <c r="H12" s="64"/>
@@ -25935,7 +25952,7 @@
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="42" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -25952,7 +25969,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" ht="87.75" customHeight="1">
@@ -25966,33 +25983,33 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" ht="98.25" customHeight="1">
       <c r="A6" s="49" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C6" s="71" t="s">
         <v>268</v>
@@ -26000,41 +26017,43 @@
       <c r="D6" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="E6" s="49" t="s">
-        <v>297</v>
-      </c>
-      <c r="F6" s="15"/>
+      <c r="E6" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="F6" s="76" t="s">
+        <v>300</v>
+      </c>
       <c r="G6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
       <c r="A8" s="49" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C8" s="71" t="s">
         <v>268</v>
@@ -26042,31 +26061,33 @@
       <c r="D8" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="E8" s="15"/>
+      <c r="E8" s="71" t="s">
+        <v>287</v>
+      </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
@@ -26078,31 +26099,33 @@
       <c r="D10" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="E10" s="15"/>
+      <c r="E10" s="71" t="s">
+        <v>287</v>
+      </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
@@ -26114,15 +26137,17 @@
       <c r="D12" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="E12" s="15"/>
+      <c r="E12" s="71" t="s">
+        <v>287</v>
+      </c>
       <c r="F12" s="15"/>
-      <c r="G12" s="76" t="s">
-        <v>321</v>
+      <c r="G12" s="77" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -26178,7 +26203,7 @@
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -26190,22 +26215,22 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
@@ -26217,31 +26242,33 @@
       <c r="D4" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="E4" s="15"/>
+      <c r="E4" s="71" t="s">
+        <v>287</v>
+      </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
@@ -26253,31 +26280,33 @@
       <c r="D6" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="E6" s="15"/>
+      <c r="E6" s="71" t="s">
+        <v>287</v>
+      </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
@@ -26289,31 +26318,33 @@
       <c r="D8" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="E8" s="15"/>
+      <c r="E8" s="71" t="s">
+        <v>287</v>
+      </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
@@ -26325,22 +26356,24 @@
       <c r="D10" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="E10" s="15"/>
+      <c r="E10" s="71" t="s">
+        <v>287</v>
+      </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -1008,7 +1008,7 @@
     <t xml:space="preserve">25 EKİM 2026 PAZAR </t>
   </si>
   <si>
-    <t xml:space="preserve"> Dedim İyi Fikir Oyunu
+    <t xml:space="preserve"> Bora Gencer-Dedim İyi Fikir Oyunu
 Tel No:5334080373
 Halil Soner Özaytekin ödendi                                        Dans Salonunda pilates 9:00-10:30 arası</t>
   </si>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -1111,7 +1111,7 @@
   </si>
   <si>
     <t>Yaşar Eğitim Kültür Vakfı
-10 Kasım Anma Günü Programı</t>
+10 Kasım Anma Günü Programı 8.00-12.30</t>
   </si>
   <si>
     <t xml:space="preserve">16 KASIM 2026 PAZARTESİ </t>
@@ -2220,7 +2220,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="23.38"/>
-    <col customWidth="1" min="2" max="2" width="20.25"/>
+    <col customWidth="1" min="2" max="2" width="20.75"/>
     <col customWidth="1" min="3" max="3" width="24.13"/>
     <col customWidth="1" min="4" max="4" width="21.5"/>
     <col customWidth="1" min="5" max="5" width="21.25"/>
@@ -26052,7 +26052,7 @@
       <c r="A8" s="49" t="s">
         <v>308</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="34" t="s">
         <v>309</v>
       </c>
       <c r="C8" s="71" t="s">

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="363">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -1037,7 +1037,8 @@
     <t>CUMHURİYET BAYRAMI RESMİ TATİL</t>
   </si>
   <si>
-    <t xml:space="preserve"> Dans Salonunda pilates 9:00-10:30 arası</t>
+    <t xml:space="preserve"> Dans Salonunda pilates 9:00-10:30 arası 
+13.00-16.00 Hacı Murat Prova </t>
   </si>
   <si>
     <t>Gülay Canikli Çeşme Eğitim-Sen
@@ -1114,6 +1115,14 @@
 10 Kasım Anma Günü Programı 8.00-12.30</t>
   </si>
   <si>
+    <t>Kent Konseyi (Her Çarşamba 20.00 - 23.00)
+13.00-16.00 Hacı Murat Prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dans Salonunda pilates 9:00-10:30 arası
+13.00-16.00 Hacı Murat Prova</t>
+  </si>
+  <si>
     <t xml:space="preserve">16 KASIM 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -1135,6 +1144,9 @@
     <t xml:space="preserve">22 KASIM 2026 PAZAR </t>
   </si>
   <si>
+    <t xml:space="preserve"> Dans Salonunda pilates 9:00-10:30 arası</t>
+  </si>
+  <si>
     <t xml:space="preserve">23 KASIM 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -1154,6 +1166,12 @@
   </si>
   <si>
     <t xml:space="preserve">29 KASIM 2026 PAZAR </t>
+  </si>
+  <si>
+    <t>Hacı Murat Hatice Özsoy Prova Tüm Gün</t>
+  </si>
+  <si>
+    <t>Hacı Murat Hatice Özsoy AA. Öğretmenler Günü Etkinliği</t>
   </si>
   <si>
     <t>Tuncay Hoca Çsm</t>
@@ -26056,38 +26074,38 @@
         <v>309</v>
       </c>
       <c r="C8" s="71" t="s">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="D8" s="71" t="s">
         <v>260</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
@@ -26100,37 +26118,41 @@
         <v>260</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
+      <c r="A12" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>328</v>
+      </c>
       <c r="C12" s="71" t="s">
         <v>268</v>
       </c>
@@ -26138,16 +26160,16 @@
         <v>260</v>
       </c>
       <c r="E12" s="71" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="77" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -26203,7 +26225,7 @@
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -26215,22 +26237,22 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="9" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
@@ -26243,32 +26265,32 @@
         <v>260</v>
       </c>
       <c r="E4" s="71" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
@@ -26281,32 +26303,32 @@
         <v>260</v>
       </c>
       <c r="E6" s="71" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
@@ -26319,32 +26341,32 @@
         <v>260</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
@@ -26357,23 +26379,23 @@
         <v>260</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="364">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -1123,6 +1123,9 @@
 13.00-16.00 Hacı Murat Prova</t>
   </si>
   <si>
+    <t xml:space="preserve">Tiyatro Opsiyon çocuk oyunu </t>
+  </si>
+  <si>
     <t xml:space="preserve">16 KASIM 2026 PAZARTESİ </t>
   </si>
   <si>
@@ -1523,7 +1526,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1740,6 +1743,9 @@
     </xf>
     <xf borderId="4" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="12" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -26082,30 +26088,32 @@
       <c r="E8" s="71" t="s">
         <v>311</v>
       </c>
-      <c r="F8" s="15"/>
+      <c r="F8" s="77" t="s">
+        <v>312</v>
+      </c>
       <c r="G8" s="15"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
@@ -26118,40 +26126,40 @@
         <v>260</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
       <c r="A12" s="34" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C12" s="71" t="s">
         <v>268</v>
@@ -26160,16 +26168,16 @@
         <v>260</v>
       </c>
       <c r="E12" s="71" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F12" s="15"/>
-      <c r="G12" s="77" t="s">
-        <v>329</v>
+      <c r="G12" s="78" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -26225,7 +26233,7 @@
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -26237,22 +26245,22 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
@@ -26265,32 +26273,32 @@
         <v>260</v>
       </c>
       <c r="E4" s="71" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
@@ -26303,32 +26311,32 @@
         <v>260</v>
       </c>
       <c r="E6" s="71" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
@@ -26341,32 +26349,32 @@
         <v>260</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
@@ -26379,23 +26387,23 @@
         <v>260</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -1526,7 +1526,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1740,6 +1740,9 @@
     </xf>
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
@@ -26044,10 +26047,10 @@
       <c r="E6" s="34" t="s">
         <v>299</v>
       </c>
-      <c r="F6" s="76" t="s">
+      <c r="F6" s="76"/>
+      <c r="G6" s="77" t="s">
         <v>300</v>
       </c>
-      <c r="G6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
@@ -26088,7 +26091,7 @@
       <c r="E8" s="71" t="s">
         <v>311</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="78" t="s">
         <v>312</v>
       </c>
       <c r="G8" s="15"/>
@@ -26171,7 +26174,7 @@
         <v>320</v>
       </c>
       <c r="F12" s="15"/>
-      <c r="G12" s="78" t="s">
+      <c r="G12" s="79" t="s">
         <v>330</v>
       </c>
     </row>

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -1082,7 +1082,6 @@
   </si>
   <si>
     <t>Rüya Takımı 
-Gülümsten Hatıralar
 Halil Soner Özaytekin Tel no:5334080373</t>
   </si>
   <si>
@@ -1741,10 +1740,10 @@
     <xf borderId="4" fillId="11" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -26047,10 +26046,10 @@
       <c r="E6" s="34" t="s">
         <v>299</v>
       </c>
-      <c r="F6" s="76"/>
-      <c r="G6" s="77" t="s">
+      <c r="F6" s="76" t="s">
         <v>300</v>
       </c>
+      <c r="G6" s="77"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">

--- a/2026 YILI ÇAKABEY.xlsx
+++ b/2026 YILI ÇAKABEY.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="365">
   <si>
     <t xml:space="preserve">2026 YILI ÇAKABEY KÜLTÜR MERKEZİ </t>
   </si>
@@ -1085,6 +1085,9 @@
 Halil Soner Özaytekin Tel no:5334080373</t>
   </si>
   <si>
+    <t>Yeni Parti Seçimi Tüm Gün</t>
+  </si>
+  <si>
     <t>9 KASIM 2026 PAZARTESİ</t>
   </si>
   <si>
@@ -1525,7 +1528,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="79">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1741,9 +1744,6 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -26049,73 +26049,75 @@
       <c r="F6" s="76" t="s">
         <v>300</v>
       </c>
-      <c r="G6" s="77"/>
+      <c r="G6" s="62" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" ht="98.25" customHeight="1">
       <c r="A8" s="49" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C8" s="71" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D8" s="71" t="s">
         <v>260</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="F8" s="78" t="s">
         <v>312</v>
+      </c>
+      <c r="F8" s="77" t="s">
+        <v>313</v>
       </c>
       <c r="G8" s="15"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" ht="107.25" customHeight="1">
@@ -26128,40 +26130,40 @@
         <v>260</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12" ht="103.5" customHeight="1">
       <c r="A12" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C12" s="71" t="s">
         <v>268</v>
@@ -26170,16 +26172,16 @@
         <v>260</v>
       </c>
       <c r="E12" s="71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F12" s="15"/>
-      <c r="G12" s="79" t="s">
-        <v>330</v>
+      <c r="G12" s="78" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -26235,7 +26237,7 @@
     </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -26247,22 +26249,22 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" ht="91.5" customHeight="1">
@@ -26275,32 +26277,32 @@
         <v>260</v>
       </c>
       <c r="E4" s="71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" ht="99.0" customHeight="1">
@@ -26313,32 +26315,32 @@
         <v>260</v>
       </c>
       <c r="E6" s="71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" ht="96.0" customHeight="1">
@@ -26351,32 +26353,32 @@
         <v>260</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" ht="96.75" customHeight="1">
@@ -26389,23 +26391,23 @@
         <v>260</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
